--- a/DATA/DATA FILES/LC RTU DATA.xlsx
+++ b/DATA/DATA FILES/LC RTU DATA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ericc\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B311C942-674D-4A7E-8DFB-4C52BDE0AB50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79390D34-63BC-4EB2-93A3-4391C920E296}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SCHEDULE" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6646" uniqueCount="468">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6790" uniqueCount="474">
   <si>
     <t>SCHEDULE RANGE</t>
   </si>
@@ -1425,16 +1425,48 @@
   </si>
   <si>
     <t>kW</t>
+  </si>
+  <si>
+    <t>10-Ton - MZVAV - HGRH - 460-3 - 0kW</t>
+  </si>
+  <si>
+    <t>10-Ton - MZVAV - HGRH - 208-3 - 0kW</t>
+  </si>
+  <si>
+    <t>8.5-Ton - MZVAV - HGRH - 460-3 - 0kW</t>
+  </si>
+  <si>
+    <t>8.5-Ton - MZVAV - HGRH - 208-3 - 0kW</t>
+  </si>
+  <si>
+    <t>7.5-Ton - MZVAV - HGRH - 460-3 - 0kW</t>
+  </si>
+  <si>
+    <t>7.5-Ton - MZVAV - HGRH - 208-3 - 0kW</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1549,7 +1581,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="44">
+  <borders count="42">
     <border>
       <left/>
       <right/>
@@ -2028,19 +2060,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="medium">
         <color indexed="64"/>
       </left>
@@ -2080,32 +2099,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="medium">
         <color indexed="64"/>
       </left>
@@ -2118,151 +2111,162 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="127">
+  <cellXfs count="135">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="12" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="12" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="10" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="10" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="12" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="12" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="10" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="10" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2301,13 +2305,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2319,176 +2323,200 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="12" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="10" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="12" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="3" fontId="10" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="12" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="10" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="12" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="10" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2824,7 +2852,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BG303"/>
+  <dimension ref="A1:BG309"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="2" bestFit="1" customWidth="1"/>
@@ -2858,7 +2886,7 @@
     <col min="40" max="41" width="6.5703125" style="45" customWidth="1"/>
     <col min="42" max="42" width="27.28515625" style="45" customWidth="1"/>
     <col min="43" max="43" width="25.5703125" style="45" customWidth="1"/>
-    <col min="44" max="44" width="28.28515625" style="45" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="34.140625" style="45" bestFit="1" customWidth="1"/>
     <col min="45" max="45" width="36" style="45" bestFit="1" customWidth="1"/>
     <col min="46" max="46" width="38.85546875" style="45" customWidth="1"/>
     <col min="47" max="47" width="37" style="45" customWidth="1"/>
@@ -2877,272 +2905,272 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:59" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="115" t="s">
+      <c r="A1" s="130" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="111"/>
-      <c r="C1" s="111"/>
-      <c r="D1" s="111"/>
-      <c r="E1" s="111"/>
-      <c r="F1" s="111"/>
-      <c r="G1" s="111"/>
-      <c r="H1" s="111"/>
-      <c r="I1" s="111"/>
-      <c r="J1" s="111"/>
-      <c r="K1" s="111"/>
-      <c r="L1" s="111"/>
-      <c r="M1" s="111"/>
-      <c r="N1" s="111"/>
-      <c r="O1" s="111"/>
-      <c r="P1" s="111"/>
-      <c r="Q1" s="111"/>
-      <c r="R1" s="111"/>
-      <c r="S1" s="111"/>
-      <c r="T1" s="111"/>
-      <c r="U1" s="111"/>
-      <c r="V1" s="111"/>
-      <c r="W1" s="111"/>
-      <c r="X1" s="111"/>
-      <c r="Y1" s="111"/>
-      <c r="Z1" s="111"/>
-      <c r="AA1" s="111"/>
-      <c r="AB1" s="111"/>
-      <c r="AC1" s="111"/>
-      <c r="AD1" s="111"/>
-      <c r="AE1" s="111"/>
-      <c r="AF1" s="112"/>
-      <c r="AH1" s="108" t="s">
+      <c r="B1" s="124"/>
+      <c r="C1" s="124"/>
+      <c r="D1" s="124"/>
+      <c r="E1" s="124"/>
+      <c r="F1" s="124"/>
+      <c r="G1" s="124"/>
+      <c r="H1" s="124"/>
+      <c r="I1" s="124"/>
+      <c r="J1" s="124"/>
+      <c r="K1" s="124"/>
+      <c r="L1" s="124"/>
+      <c r="M1" s="124"/>
+      <c r="N1" s="124"/>
+      <c r="O1" s="124"/>
+      <c r="P1" s="124"/>
+      <c r="Q1" s="124"/>
+      <c r="R1" s="124"/>
+      <c r="S1" s="124"/>
+      <c r="T1" s="124"/>
+      <c r="U1" s="124"/>
+      <c r="V1" s="124"/>
+      <c r="W1" s="124"/>
+      <c r="X1" s="124"/>
+      <c r="Y1" s="124"/>
+      <c r="Z1" s="124"/>
+      <c r="AA1" s="124"/>
+      <c r="AB1" s="124"/>
+      <c r="AC1" s="124"/>
+      <c r="AD1" s="124"/>
+      <c r="AE1" s="124"/>
+      <c r="AF1" s="125"/>
+      <c r="AH1" s="121" t="s">
         <v>1</v>
       </c>
-      <c r="AI1" s="111"/>
-      <c r="AJ1" s="111"/>
-      <c r="AK1" s="111"/>
-      <c r="AL1" s="111"/>
-      <c r="AM1" s="111"/>
-      <c r="AN1" s="112"/>
+      <c r="AI1" s="124"/>
+      <c r="AJ1" s="124"/>
+      <c r="AK1" s="124"/>
+      <c r="AL1" s="124"/>
+      <c r="AM1" s="124"/>
+      <c r="AN1" s="125"/>
       <c r="AO1" s="3"/>
-      <c r="AP1" s="115" t="s">
-        <v>2</v>
-      </c>
-      <c r="AQ1" s="111"/>
-      <c r="AR1" s="111"/>
-      <c r="AS1" s="111"/>
-      <c r="AT1" s="111"/>
-      <c r="AU1" s="111"/>
-      <c r="AV1" s="111"/>
-      <c r="AW1" s="111"/>
-      <c r="AX1" s="111"/>
-      <c r="AY1" s="111"/>
-      <c r="AZ1" s="111"/>
-      <c r="BA1" s="111"/>
-      <c r="BB1" s="111"/>
-      <c r="BC1" s="111"/>
-      <c r="BD1" s="111"/>
-      <c r="BE1" s="111"/>
-      <c r="BF1" s="111"/>
-      <c r="BG1" s="112"/>
+      <c r="AP1" s="130" t="s">
+        <v>2</v>
+      </c>
+      <c r="AQ1" s="124"/>
+      <c r="AR1" s="124"/>
+      <c r="AS1" s="124"/>
+      <c r="AT1" s="124"/>
+      <c r="AU1" s="124"/>
+      <c r="AV1" s="124"/>
+      <c r="AW1" s="124"/>
+      <c r="AX1" s="124"/>
+      <c r="AY1" s="124"/>
+      <c r="AZ1" s="124"/>
+      <c r="BA1" s="124"/>
+      <c r="BB1" s="124"/>
+      <c r="BC1" s="124"/>
+      <c r="BD1" s="124"/>
+      <c r="BE1" s="124"/>
+      <c r="BF1" s="124"/>
+      <c r="BG1" s="125"/>
     </row>
     <row r="2" spans="1:59" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="114" t="s">
+      <c r="A2" s="127" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="111"/>
-      <c r="C2" s="111"/>
-      <c r="D2" s="111"/>
-      <c r="E2" s="111"/>
-      <c r="F2" s="111"/>
-      <c r="G2" s="111"/>
-      <c r="H2" s="111"/>
-      <c r="I2" s="111"/>
-      <c r="J2" s="111"/>
-      <c r="K2" s="111"/>
-      <c r="L2" s="111"/>
-      <c r="M2" s="111"/>
-      <c r="N2" s="111"/>
-      <c r="O2" s="111"/>
-      <c r="P2" s="111"/>
-      <c r="Q2" s="111"/>
-      <c r="R2" s="111"/>
-      <c r="S2" s="111"/>
-      <c r="T2" s="111"/>
-      <c r="U2" s="111"/>
-      <c r="V2" s="111"/>
-      <c r="W2" s="111"/>
-      <c r="X2" s="111"/>
-      <c r="Y2" s="111"/>
-      <c r="Z2" s="111"/>
-      <c r="AA2" s="111"/>
-      <c r="AB2" s="111"/>
-      <c r="AC2" s="111"/>
-      <c r="AD2" s="111"/>
-      <c r="AE2" s="111"/>
-      <c r="AF2" s="112"/>
-      <c r="AH2" s="108" t="s">
+      <c r="B2" s="124"/>
+      <c r="C2" s="124"/>
+      <c r="D2" s="124"/>
+      <c r="E2" s="124"/>
+      <c r="F2" s="124"/>
+      <c r="G2" s="124"/>
+      <c r="H2" s="124"/>
+      <c r="I2" s="124"/>
+      <c r="J2" s="124"/>
+      <c r="K2" s="124"/>
+      <c r="L2" s="124"/>
+      <c r="M2" s="124"/>
+      <c r="N2" s="124"/>
+      <c r="O2" s="124"/>
+      <c r="P2" s="124"/>
+      <c r="Q2" s="124"/>
+      <c r="R2" s="124"/>
+      <c r="S2" s="124"/>
+      <c r="T2" s="124"/>
+      <c r="U2" s="124"/>
+      <c r="V2" s="124"/>
+      <c r="W2" s="124"/>
+      <c r="X2" s="124"/>
+      <c r="Y2" s="124"/>
+      <c r="Z2" s="124"/>
+      <c r="AA2" s="124"/>
+      <c r="AB2" s="124"/>
+      <c r="AC2" s="124"/>
+      <c r="AD2" s="124"/>
+      <c r="AE2" s="124"/>
+      <c r="AF2" s="125"/>
+      <c r="AH2" s="121" t="s">
         <v>4</v>
       </c>
-      <c r="AI2" s="108" t="s">
+      <c r="AI2" s="121" t="s">
         <v>5</v>
       </c>
-      <c r="AJ2" s="108" t="s">
+      <c r="AJ2" s="121" t="s">
         <v>6</v>
       </c>
-      <c r="AK2" s="108" t="s">
+      <c r="AK2" s="121" t="s">
         <v>7</v>
       </c>
-      <c r="AL2" s="108" t="s">
+      <c r="AL2" s="121" t="s">
         <v>8</v>
       </c>
-      <c r="AM2" s="108" t="s">
+      <c r="AM2" s="121" t="s">
         <v>9</v>
       </c>
-      <c r="AN2" s="108" t="s">
+      <c r="AN2" s="121" t="s">
         <v>10</v>
       </c>
       <c r="AO2" s="3"/>
-      <c r="AP2" s="101" t="s">
+      <c r="AP2" s="114" t="s">
         <v>11</v>
       </c>
-      <c r="AQ2" s="101" t="s">
+      <c r="AQ2" s="114" t="s">
         <v>12</v>
       </c>
-      <c r="AR2" s="101" t="s">
+      <c r="AR2" s="114" t="s">
         <v>13</v>
       </c>
-      <c r="AS2" s="101" t="s">
+      <c r="AS2" s="114" t="s">
         <v>14</v>
       </c>
-      <c r="AT2" s="101" t="s">
+      <c r="AT2" s="114" t="s">
         <v>15</v>
       </c>
-      <c r="AU2" s="101" t="s">
+      <c r="AU2" s="114" t="s">
         <v>16</v>
       </c>
-      <c r="AV2" s="101" t="s">
+      <c r="AV2" s="114" t="s">
         <v>17</v>
       </c>
-      <c r="AW2" s="101" t="s">
+      <c r="AW2" s="114" t="s">
         <v>18</v>
       </c>
-      <c r="AX2" s="101" t="s">
+      <c r="AX2" s="114" t="s">
         <v>19</v>
       </c>
-      <c r="AY2" s="101" t="s">
+      <c r="AY2" s="114" t="s">
         <v>20</v>
       </c>
-      <c r="AZ2" s="101" t="s">
+      <c r="AZ2" s="114" t="s">
         <v>21</v>
       </c>
-      <c r="BA2" s="101" t="s">
+      <c r="BA2" s="114" t="s">
         <v>22</v>
       </c>
-      <c r="BB2" s="101" t="s">
+      <c r="BB2" s="114" t="s">
         <v>23</v>
       </c>
-      <c r="BC2" s="101" t="s">
+      <c r="BC2" s="114" t="s">
         <v>24</v>
       </c>
-      <c r="BD2" s="101" t="s">
+      <c r="BD2" s="114" t="s">
         <v>25</v>
       </c>
-      <c r="BE2" s="101" t="s">
+      <c r="BE2" s="114" t="s">
         <v>26</v>
       </c>
-      <c r="BF2" s="101" t="s">
+      <c r="BF2" s="114" t="s">
         <v>27</v>
       </c>
-      <c r="BG2" s="101" t="s">
+      <c r="BG2" s="114" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:59" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="113" t="s">
+      <c r="A3" s="126" t="s">
         <v>464</v>
       </c>
-      <c r="B3" s="106" t="s">
+      <c r="B3" s="119" t="s">
         <v>463</v>
       </c>
-      <c r="C3" s="106" t="s">
+      <c r="C3" s="119" t="s">
         <v>29</v>
       </c>
-      <c r="D3" s="103" t="s">
+      <c r="D3" s="116" t="s">
         <v>30</v>
       </c>
-      <c r="E3" s="104"/>
-      <c r="F3" s="103" t="s">
+      <c r="E3" s="117"/>
+      <c r="F3" s="116" t="s">
         <v>31</v>
       </c>
-      <c r="G3" s="104"/>
-      <c r="H3" s="104"/>
-      <c r="I3" s="104"/>
-      <c r="J3" s="104"/>
-      <c r="K3" s="104"/>
-      <c r="L3" s="105"/>
-      <c r="M3" s="103" t="s">
+      <c r="G3" s="117"/>
+      <c r="H3" s="117"/>
+      <c r="I3" s="117"/>
+      <c r="J3" s="117"/>
+      <c r="K3" s="117"/>
+      <c r="L3" s="118"/>
+      <c r="M3" s="116" t="s">
         <v>32</v>
       </c>
-      <c r="N3" s="104"/>
-      <c r="O3" s="104"/>
-      <c r="P3" s="104"/>
-      <c r="Q3" s="105"/>
-      <c r="R3" s="110" t="s">
+      <c r="N3" s="117"/>
+      <c r="O3" s="117"/>
+      <c r="P3" s="117"/>
+      <c r="Q3" s="118"/>
+      <c r="R3" s="123" t="s">
         <v>33</v>
       </c>
-      <c r="S3" s="111"/>
-      <c r="T3" s="111"/>
-      <c r="U3" s="111"/>
-      <c r="V3" s="111"/>
-      <c r="W3" s="112"/>
-      <c r="X3" s="125" t="s">
+      <c r="S3" s="124"/>
+      <c r="T3" s="124"/>
+      <c r="U3" s="124"/>
+      <c r="V3" s="124"/>
+      <c r="W3" s="125"/>
+      <c r="X3" s="128" t="s">
         <v>34</v>
       </c>
-      <c r="Y3" s="126"/>
-      <c r="Z3" s="116" t="s">
+      <c r="Y3" s="129"/>
+      <c r="Z3" s="131" t="s">
         <v>35</v>
       </c>
-      <c r="AA3" s="109" t="s">
+      <c r="AA3" s="122" t="s">
         <v>36</v>
       </c>
-      <c r="AB3" s="103" t="s">
+      <c r="AB3" s="116" t="s">
         <v>37</v>
       </c>
-      <c r="AC3" s="104"/>
-      <c r="AD3" s="104"/>
-      <c r="AE3" s="105"/>
-      <c r="AF3" s="109" t="s">
+      <c r="AC3" s="117"/>
+      <c r="AD3" s="117"/>
+      <c r="AE3" s="118"/>
+      <c r="AF3" s="122" t="s">
         <v>38</v>
       </c>
       <c r="AG3" s="5"/>
-      <c r="AH3" s="102"/>
-      <c r="AI3" s="102"/>
-      <c r="AJ3" s="102"/>
-      <c r="AK3" s="102"/>
-      <c r="AL3" s="102"/>
-      <c r="AM3" s="102"/>
-      <c r="AN3" s="102"/>
+      <c r="AH3" s="115"/>
+      <c r="AI3" s="115"/>
+      <c r="AJ3" s="115"/>
+      <c r="AK3" s="115"/>
+      <c r="AL3" s="115"/>
+      <c r="AM3" s="115"/>
+      <c r="AN3" s="115"/>
       <c r="AO3" s="3"/>
-      <c r="AP3" s="102"/>
-      <c r="AQ3" s="102"/>
-      <c r="AR3" s="102"/>
-      <c r="AS3" s="102"/>
-      <c r="AT3" s="102"/>
-      <c r="AU3" s="102"/>
-      <c r="AV3" s="102"/>
-      <c r="AW3" s="102"/>
-      <c r="AX3" s="102"/>
-      <c r="AY3" s="102"/>
-      <c r="AZ3" s="102"/>
-      <c r="BA3" s="102"/>
-      <c r="BB3" s="102"/>
-      <c r="BC3" s="102"/>
-      <c r="BD3" s="102"/>
-      <c r="BE3" s="102"/>
-      <c r="BF3" s="102"/>
-      <c r="BG3" s="102"/>
+      <c r="AP3" s="115"/>
+      <c r="AQ3" s="115"/>
+      <c r="AR3" s="115"/>
+      <c r="AS3" s="115"/>
+      <c r="AT3" s="115"/>
+      <c r="AU3" s="115"/>
+      <c r="AV3" s="115"/>
+      <c r="AW3" s="115"/>
+      <c r="AX3" s="115"/>
+      <c r="AY3" s="115"/>
+      <c r="AZ3" s="115"/>
+      <c r="BA3" s="115"/>
+      <c r="BB3" s="115"/>
+      <c r="BC3" s="115"/>
+      <c r="BD3" s="115"/>
+      <c r="BE3" s="115"/>
+      <c r="BF3" s="115"/>
+      <c r="BG3" s="115"/>
     </row>
     <row r="4" spans="1:59" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="107"/>
-      <c r="B4" s="107"/>
-      <c r="C4" s="107"/>
+      <c r="A4" s="120"/>
+      <c r="B4" s="120"/>
+      <c r="C4" s="120"/>
       <c r="D4" s="6" t="s">
         <v>39</v>
       </c>
@@ -3209,8 +3237,8 @@
       <c r="Y4" s="4" t="s">
         <v>466</v>
       </c>
-      <c r="Z4" s="107"/>
-      <c r="AA4" s="107"/>
+      <c r="Z4" s="120"/>
+      <c r="AA4" s="120"/>
       <c r="AB4" s="4" t="s">
         <v>57</v>
       </c>
@@ -3223,33 +3251,33 @@
       <c r="AE4" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="AF4" s="107"/>
-      <c r="AH4" s="107"/>
-      <c r="AI4" s="107"/>
-      <c r="AJ4" s="107"/>
-      <c r="AK4" s="107"/>
-      <c r="AL4" s="107"/>
-      <c r="AM4" s="107"/>
-      <c r="AN4" s="107"/>
+      <c r="AF4" s="120"/>
+      <c r="AH4" s="120"/>
+      <c r="AI4" s="120"/>
+      <c r="AJ4" s="120"/>
+      <c r="AK4" s="120"/>
+      <c r="AL4" s="120"/>
+      <c r="AM4" s="120"/>
+      <c r="AN4" s="120"/>
       <c r="AO4" s="3"/>
-      <c r="AP4" s="102"/>
-      <c r="AQ4" s="102"/>
-      <c r="AR4" s="102"/>
-      <c r="AS4" s="102"/>
-      <c r="AT4" s="102"/>
-      <c r="AU4" s="102"/>
-      <c r="AV4" s="102"/>
-      <c r="AW4" s="102"/>
-      <c r="AX4" s="102"/>
-      <c r="AY4" s="102"/>
-      <c r="AZ4" s="102"/>
-      <c r="BA4" s="102"/>
-      <c r="BB4" s="102"/>
-      <c r="BC4" s="102"/>
-      <c r="BD4" s="102"/>
-      <c r="BE4" s="102"/>
-      <c r="BF4" s="102"/>
-      <c r="BG4" s="102"/>
+      <c r="AP4" s="115"/>
+      <c r="AQ4" s="115"/>
+      <c r="AR4" s="115"/>
+      <c r="AS4" s="115"/>
+      <c r="AT4" s="115"/>
+      <c r="AU4" s="115"/>
+      <c r="AV4" s="115"/>
+      <c r="AW4" s="115"/>
+      <c r="AX4" s="115"/>
+      <c r="AY4" s="115"/>
+      <c r="AZ4" s="115"/>
+      <c r="BA4" s="115"/>
+      <c r="BB4" s="115"/>
+      <c r="BC4" s="115"/>
+      <c r="BD4" s="115"/>
+      <c r="BE4" s="115"/>
+      <c r="BF4" s="115"/>
+      <c r="BG4" s="115"/>
     </row>
     <row r="5" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
@@ -3322,7 +3350,7 @@
       <c r="X5" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="Y5" s="121" t="s">
+      <c r="Y5" s="97" t="s">
         <v>64</v>
       </c>
       <c r="Z5" s="17" t="s">
@@ -3468,7 +3496,7 @@
       <c r="X6" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y6" s="122" t="s">
+      <c r="Y6" s="98" t="s">
         <v>64</v>
       </c>
       <c r="Z6" s="38" t="s">
@@ -3613,7 +3641,7 @@
       <c r="X7" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y7" s="122" t="s">
+      <c r="Y7" s="98" t="s">
         <v>64</v>
       </c>
       <c r="Z7" s="38" t="s">
@@ -3758,7 +3786,7 @@
       <c r="X8" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y8" s="122" t="s">
+      <c r="Y8" s="98" t="s">
         <v>64</v>
       </c>
       <c r="Z8" s="38" t="s">
@@ -3903,7 +3931,7 @@
       <c r="X9" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y9" s="122" t="s">
+      <c r="Y9" s="98" t="s">
         <v>64</v>
       </c>
       <c r="Z9" s="38" t="s">
@@ -4048,7 +4076,7 @@
       <c r="X10" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y10" s="122" t="s">
+      <c r="Y10" s="98" t="s">
         <v>64</v>
       </c>
       <c r="Z10" s="38" t="s">
@@ -4193,7 +4221,7 @@
       <c r="X11" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y11" s="122" t="s">
+      <c r="Y11" s="98" t="s">
         <v>64</v>
       </c>
       <c r="Z11" s="38" t="s">
@@ -4338,7 +4366,7 @@
       <c r="X12" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y12" s="122" t="s">
+      <c r="Y12" s="98" t="s">
         <v>64</v>
       </c>
       <c r="Z12" s="38" t="s">
@@ -4483,7 +4511,7 @@
       <c r="X13" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y13" s="122" t="s">
+      <c r="Y13" s="98" t="s">
         <v>64</v>
       </c>
       <c r="Z13" s="38" t="s">
@@ -4628,7 +4656,7 @@
       <c r="X14" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y14" s="122" t="s">
+      <c r="Y14" s="98" t="s">
         <v>64</v>
       </c>
       <c r="Z14" s="38" t="s">
@@ -4773,7 +4801,7 @@
       <c r="X15" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y15" s="122" t="s">
+      <c r="Y15" s="98" t="s">
         <v>64</v>
       </c>
       <c r="Z15" s="38" t="s">
@@ -4918,7 +4946,7 @@
       <c r="X16" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y16" s="122" t="s">
+      <c r="Y16" s="98" t="s">
         <v>64</v>
       </c>
       <c r="Z16" s="38" t="s">
@@ -5063,7 +5091,7 @@
       <c r="X17" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y17" s="122" t="s">
+      <c r="Y17" s="98" t="s">
         <v>64</v>
       </c>
       <c r="Z17" s="38" t="s">
@@ -5208,7 +5236,7 @@
       <c r="X18" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y18" s="122" t="s">
+      <c r="Y18" s="98" t="s">
         <v>64</v>
       </c>
       <c r="Z18" s="38" t="s">
@@ -5353,7 +5381,7 @@
       <c r="X19" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y19" s="122" t="s">
+      <c r="Y19" s="98" t="s">
         <v>64</v>
       </c>
       <c r="Z19" s="38" t="s">
@@ -5498,7 +5526,7 @@
       <c r="X20" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y20" s="122" t="s">
+      <c r="Y20" s="98" t="s">
         <v>64</v>
       </c>
       <c r="Z20" s="38" t="s">
@@ -5643,7 +5671,7 @@
       <c r="X21" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y21" s="122" t="s">
+      <c r="Y21" s="98" t="s">
         <v>64</v>
       </c>
       <c r="Z21" s="38" t="s">
@@ -5788,7 +5816,7 @@
       <c r="X22" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y22" s="122" t="s">
+      <c r="Y22" s="98" t="s">
         <v>64</v>
       </c>
       <c r="Z22" s="38" t="s">
@@ -5933,7 +5961,7 @@
       <c r="X23" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y23" s="122" t="s">
+      <c r="Y23" s="98" t="s">
         <v>64</v>
       </c>
       <c r="Z23" s="38" t="s">
@@ -6078,7 +6106,7 @@
       <c r="X24" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y24" s="122" t="s">
+      <c r="Y24" s="98" t="s">
         <v>64</v>
       </c>
       <c r="Z24" s="38" t="s">
@@ -6223,7 +6251,7 @@
       <c r="X25" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y25" s="122" t="s">
+      <c r="Y25" s="98" t="s">
         <v>64</v>
       </c>
       <c r="Z25" s="38" t="s">
@@ -6368,7 +6396,7 @@
       <c r="X26" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y26" s="122" t="s">
+      <c r="Y26" s="98" t="s">
         <v>64</v>
       </c>
       <c r="Z26" s="38" t="s">
@@ -6513,7 +6541,7 @@
       <c r="X27" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y27" s="122" t="s">
+      <c r="Y27" s="98" t="s">
         <v>64</v>
       </c>
       <c r="Z27" s="38" t="s">
@@ -6658,7 +6686,7 @@
       <c r="X28" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y28" s="122" t="s">
+      <c r="Y28" s="98" t="s">
         <v>64</v>
       </c>
       <c r="Z28" s="38" t="s">
@@ -6803,7 +6831,7 @@
       <c r="X29" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y29" s="122" t="s">
+      <c r="Y29" s="98" t="s">
         <v>64</v>
       </c>
       <c r="Z29" s="38" t="s">
@@ -6948,7 +6976,7 @@
       <c r="X30" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y30" s="122" t="s">
+      <c r="Y30" s="98" t="s">
         <v>64</v>
       </c>
       <c r="Z30" s="38" t="s">
@@ -7093,7 +7121,7 @@
       <c r="X31" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y31" s="122" t="s">
+      <c r="Y31" s="98" t="s">
         <v>64</v>
       </c>
       <c r="Z31" s="38" t="s">
@@ -7238,7 +7266,7 @@
       <c r="X32" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y32" s="122" t="s">
+      <c r="Y32" s="98" t="s">
         <v>64</v>
       </c>
       <c r="Z32" s="38" t="s">
@@ -7383,7 +7411,7 @@
       <c r="X33" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y33" s="122" t="s">
+      <c r="Y33" s="98" t="s">
         <v>64</v>
       </c>
       <c r="Z33" s="38" t="s">
@@ -7528,7 +7556,7 @@
       <c r="X34" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y34" s="122" t="s">
+      <c r="Y34" s="98" t="s">
         <v>64</v>
       </c>
       <c r="Z34" s="38" t="s">
@@ -7673,7 +7701,7 @@
       <c r="X35" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y35" s="122" t="s">
+      <c r="Y35" s="98" t="s">
         <v>64</v>
       </c>
       <c r="Z35" s="38" t="s">
@@ -7818,7 +7846,7 @@
       <c r="X36" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y36" s="122" t="s">
+      <c r="Y36" s="98" t="s">
         <v>64</v>
       </c>
       <c r="Z36" s="38" t="s">
@@ -7963,7 +7991,7 @@
       <c r="X37" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y37" s="122" t="s">
+      <c r="Y37" s="98" t="s">
         <v>64</v>
       </c>
       <c r="Z37" s="38" t="s">
@@ -8108,7 +8136,7 @@
       <c r="X38" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y38" s="122" t="s">
+      <c r="Y38" s="98" t="s">
         <v>64</v>
       </c>
       <c r="Z38" s="38" t="s">
@@ -8253,7 +8281,7 @@
       <c r="X39" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y39" s="122" t="s">
+      <c r="Y39" s="98" t="s">
         <v>64</v>
       </c>
       <c r="Z39" s="38" t="s">
@@ -8398,7 +8426,7 @@
       <c r="X40" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y40" s="122" t="s">
+      <c r="Y40" s="98" t="s">
         <v>64</v>
       </c>
       <c r="Z40" s="38" t="s">
@@ -8543,7 +8571,7 @@
       <c r="X41" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y41" s="122" t="s">
+      <c r="Y41" s="98" t="s">
         <v>64</v>
       </c>
       <c r="Z41" s="38" t="s">
@@ -8688,7 +8716,7 @@
       <c r="X42" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y42" s="122" t="s">
+      <c r="Y42" s="98" t="s">
         <v>64</v>
       </c>
       <c r="Z42" s="38" t="s">
@@ -8833,7 +8861,7 @@
       <c r="X43" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y43" s="122" t="s">
+      <c r="Y43" s="98" t="s">
         <v>64</v>
       </c>
       <c r="Z43" s="38" t="s">
@@ -8978,7 +9006,7 @@
       <c r="X44" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y44" s="122" t="s">
+      <c r="Y44" s="98" t="s">
         <v>64</v>
       </c>
       <c r="Z44" s="38" t="s">
@@ -9123,7 +9151,7 @@
       <c r="X45" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y45" s="122" t="s">
+      <c r="Y45" s="98" t="s">
         <v>64</v>
       </c>
       <c r="Z45" s="38" t="s">
@@ -9268,7 +9296,7 @@
       <c r="X46" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y46" s="122" t="s">
+      <c r="Y46" s="98" t="s">
         <v>64</v>
       </c>
       <c r="Z46" s="38" t="s">
@@ -9413,7 +9441,7 @@
       <c r="X47" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y47" s="122" t="s">
+      <c r="Y47" s="98" t="s">
         <v>64</v>
       </c>
       <c r="Z47" s="38" t="s">
@@ -9558,7 +9586,7 @@
       <c r="X48" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y48" s="122" t="s">
+      <c r="Y48" s="98" t="s">
         <v>64</v>
       </c>
       <c r="Z48" s="38" t="s">
@@ -9703,7 +9731,7 @@
       <c r="X49" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y49" s="122" t="s">
+      <c r="Y49" s="98" t="s">
         <v>64</v>
       </c>
       <c r="Z49" s="38" t="s">
@@ -9848,7 +9876,7 @@
       <c r="X50" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y50" s="122" t="s">
+      <c r="Y50" s="98" t="s">
         <v>64</v>
       </c>
       <c r="Z50" s="38" t="s">
@@ -9993,7 +10021,7 @@
       <c r="X51" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y51" s="122" t="s">
+      <c r="Y51" s="98" t="s">
         <v>64</v>
       </c>
       <c r="Z51" s="38" t="s">
@@ -10138,7 +10166,7 @@
       <c r="X52" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y52" s="122" t="s">
+      <c r="Y52" s="98" t="s">
         <v>64</v>
       </c>
       <c r="Z52" s="38" t="s">
@@ -10283,7 +10311,7 @@
       <c r="X53" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y53" s="122" t="s">
+      <c r="Y53" s="98" t="s">
         <v>64</v>
       </c>
       <c r="Z53" s="38" t="s">
@@ -10428,7 +10456,7 @@
       <c r="X54" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y54" s="122" t="s">
+      <c r="Y54" s="98" t="s">
         <v>64</v>
       </c>
       <c r="Z54" s="38" t="s">
@@ -10573,7 +10601,7 @@
       <c r="X55" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y55" s="122" t="s">
+      <c r="Y55" s="98" t="s">
         <v>64</v>
       </c>
       <c r="Z55" s="38" t="s">
@@ -10718,7 +10746,7 @@
       <c r="X56" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y56" s="122" t="s">
+      <c r="Y56" s="98" t="s">
         <v>64</v>
       </c>
       <c r="Z56" s="38" t="s">
@@ -10863,7 +10891,7 @@
       <c r="X57" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y57" s="122" t="s">
+      <c r="Y57" s="98" t="s">
         <v>64</v>
       </c>
       <c r="Z57" s="38" t="s">
@@ -11008,7 +11036,7 @@
       <c r="X58" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y58" s="122" t="s">
+      <c r="Y58" s="98" t="s">
         <v>64</v>
       </c>
       <c r="Z58" s="38" t="s">
@@ -11153,7 +11181,7 @@
       <c r="X59" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y59" s="122" t="s">
+      <c r="Y59" s="98" t="s">
         <v>64</v>
       </c>
       <c r="Z59" s="38" t="s">
@@ -11298,7 +11326,7 @@
       <c r="X60" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y60" s="122" t="s">
+      <c r="Y60" s="98" t="s">
         <v>64</v>
       </c>
       <c r="Z60" s="38" t="s">
@@ -11443,7 +11471,7 @@
       <c r="X61" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y61" s="122" t="s">
+      <c r="Y61" s="98" t="s">
         <v>64</v>
       </c>
       <c r="Z61" s="38" t="s">
@@ -11588,7 +11616,7 @@
       <c r="X62" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y62" s="122" t="s">
+      <c r="Y62" s="98" t="s">
         <v>64</v>
       </c>
       <c r="Z62" s="38" t="s">
@@ -11733,7 +11761,7 @@
       <c r="X63" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y63" s="122" t="s">
+      <c r="Y63" s="98" t="s">
         <v>64</v>
       </c>
       <c r="Z63" s="38" t="s">
@@ -11878,7 +11906,7 @@
       <c r="X64" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y64" s="122" t="s">
+      <c r="Y64" s="98" t="s">
         <v>64</v>
       </c>
       <c r="Z64" s="38" t="s">
@@ -12023,7 +12051,7 @@
       <c r="X65" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y65" s="122" t="s">
+      <c r="Y65" s="98" t="s">
         <v>64</v>
       </c>
       <c r="Z65" s="38" t="s">
@@ -12168,7 +12196,7 @@
       <c r="X66" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y66" s="122" t="s">
+      <c r="Y66" s="98" t="s">
         <v>64</v>
       </c>
       <c r="Z66" s="38" t="s">
@@ -12313,7 +12341,7 @@
       <c r="X67" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y67" s="122" t="s">
+      <c r="Y67" s="98" t="s">
         <v>64</v>
       </c>
       <c r="Z67" s="38" t="s">
@@ -12458,7 +12486,7 @@
       <c r="X68" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y68" s="122" t="s">
+      <c r="Y68" s="98" t="s">
         <v>64</v>
       </c>
       <c r="Z68" s="38" t="s">
@@ -12603,7 +12631,7 @@
       <c r="X69" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y69" s="122" t="s">
+      <c r="Y69" s="98" t="s">
         <v>64</v>
       </c>
       <c r="Z69" s="38" t="s">
@@ -12748,7 +12776,7 @@
       <c r="X70" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y70" s="122" t="s">
+      <c r="Y70" s="98" t="s">
         <v>64</v>
       </c>
       <c r="Z70" s="38" t="s">
@@ -12893,7 +12921,7 @@
       <c r="X71" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y71" s="122" t="s">
+      <c r="Y71" s="98" t="s">
         <v>64</v>
       </c>
       <c r="Z71" s="38" t="s">
@@ -13038,7 +13066,7 @@
       <c r="X72" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y72" s="122" t="s">
+      <c r="Y72" s="98" t="s">
         <v>64</v>
       </c>
       <c r="Z72" s="38" t="s">
@@ -13183,7 +13211,7 @@
       <c r="X73" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y73" s="122" t="s">
+      <c r="Y73" s="98" t="s">
         <v>64</v>
       </c>
       <c r="Z73" s="38" t="s">
@@ -13328,7 +13356,7 @@
       <c r="X74" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y74" s="122" t="s">
+      <c r="Y74" s="98" t="s">
         <v>64</v>
       </c>
       <c r="Z74" s="38" t="s">
@@ -13473,7 +13501,7 @@
       <c r="X75" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y75" s="122" t="s">
+      <c r="Y75" s="98" t="s">
         <v>64</v>
       </c>
       <c r="Z75" s="38" t="s">
@@ -13618,7 +13646,7 @@
       <c r="X76" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y76" s="122" t="s">
+      <c r="Y76" s="98" t="s">
         <v>64</v>
       </c>
       <c r="Z76" s="38" t="s">
@@ -13763,7 +13791,7 @@
       <c r="X77" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y77" s="122" t="s">
+      <c r="Y77" s="98" t="s">
         <v>64</v>
       </c>
       <c r="Z77" s="38" t="s">
@@ -13908,7 +13936,7 @@
       <c r="X78" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y78" s="122" t="s">
+      <c r="Y78" s="98" t="s">
         <v>64</v>
       </c>
       <c r="Z78" s="38" t="s">
@@ -14053,7 +14081,7 @@
       <c r="X79" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y79" s="122" t="s">
+      <c r="Y79" s="98" t="s">
         <v>64</v>
       </c>
       <c r="Z79" s="38" t="s">
@@ -14198,7 +14226,7 @@
       <c r="X80" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y80" s="122" t="s">
+      <c r="Y80" s="98" t="s">
         <v>64</v>
       </c>
       <c r="Z80" s="38" t="s">
@@ -14343,7 +14371,7 @@
       <c r="X81" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y81" s="122" t="s">
+      <c r="Y81" s="98" t="s">
         <v>64</v>
       </c>
       <c r="Z81" s="38" t="s">
@@ -14488,7 +14516,7 @@
       <c r="X82" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y82" s="122" t="s">
+      <c r="Y82" s="98" t="s">
         <v>64</v>
       </c>
       <c r="Z82" s="38" t="s">
@@ -14633,7 +14661,7 @@
       <c r="X83" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y83" s="122" t="s">
+      <c r="Y83" s="98" t="s">
         <v>64</v>
       </c>
       <c r="Z83" s="38" t="s">
@@ -14778,7 +14806,7 @@
       <c r="X84" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y84" s="122" t="s">
+      <c r="Y84" s="98" t="s">
         <v>64</v>
       </c>
       <c r="Z84" s="38" t="s">
@@ -14923,7 +14951,7 @@
       <c r="X85" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y85" s="122" t="s">
+      <c r="Y85" s="98" t="s">
         <v>64</v>
       </c>
       <c r="Z85" s="38" t="s">
@@ -15068,7 +15096,7 @@
       <c r="X86" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y86" s="122" t="s">
+      <c r="Y86" s="98" t="s">
         <v>64</v>
       </c>
       <c r="Z86" s="38" t="s">
@@ -15213,7 +15241,7 @@
       <c r="X87" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y87" s="122" t="s">
+      <c r="Y87" s="98" t="s">
         <v>64</v>
       </c>
       <c r="Z87" s="38" t="s">
@@ -15358,7 +15386,7 @@
       <c r="X88" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y88" s="122" t="s">
+      <c r="Y88" s="98" t="s">
         <v>64</v>
       </c>
       <c r="Z88" s="38" t="s">
@@ -15503,7 +15531,7 @@
       <c r="X89" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y89" s="122" t="s">
+      <c r="Y89" s="98" t="s">
         <v>64</v>
       </c>
       <c r="Z89" s="38" t="s">
@@ -15648,7 +15676,7 @@
       <c r="X90" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y90" s="122" t="s">
+      <c r="Y90" s="98" t="s">
         <v>64</v>
       </c>
       <c r="Z90" s="38" t="s">
@@ -15793,7 +15821,7 @@
       <c r="X91" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y91" s="122" t="s">
+      <c r="Y91" s="98" t="s">
         <v>64</v>
       </c>
       <c r="Z91" s="38" t="s">
@@ -15938,7 +15966,7 @@
       <c r="X92" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y92" s="122" t="s">
+      <c r="Y92" s="98" t="s">
         <v>64</v>
       </c>
       <c r="Z92" s="38" t="s">
@@ -16083,7 +16111,7 @@
       <c r="X93" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y93" s="122" t="s">
+      <c r="Y93" s="98" t="s">
         <v>64</v>
       </c>
       <c r="Z93" s="38" t="s">
@@ -16228,7 +16256,7 @@
       <c r="X94" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y94" s="122" t="s">
+      <c r="Y94" s="98" t="s">
         <v>64</v>
       </c>
       <c r="Z94" s="38" t="s">
@@ -16373,7 +16401,7 @@
       <c r="X95" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y95" s="122" t="s">
+      <c r="Y95" s="98" t="s">
         <v>64</v>
       </c>
       <c r="Z95" s="38" t="s">
@@ -16518,7 +16546,7 @@
       <c r="X96" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y96" s="122" t="s">
+      <c r="Y96" s="98" t="s">
         <v>64</v>
       </c>
       <c r="Z96" s="38" t="s">
@@ -16663,7 +16691,7 @@
       <c r="X97" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y97" s="122" t="s">
+      <c r="Y97" s="98" t="s">
         <v>64</v>
       </c>
       <c r="Z97" s="38" t="s">
@@ -16808,7 +16836,7 @@
       <c r="X98" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y98" s="122" t="s">
+      <c r="Y98" s="98" t="s">
         <v>64</v>
       </c>
       <c r="Z98" s="38" t="s">
@@ -16953,7 +16981,7 @@
       <c r="X99" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y99" s="122" t="s">
+      <c r="Y99" s="98" t="s">
         <v>64</v>
       </c>
       <c r="Z99" s="38" t="s">
@@ -17098,7 +17126,7 @@
       <c r="X100" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y100" s="122" t="s">
+      <c r="Y100" s="98" t="s">
         <v>64</v>
       </c>
       <c r="Z100" s="38" t="s">
@@ -17243,7 +17271,7 @@
       <c r="X101" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y101" s="122" t="s">
+      <c r="Y101" s="98" t="s">
         <v>64</v>
       </c>
       <c r="Z101" s="38" t="s">
@@ -17388,7 +17416,7 @@
       <c r="X102" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y102" s="122" t="s">
+      <c r="Y102" s="98" t="s">
         <v>64</v>
       </c>
       <c r="Z102" s="38" t="s">
@@ -17533,7 +17561,7 @@
       <c r="X103" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y103" s="122" t="s">
+      <c r="Y103" s="98" t="s">
         <v>64</v>
       </c>
       <c r="Z103" s="38" t="s">
@@ -17678,7 +17706,7 @@
       <c r="X104" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y104" s="122" t="s">
+      <c r="Y104" s="98" t="s">
         <v>64</v>
       </c>
       <c r="Z104" s="38" t="s">
@@ -17823,7 +17851,7 @@
       <c r="X105" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y105" s="122" t="s">
+      <c r="Y105" s="98" t="s">
         <v>64</v>
       </c>
       <c r="Z105" s="38" t="s">
@@ -17968,7 +17996,7 @@
       <c r="X106" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y106" s="122" t="s">
+      <c r="Y106" s="98" t="s">
         <v>64</v>
       </c>
       <c r="Z106" s="38" t="s">
@@ -18113,7 +18141,7 @@
       <c r="X107" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y107" s="122" t="s">
+      <c r="Y107" s="98" t="s">
         <v>64</v>
       </c>
       <c r="Z107" s="38" t="s">
@@ -18258,7 +18286,7 @@
       <c r="X108" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y108" s="122" t="s">
+      <c r="Y108" s="98" t="s">
         <v>64</v>
       </c>
       <c r="Z108" s="38" t="s">
@@ -18403,7 +18431,7 @@
       <c r="X109" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y109" s="122" t="s">
+      <c r="Y109" s="98" t="s">
         <v>64</v>
       </c>
       <c r="Z109" s="38" t="s">
@@ -18548,7 +18576,7 @@
       <c r="X110" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y110" s="122" t="s">
+      <c r="Y110" s="98" t="s">
         <v>64</v>
       </c>
       <c r="Z110" s="38" t="s">
@@ -18693,7 +18721,7 @@
       <c r="X111" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y111" s="122" t="s">
+      <c r="Y111" s="98" t="s">
         <v>64</v>
       </c>
       <c r="Z111" s="38" t="s">
@@ -18838,7 +18866,7 @@
       <c r="X112" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y112" s="122" t="s">
+      <c r="Y112" s="98" t="s">
         <v>64</v>
       </c>
       <c r="Z112" s="38" t="s">
@@ -18983,7 +19011,7 @@
       <c r="X113" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y113" s="122" t="s">
+      <c r="Y113" s="98" t="s">
         <v>64</v>
       </c>
       <c r="Z113" s="38" t="s">
@@ -19128,7 +19156,7 @@
       <c r="X114" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y114" s="122" t="s">
+      <c r="Y114" s="98" t="s">
         <v>64</v>
       </c>
       <c r="Z114" s="38" t="s">
@@ -19273,7 +19301,7 @@
       <c r="X115" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y115" s="122" t="s">
+      <c r="Y115" s="98" t="s">
         <v>64</v>
       </c>
       <c r="Z115" s="38" t="s">
@@ -19418,7 +19446,7 @@
       <c r="X116" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y116" s="122" t="s">
+      <c r="Y116" s="98" t="s">
         <v>64</v>
       </c>
       <c r="Z116" s="38" t="s">
@@ -19563,7 +19591,7 @@
       <c r="X117" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y117" s="122" t="s">
+      <c r="Y117" s="98" t="s">
         <v>64</v>
       </c>
       <c r="Z117" s="38" t="s">
@@ -19708,7 +19736,7 @@
       <c r="X118" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y118" s="122" t="s">
+      <c r="Y118" s="98" t="s">
         <v>64</v>
       </c>
       <c r="Z118" s="38" t="s">
@@ -19853,7 +19881,7 @@
       <c r="X119" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y119" s="122" t="s">
+      <c r="Y119" s="98" t="s">
         <v>64</v>
       </c>
       <c r="Z119" s="53" t="s">
@@ -19999,7 +20027,7 @@
       <c r="X120" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y120" s="122" t="s">
+      <c r="Y120" s="98" t="s">
         <v>64</v>
       </c>
       <c r="Z120" s="53" t="s">
@@ -20145,7 +20173,7 @@
       <c r="X121" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y121" s="122" t="s">
+      <c r="Y121" s="98" t="s">
         <v>64</v>
       </c>
       <c r="Z121" s="53" t="s">
@@ -20291,7 +20319,7 @@
       <c r="X122" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y122" s="122" t="s">
+      <c r="Y122" s="98" t="s">
         <v>64</v>
       </c>
       <c r="Z122" s="53" t="s">
@@ -20437,7 +20465,7 @@
       <c r="X123" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y123" s="122" t="s">
+      <c r="Y123" s="98" t="s">
         <v>64</v>
       </c>
       <c r="Z123" s="53" t="s">
@@ -20583,7 +20611,7 @@
       <c r="X124" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y124" s="122" t="s">
+      <c r="Y124" s="98" t="s">
         <v>64</v>
       </c>
       <c r="Z124" s="53" t="s">
@@ -20729,7 +20757,7 @@
       <c r="X125" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y125" s="122" t="s">
+      <c r="Y125" s="98" t="s">
         <v>64</v>
       </c>
       <c r="Z125" s="53" t="s">
@@ -20875,7 +20903,7 @@
       <c r="X126" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y126" s="122" t="s">
+      <c r="Y126" s="98" t="s">
         <v>64</v>
       </c>
       <c r="Z126" s="53" t="s">
@@ -21021,7 +21049,7 @@
       <c r="X127" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y127" s="122" t="s">
+      <c r="Y127" s="98" t="s">
         <v>64</v>
       </c>
       <c r="Z127" s="53" t="s">
@@ -21167,7 +21195,7 @@
       <c r="X128" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y128" s="122" t="s">
+      <c r="Y128" s="98" t="s">
         <v>64</v>
       </c>
       <c r="Z128" s="53" t="s">
@@ -21313,7 +21341,7 @@
       <c r="X129" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y129" s="122" t="s">
+      <c r="Y129" s="98" t="s">
         <v>64</v>
       </c>
       <c r="Z129" s="53" t="s">
@@ -21459,7 +21487,7 @@
       <c r="X130" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y130" s="122" t="s">
+      <c r="Y130" s="98" t="s">
         <v>64</v>
       </c>
       <c r="Z130" s="53" t="s">
@@ -21605,7 +21633,7 @@
       <c r="X131" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y131" s="122" t="s">
+      <c r="Y131" s="98" t="s">
         <v>64</v>
       </c>
       <c r="Z131" s="53" t="s">
@@ -21751,7 +21779,7 @@
       <c r="X132" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y132" s="122" t="s">
+      <c r="Y132" s="98" t="s">
         <v>64</v>
       </c>
       <c r="Z132" s="53" t="s">
@@ -21897,7 +21925,7 @@
       <c r="X133" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y133" s="122" t="s">
+      <c r="Y133" s="98" t="s">
         <v>64</v>
       </c>
       <c r="Z133" s="53" t="s">
@@ -22043,7 +22071,7 @@
       <c r="X134" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y134" s="122" t="s">
+      <c r="Y134" s="98" t="s">
         <v>64</v>
       </c>
       <c r="Z134" s="53" t="s">
@@ -22189,7 +22217,7 @@
       <c r="X135" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y135" s="122" t="s">
+      <c r="Y135" s="98" t="s">
         <v>64</v>
       </c>
       <c r="Z135" s="53" t="s">
@@ -22335,7 +22363,7 @@
       <c r="X136" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y136" s="122" t="s">
+      <c r="Y136" s="98" t="s">
         <v>64</v>
       </c>
       <c r="Z136" s="53" t="s">
@@ -22481,7 +22509,7 @@
       <c r="X137" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y137" s="122" t="s">
+      <c r="Y137" s="98" t="s">
         <v>64</v>
       </c>
       <c r="Z137" s="53" t="s">
@@ -22627,7 +22655,7 @@
       <c r="X138" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y138" s="122" t="s">
+      <c r="Y138" s="98" t="s">
         <v>64</v>
       </c>
       <c r="Z138" s="53" t="s">
@@ -22773,7 +22801,7 @@
       <c r="X139" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y139" s="122" t="s">
+      <c r="Y139" s="98" t="s">
         <v>64</v>
       </c>
       <c r="Z139" s="53" t="s">
@@ -22919,7 +22947,7 @@
       <c r="X140" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y140" s="122" t="s">
+      <c r="Y140" s="98" t="s">
         <v>64</v>
       </c>
       <c r="Z140" s="53" t="s">
@@ -23065,7 +23093,7 @@
       <c r="X141" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y141" s="122" t="s">
+      <c r="Y141" s="98" t="s">
         <v>64</v>
       </c>
       <c r="Z141" s="53" t="s">
@@ -23211,7 +23239,7 @@
       <c r="X142" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y142" s="122" t="s">
+      <c r="Y142" s="98" t="s">
         <v>64</v>
       </c>
       <c r="Z142" s="53" t="s">
@@ -23357,7 +23385,7 @@
       <c r="X143" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y143" s="122" t="s">
+      <c r="Y143" s="98" t="s">
         <v>64</v>
       </c>
       <c r="Z143" s="53" t="s">
@@ -23503,7 +23531,7 @@
       <c r="X144" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y144" s="122" t="s">
+      <c r="Y144" s="98" t="s">
         <v>64</v>
       </c>
       <c r="Z144" s="53" t="s">
@@ -23649,7 +23677,7 @@
       <c r="X145" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y145" s="122" t="s">
+      <c r="Y145" s="98" t="s">
         <v>64</v>
       </c>
       <c r="Z145" s="53" t="s">
@@ -23795,7 +23823,7 @@
       <c r="X146" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y146" s="122" t="s">
+      <c r="Y146" s="98" t="s">
         <v>64</v>
       </c>
       <c r="Z146" s="53" t="s">
@@ -23941,7 +23969,7 @@
       <c r="X147" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y147" s="122" t="s">
+      <c r="Y147" s="98" t="s">
         <v>64</v>
       </c>
       <c r="Z147" s="53" t="s">
@@ -24087,7 +24115,7 @@
       <c r="X148" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y148" s="122" t="s">
+      <c r="Y148" s="98" t="s">
         <v>64</v>
       </c>
       <c r="Z148" s="53" t="s">
@@ -24233,7 +24261,7 @@
       <c r="X149" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y149" s="122" t="s">
+      <c r="Y149" s="98" t="s">
         <v>64</v>
       </c>
       <c r="Z149" s="53" t="s">
@@ -24379,7 +24407,7 @@
       <c r="X150" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y150" s="122" t="s">
+      <c r="Y150" s="98" t="s">
         <v>64</v>
       </c>
       <c r="Z150" s="53" t="s">
@@ -24525,7 +24553,7 @@
       <c r="X151" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y151" s="122" t="s">
+      <c r="Y151" s="98" t="s">
         <v>64</v>
       </c>
       <c r="Z151" s="53" t="s">
@@ -24671,7 +24699,7 @@
       <c r="X152" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y152" s="122" t="s">
+      <c r="Y152" s="98" t="s">
         <v>64</v>
       </c>
       <c r="Z152" s="53" t="s">
@@ -24817,7 +24845,7 @@
       <c r="X153" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y153" s="122" t="s">
+      <c r="Y153" s="98" t="s">
         <v>64</v>
       </c>
       <c r="Z153" s="53" t="s">
@@ -24963,7 +24991,7 @@
       <c r="X154" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y154" s="122" t="s">
+      <c r="Y154" s="98" t="s">
         <v>64</v>
       </c>
       <c r="Z154" s="53" t="s">
@@ -25109,7 +25137,7 @@
       <c r="X155" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y155" s="122" t="s">
+      <c r="Y155" s="98" t="s">
         <v>64</v>
       </c>
       <c r="Z155" s="53" t="s">
@@ -25255,7 +25283,7 @@
       <c r="X156" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y156" s="122" t="s">
+      <c r="Y156" s="98" t="s">
         <v>64</v>
       </c>
       <c r="Z156" s="53" t="s">
@@ -25401,7 +25429,7 @@
       <c r="X157" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y157" s="122" t="s">
+      <c r="Y157" s="98" t="s">
         <v>64</v>
       </c>
       <c r="Z157" s="53" t="s">
@@ -25547,7 +25575,7 @@
       <c r="X158" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y158" s="122" t="s">
+      <c r="Y158" s="98" t="s">
         <v>64</v>
       </c>
       <c r="Z158" s="53" t="s">
@@ -25693,7 +25721,7 @@
       <c r="X159" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y159" s="122" t="s">
+      <c r="Y159" s="98" t="s">
         <v>64</v>
       </c>
       <c r="Z159" s="53" t="s">
@@ -25839,7 +25867,7 @@
       <c r="X160" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y160" s="122" t="s">
+      <c r="Y160" s="98" t="s">
         <v>64</v>
       </c>
       <c r="Z160" s="53" t="s">
@@ -25985,7 +26013,7 @@
       <c r="X161" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y161" s="122" t="s">
+      <c r="Y161" s="98" t="s">
         <v>64</v>
       </c>
       <c r="Z161" s="53" t="s">
@@ -26131,7 +26159,7 @@
       <c r="X162" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y162" s="122" t="s">
+      <c r="Y162" s="98" t="s">
         <v>64</v>
       </c>
       <c r="Z162" s="53" t="s">
@@ -26277,7 +26305,7 @@
       <c r="X163" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y163" s="122" t="s">
+      <c r="Y163" s="98" t="s">
         <v>64</v>
       </c>
       <c r="Z163" s="53" t="s">
@@ -26423,7 +26451,7 @@
       <c r="X164" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y164" s="122" t="s">
+      <c r="Y164" s="98" t="s">
         <v>64</v>
       </c>
       <c r="Z164" s="53" t="s">
@@ -26569,7 +26597,7 @@
       <c r="X165" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y165" s="122" t="s">
+      <c r="Y165" s="98" t="s">
         <v>64</v>
       </c>
       <c r="Z165" s="53" t="s">
@@ -26715,7 +26743,7 @@
       <c r="X166" s="60" t="s">
         <v>64</v>
       </c>
-      <c r="Y166" s="123" t="s">
+      <c r="Y166" s="99" t="s">
         <v>64</v>
       </c>
       <c r="Z166" s="63" t="s">
@@ -26860,7 +26888,7 @@
         <v>5</v>
       </c>
       <c r="Y167" s="75"/>
-      <c r="Z167" s="118" t="s">
+      <c r="Z167" s="95" t="s">
         <v>65</v>
       </c>
       <c r="AA167" s="7">
@@ -27001,7 +27029,7 @@
         <v>45</v>
       </c>
       <c r="Y168" s="83"/>
-      <c r="Z168" s="119" t="s">
+      <c r="Z168" s="96" t="s">
         <v>65</v>
       </c>
       <c r="AA168" s="28">
@@ -27142,7 +27170,7 @@
         <v>30</v>
       </c>
       <c r="Y169" s="83"/>
-      <c r="Z169" s="119" t="s">
+      <c r="Z169" s="96" t="s">
         <v>65</v>
       </c>
       <c r="AA169" s="28">
@@ -27283,7 +27311,7 @@
         <v>20</v>
       </c>
       <c r="Y170" s="83"/>
-      <c r="Z170" s="119" t="s">
+      <c r="Z170" s="96" t="s">
         <v>65</v>
       </c>
       <c r="AA170" s="28">
@@ -27424,7 +27452,7 @@
         <v>60</v>
       </c>
       <c r="Y171" s="83"/>
-      <c r="Z171" s="119" t="s">
+      <c r="Z171" s="96" t="s">
         <v>65</v>
       </c>
       <c r="AA171" s="28">
@@ -27565,7 +27593,7 @@
         <v>45</v>
       </c>
       <c r="Y172" s="83"/>
-      <c r="Z172" s="119" t="s">
+      <c r="Z172" s="96" t="s">
         <v>65</v>
       </c>
       <c r="AA172" s="28">
@@ -27706,7 +27734,7 @@
         <v>15</v>
       </c>
       <c r="Y173" s="83"/>
-      <c r="Z173" s="119" t="s">
+      <c r="Z173" s="96" t="s">
         <v>65</v>
       </c>
       <c r="AA173" s="28">
@@ -27847,7 +27875,7 @@
         <v>10</v>
       </c>
       <c r="Y174" s="83"/>
-      <c r="Z174" s="119" t="s">
+      <c r="Z174" s="96" t="s">
         <v>65</v>
       </c>
       <c r="AA174" s="28">
@@ -27988,7 +28016,7 @@
         <v>30</v>
       </c>
       <c r="Y175" s="83"/>
-      <c r="Z175" s="119" t="s">
+      <c r="Z175" s="96" t="s">
         <v>65</v>
       </c>
       <c r="AA175" s="28">
@@ -28129,7 +28157,7 @@
         <v>20</v>
       </c>
       <c r="Y176" s="83"/>
-      <c r="Z176" s="119" t="s">
+      <c r="Z176" s="96" t="s">
         <v>65</v>
       </c>
       <c r="AA176" s="28">
@@ -28269,10 +28297,10 @@
       <c r="X177" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y177" s="122" t="s">
-        <v>64</v>
-      </c>
-      <c r="Z177" s="119" t="s">
+      <c r="Y177" s="98" t="s">
+        <v>64</v>
+      </c>
+      <c r="Z177" s="96" t="s">
         <v>65</v>
       </c>
       <c r="AA177" s="28">
@@ -28412,10 +28440,10 @@
       <c r="X178" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y178" s="122" t="s">
-        <v>64</v>
-      </c>
-      <c r="Z178" s="119" t="s">
+      <c r="Y178" s="98" t="s">
+        <v>64</v>
+      </c>
+      <c r="Z178" s="96" t="s">
         <v>65</v>
       </c>
       <c r="AA178" s="28" t="s">
@@ -28555,10 +28583,10 @@
       <c r="X179" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y179" s="122" t="s">
-        <v>64</v>
-      </c>
-      <c r="Z179" s="119" t="s">
+      <c r="Y179" s="98" t="s">
+        <v>64</v>
+      </c>
+      <c r="Z179" s="96" t="s">
         <v>65</v>
       </c>
       <c r="AA179" s="28" t="s">
@@ -28698,10 +28726,10 @@
       <c r="X180" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y180" s="122" t="s">
-        <v>64</v>
-      </c>
-      <c r="Z180" s="119" t="s">
+      <c r="Y180" s="98" t="s">
+        <v>64</v>
+      </c>
+      <c r="Z180" s="96" t="s">
         <v>65</v>
       </c>
       <c r="AA180" s="28" t="s">
@@ -28841,10 +28869,10 @@
       <c r="X181" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y181" s="122" t="s">
-        <v>64</v>
-      </c>
-      <c r="Z181" s="119" t="s">
+      <c r="Y181" s="98" t="s">
+        <v>64</v>
+      </c>
+      <c r="Z181" s="96" t="s">
         <v>65</v>
       </c>
       <c r="AA181" s="28" t="s">
@@ -28984,10 +29012,10 @@
       <c r="X182" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y182" s="122" t="s">
-        <v>64</v>
-      </c>
-      <c r="Z182" s="119" t="s">
+      <c r="Y182" s="98" t="s">
+        <v>64</v>
+      </c>
+      <c r="Z182" s="96" t="s">
         <v>65</v>
       </c>
       <c r="AA182" s="28" t="s">
@@ -29127,10 +29155,10 @@
       <c r="X183" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y183" s="122" t="s">
-        <v>64</v>
-      </c>
-      <c r="Z183" s="119" t="s">
+      <c r="Y183" s="98" t="s">
+        <v>64</v>
+      </c>
+      <c r="Z183" s="96" t="s">
         <v>65</v>
       </c>
       <c r="AA183" s="28" t="s">
@@ -29271,7 +29299,7 @@
         <v>15</v>
       </c>
       <c r="Y184" s="83"/>
-      <c r="Z184" s="119" t="s">
+      <c r="Z184" s="96" t="s">
         <v>65</v>
       </c>
       <c r="AA184" s="28">
@@ -29412,7 +29440,7 @@
         <v>10</v>
       </c>
       <c r="Y185" s="83"/>
-      <c r="Z185" s="119" t="s">
+      <c r="Z185" s="96" t="s">
         <v>65</v>
       </c>
       <c r="AA185" s="28">
@@ -29553,7 +29581,7 @@
         <v>5</v>
       </c>
       <c r="Y186" s="83"/>
-      <c r="Z186" s="119" t="s">
+      <c r="Z186" s="96" t="s">
         <v>65</v>
       </c>
       <c r="AA186" s="28">
@@ -29694,7 +29722,7 @@
         <v>30</v>
       </c>
       <c r="Y187" s="83"/>
-      <c r="Z187" s="119" t="s">
+      <c r="Z187" s="96" t="s">
         <v>65</v>
       </c>
       <c r="AA187" s="28">
@@ -29835,7 +29863,7 @@
         <v>20</v>
       </c>
       <c r="Y188" s="83"/>
-      <c r="Z188" s="119" t="s">
+      <c r="Z188" s="96" t="s">
         <v>65</v>
       </c>
       <c r="AA188" s="28">
@@ -29976,7 +30004,7 @@
         <v>15</v>
       </c>
       <c r="Y189" s="83"/>
-      <c r="Z189" s="119" t="s">
+      <c r="Z189" s="96" t="s">
         <v>65</v>
       </c>
       <c r="AA189" s="28">
@@ -30117,7 +30145,7 @@
         <v>10</v>
       </c>
       <c r="Y190" s="83"/>
-      <c r="Z190" s="119" t="s">
+      <c r="Z190" s="96" t="s">
         <v>65</v>
       </c>
       <c r="AA190" s="28">
@@ -30258,7 +30286,7 @@
         <v>10</v>
       </c>
       <c r="Y191" s="83"/>
-      <c r="Z191" s="119" t="s">
+      <c r="Z191" s="96" t="s">
         <v>65</v>
       </c>
       <c r="AA191" s="28">
@@ -30399,7 +30427,7 @@
         <v>5</v>
       </c>
       <c r="Y192" s="83"/>
-      <c r="Z192" s="119" t="s">
+      <c r="Z192" s="96" t="s">
         <v>65</v>
       </c>
       <c r="AA192" s="28">
@@ -30539,10 +30567,10 @@
       <c r="X193" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y193" s="122" t="s">
-        <v>64</v>
-      </c>
-      <c r="Z193" s="119" t="s">
+      <c r="Y193" s="98" t="s">
+        <v>64</v>
+      </c>
+      <c r="Z193" s="96" t="s">
         <v>65</v>
       </c>
       <c r="AA193" s="28">
@@ -30683,7 +30711,7 @@
         <v>20</v>
       </c>
       <c r="Y194" s="83"/>
-      <c r="Z194" s="119" t="s">
+      <c r="Z194" s="96" t="s">
         <v>65</v>
       </c>
       <c r="AA194" s="28">
@@ -30824,7 +30852,7 @@
         <v>5</v>
       </c>
       <c r="Y195" s="83"/>
-      <c r="Z195" s="119" t="s">
+      <c r="Z195" s="96" t="s">
         <v>65</v>
       </c>
       <c r="AA195" s="28">
@@ -30965,7 +30993,7 @@
         <v>15</v>
       </c>
       <c r="Y196" s="83"/>
-      <c r="Z196" s="119" t="s">
+      <c r="Z196" s="96" t="s">
         <v>65</v>
       </c>
       <c r="AA196" s="28">
@@ -31105,10 +31133,10 @@
       <c r="X197" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y197" s="122" t="s">
-        <v>64</v>
-      </c>
-      <c r="Z197" s="119" t="s">
+      <c r="Y197" s="98" t="s">
+        <v>64</v>
+      </c>
+      <c r="Z197" s="96" t="s">
         <v>65</v>
       </c>
       <c r="AA197" s="28">
@@ -31249,7 +31277,7 @@
         <v>5</v>
       </c>
       <c r="Y198" s="83"/>
-      <c r="Z198" s="119" t="s">
+      <c r="Z198" s="96" t="s">
         <v>65</v>
       </c>
       <c r="AA198" s="28">
@@ -31390,7 +31418,7 @@
         <v>20</v>
       </c>
       <c r="Y199" s="83"/>
-      <c r="Z199" s="119" t="s">
+      <c r="Z199" s="96" t="s">
         <v>65</v>
       </c>
       <c r="AA199" s="28">
@@ -31531,7 +31559,7 @@
         <v>10</v>
       </c>
       <c r="Y200" s="83"/>
-      <c r="Z200" s="119" t="s">
+      <c r="Z200" s="96" t="s">
         <v>65</v>
       </c>
       <c r="AA200" s="28">
@@ -31671,10 +31699,10 @@
       <c r="X201" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y201" s="122" t="s">
-        <v>64</v>
-      </c>
-      <c r="Z201" s="119" t="s">
+      <c r="Y201" s="98" t="s">
+        <v>64</v>
+      </c>
+      <c r="Z201" s="96" t="s">
         <v>65</v>
       </c>
       <c r="AA201" s="28">
@@ -31815,7 +31843,7 @@
         <v>10</v>
       </c>
       <c r="Y202" s="83"/>
-      <c r="Z202" s="119" t="s">
+      <c r="Z202" s="96" t="s">
         <v>65</v>
       </c>
       <c r="AA202" s="28">
@@ -31955,10 +31983,10 @@
       <c r="X203" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y203" s="122" t="s">
-        <v>64</v>
-      </c>
-      <c r="Z203" s="119" t="s">
+      <c r="Y203" s="98" t="s">
+        <v>64</v>
+      </c>
+      <c r="Z203" s="96" t="s">
         <v>65</v>
       </c>
       <c r="AA203" s="28">
@@ -32099,7 +32127,7 @@
         <v>10</v>
       </c>
       <c r="Y204" s="83"/>
-      <c r="Z204" s="119" t="s">
+      <c r="Z204" s="96" t="s">
         <v>65</v>
       </c>
       <c r="AA204" s="28">
@@ -32240,7 +32268,7 @@
         <v>5</v>
       </c>
       <c r="Y205" s="83"/>
-      <c r="Z205" s="119" t="s">
+      <c r="Z205" s="96" t="s">
         <v>65</v>
       </c>
       <c r="AA205" s="28">
@@ -32381,7 +32409,7 @@
         <v>15</v>
       </c>
       <c r="Y206" s="83"/>
-      <c r="Z206" s="119" t="s">
+      <c r="Z206" s="96" t="s">
         <v>65</v>
       </c>
       <c r="AA206" s="28">
@@ -32521,10 +32549,10 @@
       <c r="X207" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y207" s="122" t="s">
-        <v>64</v>
-      </c>
-      <c r="Z207" s="119" t="s">
+      <c r="Y207" s="98" t="s">
+        <v>64</v>
+      </c>
+      <c r="Z207" s="96" t="s">
         <v>65</v>
       </c>
       <c r="AA207" s="28">
@@ -32665,7 +32693,7 @@
         <v>20</v>
       </c>
       <c r="Y208" s="83"/>
-      <c r="Z208" s="119" t="s">
+      <c r="Z208" s="96" t="s">
         <v>65</v>
       </c>
       <c r="AA208" s="28">
@@ -32806,7 +32834,7 @@
         <v>15</v>
       </c>
       <c r="Y209" s="83"/>
-      <c r="Z209" s="119" t="s">
+      <c r="Z209" s="96" t="s">
         <v>65</v>
       </c>
       <c r="AA209" s="28">
@@ -32947,7 +32975,7 @@
         <v>5</v>
       </c>
       <c r="Y210" s="83"/>
-      <c r="Z210" s="119" t="s">
+      <c r="Z210" s="96" t="s">
         <v>65</v>
       </c>
       <c r="AA210" s="28">
@@ -33088,7 +33116,7 @@
         <v>10</v>
       </c>
       <c r="Y211" s="83"/>
-      <c r="Z211" s="119" t="s">
+      <c r="Z211" s="96" t="s">
         <v>65</v>
       </c>
       <c r="AA211" s="28">
@@ -33229,7 +33257,7 @@
         <v>5</v>
       </c>
       <c r="Y212" s="83"/>
-      <c r="Z212" s="119" t="s">
+      <c r="Z212" s="96" t="s">
         <v>65</v>
       </c>
       <c r="AA212" s="28">
@@ -33369,10 +33397,10 @@
       <c r="X213" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y213" s="122" t="s">
-        <v>64</v>
-      </c>
-      <c r="Z213" s="119" t="s">
+      <c r="Y213" s="98" t="s">
+        <v>64</v>
+      </c>
+      <c r="Z213" s="96" t="s">
         <v>65</v>
       </c>
       <c r="AA213" s="28">
@@ -33513,7 +33541,7 @@
         <v>15</v>
       </c>
       <c r="Y214" s="83"/>
-      <c r="Z214" s="119" t="s">
+      <c r="Z214" s="96" t="s">
         <v>65</v>
       </c>
       <c r="AA214" s="28">
@@ -33654,7 +33682,7 @@
         <v>15</v>
       </c>
       <c r="Y215" s="83"/>
-      <c r="Z215" s="119" t="s">
+      <c r="Z215" s="96" t="s">
         <v>65</v>
       </c>
       <c r="AA215" s="28">
@@ -33795,7 +33823,7 @@
         <v>5</v>
       </c>
       <c r="Y216" s="83"/>
-      <c r="Z216" s="119" t="s">
+      <c r="Z216" s="96" t="s">
         <v>65</v>
       </c>
       <c r="AA216" s="28">
@@ -33935,10 +33963,10 @@
       <c r="X217" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y217" s="122" t="s">
-        <v>64</v>
-      </c>
-      <c r="Z217" s="119" t="s">
+      <c r="Y217" s="98" t="s">
+        <v>64</v>
+      </c>
+      <c r="Z217" s="96" t="s">
         <v>65</v>
       </c>
       <c r="AA217" s="28">
@@ -34079,7 +34107,7 @@
         <v>20</v>
       </c>
       <c r="Y218" s="83"/>
-      <c r="Z218" s="119" t="s">
+      <c r="Z218" s="96" t="s">
         <v>65</v>
       </c>
       <c r="AA218" s="28">
@@ -34220,7 +34248,7 @@
         <v>15</v>
       </c>
       <c r="Y219" s="83"/>
-      <c r="Z219" s="119" t="s">
+      <c r="Z219" s="96" t="s">
         <v>65</v>
       </c>
       <c r="AA219" s="28">
@@ -34361,7 +34389,7 @@
         <v>60</v>
       </c>
       <c r="Y220" s="83"/>
-      <c r="Z220" s="119" t="s">
+      <c r="Z220" s="96" t="s">
         <v>65</v>
       </c>
       <c r="AA220" s="28">
@@ -34501,10 +34529,10 @@
       <c r="X221" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y221" s="122" t="s">
-        <v>64</v>
-      </c>
-      <c r="Z221" s="119" t="s">
+      <c r="Y221" s="98" t="s">
+        <v>64</v>
+      </c>
+      <c r="Z221" s="96" t="s">
         <v>65</v>
       </c>
       <c r="AA221" s="28">
@@ -34645,7 +34673,7 @@
         <v>60</v>
       </c>
       <c r="Y222" s="83"/>
-      <c r="Z222" s="119" t="s">
+      <c r="Z222" s="96" t="s">
         <v>65</v>
       </c>
       <c r="AA222" s="28">
@@ -34786,7 +34814,7 @@
         <v>75</v>
       </c>
       <c r="Y223" s="83"/>
-      <c r="Z223" s="119" t="s">
+      <c r="Z223" s="96" t="s">
         <v>65</v>
       </c>
       <c r="AA223" s="28">
@@ -34927,7 +34955,7 @@
         <v>45</v>
       </c>
       <c r="Y224" s="83"/>
-      <c r="Z224" s="119" t="s">
+      <c r="Z224" s="96" t="s">
         <v>65</v>
       </c>
       <c r="AA224" s="28">
@@ -35068,7 +35096,7 @@
         <v>30</v>
       </c>
       <c r="Y225" s="83"/>
-      <c r="Z225" s="119" t="s">
+      <c r="Z225" s="96" t="s">
         <v>65</v>
       </c>
       <c r="AA225" s="28">
@@ -35209,7 +35237,7 @@
         <v>75</v>
       </c>
       <c r="Y226" s="83"/>
-      <c r="Z226" s="119" t="s">
+      <c r="Z226" s="96" t="s">
         <v>65</v>
       </c>
       <c r="AA226" s="28">
@@ -35350,7 +35378,7 @@
         <v>60</v>
       </c>
       <c r="Y227" s="83"/>
-      <c r="Z227" s="119" t="s">
+      <c r="Z227" s="96" t="s">
         <v>65</v>
       </c>
       <c r="AA227" s="28">
@@ -35491,7 +35519,7 @@
         <v>45</v>
       </c>
       <c r="Y228" s="83"/>
-      <c r="Z228" s="119" t="s">
+      <c r="Z228" s="96" t="s">
         <v>65</v>
       </c>
       <c r="AA228" s="28">
@@ -35632,7 +35660,7 @@
         <v>30</v>
       </c>
       <c r="Y229" s="83"/>
-      <c r="Z229" s="119" t="s">
+      <c r="Z229" s="96" t="s">
         <v>65</v>
       </c>
       <c r="AA229" s="28">
@@ -35772,10 +35800,10 @@
       <c r="X230" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y230" s="122" t="s">
-        <v>64</v>
-      </c>
-      <c r="Z230" s="119" t="s">
+      <c r="Y230" s="98" t="s">
+        <v>64</v>
+      </c>
+      <c r="Z230" s="96" t="s">
         <v>65</v>
       </c>
       <c r="AA230" s="28">
@@ -35915,10 +35943,10 @@
       <c r="X231" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y231" s="122" t="s">
-        <v>64</v>
-      </c>
-      <c r="Z231" s="119" t="s">
+      <c r="Y231" s="98" t="s">
+        <v>64</v>
+      </c>
+      <c r="Z231" s="96" t="s">
         <v>65</v>
       </c>
       <c r="AA231" s="28">
@@ -36059,7 +36087,7 @@
         <v>60</v>
       </c>
       <c r="Y232" s="83"/>
-      <c r="Z232" s="119" t="s">
+      <c r="Z232" s="96" t="s">
         <v>65</v>
       </c>
       <c r="AA232" s="28">
@@ -36200,7 +36228,7 @@
         <v>45</v>
       </c>
       <c r="Y233" s="83"/>
-      <c r="Z233" s="119" t="s">
+      <c r="Z233" s="96" t="s">
         <v>65</v>
       </c>
       <c r="AA233" s="28">
@@ -36341,7 +36369,7 @@
         <v>30</v>
       </c>
       <c r="Y234" s="83"/>
-      <c r="Z234" s="119" t="s">
+      <c r="Z234" s="96" t="s">
         <v>65</v>
       </c>
       <c r="AA234" s="28">
@@ -36481,10 +36509,10 @@
       <c r="X235" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y235" s="122" t="s">
-        <v>64</v>
-      </c>
-      <c r="Z235" s="119" t="s">
+      <c r="Y235" s="98" t="s">
+        <v>64</v>
+      </c>
+      <c r="Z235" s="96" t="s">
         <v>65</v>
       </c>
       <c r="AA235" s="28">
@@ -36625,7 +36653,7 @@
         <v>30</v>
       </c>
       <c r="Y236" s="83"/>
-      <c r="Z236" s="119" t="s">
+      <c r="Z236" s="96" t="s">
         <v>65</v>
       </c>
       <c r="AA236" s="28">
@@ -36765,10 +36793,10 @@
       <c r="X237" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y237" s="122" t="s">
-        <v>64</v>
-      </c>
-      <c r="Z237" s="119" t="s">
+      <c r="Y237" s="98" t="s">
+        <v>64</v>
+      </c>
+      <c r="Z237" s="96" t="s">
         <v>65</v>
       </c>
       <c r="AA237" s="28">
@@ -36909,7 +36937,7 @@
         <v>60</v>
       </c>
       <c r="Y238" s="83"/>
-      <c r="Z238" s="119" t="s">
+      <c r="Z238" s="96" t="s">
         <v>65</v>
       </c>
       <c r="AA238" s="28">
@@ -37050,7 +37078,7 @@
         <v>30</v>
       </c>
       <c r="Y239" s="83"/>
-      <c r="Z239" s="119" t="s">
+      <c r="Z239" s="96" t="s">
         <v>65</v>
       </c>
       <c r="AA239" s="28">
@@ -37191,7 +37219,7 @@
         <v>45</v>
       </c>
       <c r="Y240" s="83"/>
-      <c r="Z240" s="119" t="s">
+      <c r="Z240" s="96" t="s">
         <v>65</v>
       </c>
       <c r="AA240" s="28">
@@ -37332,7 +37360,7 @@
         <v>30</v>
       </c>
       <c r="Y241" s="83"/>
-      <c r="Z241" s="119" t="s">
+      <c r="Z241" s="96" t="s">
         <v>65</v>
       </c>
       <c r="AA241" s="28">
@@ -37473,7 +37501,7 @@
         <v>15</v>
       </c>
       <c r="Y242" s="83"/>
-      <c r="Z242" s="119" t="s">
+      <c r="Z242" s="96" t="s">
         <v>65</v>
       </c>
       <c r="AA242" s="28">
@@ -37613,10 +37641,10 @@
       <c r="X243" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y243" s="122" t="s">
-        <v>64</v>
-      </c>
-      <c r="Z243" s="119" t="s">
+      <c r="Y243" s="98" t="s">
+        <v>64</v>
+      </c>
+      <c r="Z243" s="96" t="s">
         <v>65</v>
       </c>
       <c r="AA243" s="28">
@@ -37757,7 +37785,7 @@
         <v>45</v>
       </c>
       <c r="Y244" s="83"/>
-      <c r="Z244" s="119" t="s">
+      <c r="Z244" s="96" t="s">
         <v>65</v>
       </c>
       <c r="AA244" s="28">
@@ -37897,10 +37925,10 @@
       <c r="X245" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y245" s="122" t="s">
-        <v>64</v>
-      </c>
-      <c r="Z245" s="119" t="s">
+      <c r="Y245" s="98" t="s">
+        <v>64</v>
+      </c>
+      <c r="Z245" s="96" t="s">
         <v>65</v>
       </c>
       <c r="AA245" s="28">
@@ -38041,7 +38069,7 @@
         <v>45</v>
       </c>
       <c r="Y246" s="83"/>
-      <c r="Z246" s="119" t="s">
+      <c r="Z246" s="96" t="s">
         <v>65</v>
       </c>
       <c r="AA246" s="28">
@@ -38182,7 +38210,7 @@
         <v>30</v>
       </c>
       <c r="Y247" s="83"/>
-      <c r="Z247" s="119" t="s">
+      <c r="Z247" s="96" t="s">
         <v>65</v>
       </c>
       <c r="AA247" s="28">
@@ -38323,7 +38351,7 @@
         <v>15</v>
       </c>
       <c r="Y248" s="83"/>
-      <c r="Z248" s="119" t="s">
+      <c r="Z248" s="96" t="s">
         <v>65</v>
       </c>
       <c r="AA248" s="28">
@@ -38463,10 +38491,10 @@
       <c r="X249" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y249" s="122" t="s">
-        <v>64</v>
-      </c>
-      <c r="Z249" s="119" t="s">
+      <c r="Y249" s="98" t="s">
+        <v>64</v>
+      </c>
+      <c r="Z249" s="96" t="s">
         <v>65</v>
       </c>
       <c r="AA249" s="28">
@@ -38606,10 +38634,10 @@
       <c r="X250" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y250" s="122" t="s">
-        <v>64</v>
-      </c>
-      <c r="Z250" s="119" t="s">
+      <c r="Y250" s="98" t="s">
+        <v>64</v>
+      </c>
+      <c r="Z250" s="96" t="s">
         <v>65</v>
       </c>
       <c r="AA250" s="28">
@@ -38750,7 +38778,7 @@
         <v>15</v>
       </c>
       <c r="Y251" s="83"/>
-      <c r="Z251" s="119" t="s">
+      <c r="Z251" s="96" t="s">
         <v>65</v>
       </c>
       <c r="AA251" s="28">
@@ -38890,10 +38918,10 @@
       <c r="X252" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y252" s="122" t="s">
-        <v>64</v>
-      </c>
-      <c r="Z252" s="119" t="s">
+      <c r="Y252" s="98" t="s">
+        <v>64</v>
+      </c>
+      <c r="Z252" s="96" t="s">
         <v>65</v>
       </c>
       <c r="AA252" s="28">
@@ -39034,7 +39062,7 @@
         <v>45</v>
       </c>
       <c r="Y253" s="83"/>
-      <c r="Z253" s="119" t="s">
+      <c r="Z253" s="96" t="s">
         <v>65</v>
       </c>
       <c r="AA253" s="28">
@@ -39175,7 +39203,7 @@
         <v>30</v>
       </c>
       <c r="Y254" s="83"/>
-      <c r="Z254" s="119" t="s">
+      <c r="Z254" s="96" t="s">
         <v>65</v>
       </c>
       <c r="AA254" s="28">
@@ -39316,7 +39344,7 @@
         <v>15</v>
       </c>
       <c r="Y255" s="83"/>
-      <c r="Z255" s="119" t="s">
+      <c r="Z255" s="96" t="s">
         <v>65</v>
       </c>
       <c r="AA255" s="28">
@@ -39456,10 +39484,10 @@
       <c r="X256" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y256" s="122" t="s">
-        <v>64</v>
-      </c>
-      <c r="Z256" s="119" t="s">
+      <c r="Y256" s="98" t="s">
+        <v>64</v>
+      </c>
+      <c r="Z256" s="96" t="s">
         <v>65</v>
       </c>
       <c r="AA256" s="28">
@@ -39600,7 +39628,7 @@
         <v>45</v>
       </c>
       <c r="Y257" s="83"/>
-      <c r="Z257" s="119" t="s">
+      <c r="Z257" s="96" t="s">
         <v>65</v>
       </c>
       <c r="AA257" s="28">
@@ -39741,7 +39769,7 @@
         <v>30</v>
       </c>
       <c r="Y258" s="83"/>
-      <c r="Z258" s="119" t="s">
+      <c r="Z258" s="96" t="s">
         <v>65</v>
       </c>
       <c r="AA258" s="28">
@@ -39882,7 +39910,7 @@
         <v>15</v>
       </c>
       <c r="Y259" s="83"/>
-      <c r="Z259" s="119" t="s">
+      <c r="Z259" s="96" t="s">
         <v>65</v>
       </c>
       <c r="AA259" s="28">
@@ -40023,7 +40051,7 @@
         <v>45</v>
       </c>
       <c r="Y260" s="83"/>
-      <c r="Z260" s="119" t="s">
+      <c r="Z260" s="96" t="s">
         <v>65</v>
       </c>
       <c r="AA260" s="28">
@@ -40164,7 +40192,7 @@
         <v>30</v>
       </c>
       <c r="Y261" s="83"/>
-      <c r="Z261" s="119" t="s">
+      <c r="Z261" s="96" t="s">
         <v>65</v>
       </c>
       <c r="AA261" s="28">
@@ -40305,7 +40333,7 @@
         <v>15</v>
       </c>
       <c r="Y262" s="83"/>
-      <c r="Z262" s="119" t="s">
+      <c r="Z262" s="96" t="s">
         <v>65</v>
       </c>
       <c r="AA262" s="28">
@@ -40445,10 +40473,10 @@
       <c r="X263" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y263" s="122" t="s">
-        <v>64</v>
-      </c>
-      <c r="Z263" s="119" t="s">
+      <c r="Y263" s="98" t="s">
+        <v>64</v>
+      </c>
+      <c r="Z263" s="96" t="s">
         <v>65</v>
       </c>
       <c r="AA263" s="28">
@@ -40589,7 +40617,7 @@
         <v>45</v>
       </c>
       <c r="Y264" s="83"/>
-      <c r="Z264" s="119" t="s">
+      <c r="Z264" s="96" t="s">
         <v>65</v>
       </c>
       <c r="AA264" s="28">
@@ -40730,7 +40758,7 @@
         <v>30</v>
       </c>
       <c r="Y265" s="83"/>
-      <c r="Z265" s="119" t="s">
+      <c r="Z265" s="96" t="s">
         <v>65</v>
       </c>
       <c r="AA265" s="28">
@@ -40871,7 +40899,7 @@
         <v>15</v>
       </c>
       <c r="Y266" s="83"/>
-      <c r="Z266" s="119" t="s">
+      <c r="Z266" s="96" t="s">
         <v>65</v>
       </c>
       <c r="AA266" s="28">
@@ -41011,10 +41039,10 @@
       <c r="X267" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y267" s="122" t="s">
-        <v>64</v>
-      </c>
-      <c r="Z267" s="119" t="s">
+      <c r="Y267" s="98" t="s">
+        <v>64</v>
+      </c>
+      <c r="Z267" s="96" t="s">
         <v>65</v>
       </c>
       <c r="AA267" s="28">
@@ -41155,7 +41183,7 @@
         <v>5</v>
       </c>
       <c r="Y268" s="83"/>
-      <c r="Z268" s="119" t="s">
+      <c r="Z268" s="96" t="s">
         <v>65</v>
       </c>
       <c r="AA268" s="28">
@@ -41296,7 +41324,7 @@
         <v>30</v>
       </c>
       <c r="Y269" s="83"/>
-      <c r="Z269" s="119" t="s">
+      <c r="Z269" s="96" t="s">
         <v>65</v>
       </c>
       <c r="AA269" s="28">
@@ -41437,7 +41465,7 @@
         <v>15</v>
       </c>
       <c r="Y270" s="83"/>
-      <c r="Z270" s="119" t="s">
+      <c r="Z270" s="96" t="s">
         <v>65</v>
       </c>
       <c r="AA270" s="28">
@@ -41578,7 +41606,7 @@
         <v>10</v>
       </c>
       <c r="Y271" s="83"/>
-      <c r="Z271" s="119" t="s">
+      <c r="Z271" s="96" t="s">
         <v>65</v>
       </c>
       <c r="AA271" s="28">
@@ -41718,10 +41746,10 @@
       <c r="X272" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y272" s="122" t="s">
-        <v>64</v>
-      </c>
-      <c r="Z272" s="119" t="s">
+      <c r="Y272" s="98" t="s">
+        <v>64</v>
+      </c>
+      <c r="Z272" s="96" t="s">
         <v>65</v>
       </c>
       <c r="AA272" s="28">
@@ -41862,7 +41890,7 @@
         <v>30</v>
       </c>
       <c r="Y273" s="83"/>
-      <c r="Z273" s="119" t="s">
+      <c r="Z273" s="96" t="s">
         <v>65</v>
       </c>
       <c r="AA273" s="28">
@@ -42003,7 +42031,7 @@
         <v>20</v>
       </c>
       <c r="Y274" s="83"/>
-      <c r="Z274" s="119" t="s">
+      <c r="Z274" s="96" t="s">
         <v>65</v>
       </c>
       <c r="AA274" s="28">
@@ -42144,7 +42172,7 @@
         <v>15</v>
       </c>
       <c r="Y275" s="83"/>
-      <c r="Z275" s="119" t="s">
+      <c r="Z275" s="96" t="s">
         <v>65</v>
       </c>
       <c r="AA275" s="28">
@@ -42285,7 +42313,7 @@
         <v>10</v>
       </c>
       <c r="Y276" s="83"/>
-      <c r="Z276" s="119" t="s">
+      <c r="Z276" s="96" t="s">
         <v>65</v>
       </c>
       <c r="AA276" s="28">
@@ -42425,10 +42453,10 @@
       <c r="X277" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y277" s="122" t="s">
-        <v>64</v>
-      </c>
-      <c r="Z277" s="119" t="s">
+      <c r="Y277" s="98" t="s">
+        <v>64</v>
+      </c>
+      <c r="Z277" s="96" t="s">
         <v>65</v>
       </c>
       <c r="AA277" s="28">
@@ -42569,7 +42597,7 @@
         <v>15</v>
       </c>
       <c r="Y278" s="83"/>
-      <c r="Z278" s="119" t="s">
+      <c r="Z278" s="96" t="s">
         <v>65</v>
       </c>
       <c r="AA278" s="28">
@@ -42710,7 +42738,7 @@
         <v>10</v>
       </c>
       <c r="Y279" s="83"/>
-      <c r="Z279" s="119" t="s">
+      <c r="Z279" s="96" t="s">
         <v>65</v>
       </c>
       <c r="AA279" s="28">
@@ -42851,7 +42879,7 @@
         <v>5</v>
       </c>
       <c r="Y280" s="83"/>
-      <c r="Z280" s="119" t="s">
+      <c r="Z280" s="96" t="s">
         <v>65</v>
       </c>
       <c r="AA280" s="28">
@@ -42991,10 +43019,10 @@
       <c r="X281" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y281" s="122" t="s">
-        <v>64</v>
-      </c>
-      <c r="Z281" s="119" t="s">
+      <c r="Y281" s="98" t="s">
+        <v>64</v>
+      </c>
+      <c r="Z281" s="96" t="s">
         <v>65</v>
       </c>
       <c r="AA281" s="28">
@@ -43135,7 +43163,7 @@
         <v>20</v>
       </c>
       <c r="Y282" s="83"/>
-      <c r="Z282" s="119" t="s">
+      <c r="Z282" s="96" t="s">
         <v>65</v>
       </c>
       <c r="AA282" s="28">
@@ -43276,7 +43304,7 @@
         <v>15</v>
       </c>
       <c r="Y283" s="83"/>
-      <c r="Z283" s="119" t="s">
+      <c r="Z283" s="96" t="s">
         <v>65</v>
       </c>
       <c r="AA283" s="28">
@@ -43417,7 +43445,7 @@
         <v>5</v>
       </c>
       <c r="Y284" s="83"/>
-      <c r="Z284" s="119" t="s">
+      <c r="Z284" s="96" t="s">
         <v>65</v>
       </c>
       <c r="AA284" s="28">
@@ -43557,10 +43585,10 @@
       <c r="X285" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y285" s="122" t="s">
-        <v>64</v>
-      </c>
-      <c r="Z285" s="119" t="s">
+      <c r="Y285" s="98" t="s">
+        <v>64</v>
+      </c>
+      <c r="Z285" s="96" t="s">
         <v>65</v>
       </c>
       <c r="AA285" s="28">
@@ -43701,7 +43729,7 @@
         <v>20</v>
       </c>
       <c r="Y286" s="83"/>
-      <c r="Z286" s="119" t="s">
+      <c r="Z286" s="96" t="s">
         <v>65</v>
       </c>
       <c r="AA286" s="28">
@@ -43842,7 +43870,7 @@
         <v>15</v>
       </c>
       <c r="Y287" s="83"/>
-      <c r="Z287" s="119" t="s">
+      <c r="Z287" s="96" t="s">
         <v>65</v>
       </c>
       <c r="AA287" s="28">
@@ -43983,7 +44011,7 @@
         <v>10</v>
       </c>
       <c r="Y288" s="83"/>
-      <c r="Z288" s="119" t="s">
+      <c r="Z288" s="96" t="s">
         <v>65</v>
       </c>
       <c r="AA288" s="28">
@@ -44124,7 +44152,7 @@
         <v>5</v>
       </c>
       <c r="Y289" s="83"/>
-      <c r="Z289" s="119" t="s">
+      <c r="Z289" s="96" t="s">
         <v>65</v>
       </c>
       <c r="AA289" s="28">
@@ -44264,10 +44292,10 @@
       <c r="X290" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y290" s="122" t="s">
-        <v>64</v>
-      </c>
-      <c r="Z290" s="119" t="s">
+      <c r="Y290" s="98" t="s">
+        <v>64</v>
+      </c>
+      <c r="Z290" s="96" t="s">
         <v>65</v>
       </c>
       <c r="AA290" s="28">
@@ -44408,7 +44436,7 @@
         <v>20</v>
       </c>
       <c r="Y291" s="83"/>
-      <c r="Z291" s="119" t="s">
+      <c r="Z291" s="96" t="s">
         <v>65</v>
       </c>
       <c r="AA291" s="28">
@@ -44549,7 +44577,7 @@
         <v>15</v>
       </c>
       <c r="Y292" s="83"/>
-      <c r="Z292" s="119" t="s">
+      <c r="Z292" s="96" t="s">
         <v>65</v>
       </c>
       <c r="AA292" s="28">
@@ -44690,7 +44718,7 @@
         <v>10</v>
       </c>
       <c r="Y293" s="83"/>
-      <c r="Z293" s="119" t="s">
+      <c r="Z293" s="96" t="s">
         <v>65</v>
       </c>
       <c r="AA293" s="28">
@@ -44831,7 +44859,7 @@
         <v>5</v>
       </c>
       <c r="Y294" s="83"/>
-      <c r="Z294" s="119" t="s">
+      <c r="Z294" s="96" t="s">
         <v>65</v>
       </c>
       <c r="AA294" s="28">
@@ -44971,10 +44999,10 @@
       <c r="X295" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y295" s="122" t="s">
-        <v>64</v>
-      </c>
-      <c r="Z295" s="119" t="s">
+      <c r="Y295" s="98" t="s">
+        <v>64</v>
+      </c>
+      <c r="Z295" s="96" t="s">
         <v>65</v>
       </c>
       <c r="AA295" s="28">
@@ -45115,7 +45143,7 @@
         <v>15</v>
       </c>
       <c r="Y296" s="83"/>
-      <c r="Z296" s="119" t="s">
+      <c r="Z296" s="96" t="s">
         <v>65</v>
       </c>
       <c r="AA296" s="28">
@@ -45256,7 +45284,7 @@
         <v>10</v>
       </c>
       <c r="Y297" s="83"/>
-      <c r="Z297" s="119" t="s">
+      <c r="Z297" s="96" t="s">
         <v>65</v>
       </c>
       <c r="AA297" s="28">
@@ -45397,7 +45425,7 @@
         <v>5</v>
       </c>
       <c r="Y298" s="83"/>
-      <c r="Z298" s="119" t="s">
+      <c r="Z298" s="96" t="s">
         <v>65</v>
       </c>
       <c r="AA298" s="28">
@@ -45537,10 +45565,10 @@
       <c r="X299" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="Y299" s="122" t="s">
-        <v>64</v>
-      </c>
-      <c r="Z299" s="119" t="s">
+      <c r="Y299" s="98" t="s">
+        <v>64</v>
+      </c>
+      <c r="Z299" s="96" t="s">
         <v>65</v>
       </c>
       <c r="AA299" s="28">
@@ -45681,7 +45709,7 @@
         <v>15</v>
       </c>
       <c r="Y300" s="83"/>
-      <c r="Z300" s="119" t="s">
+      <c r="Z300" s="96" t="s">
         <v>65</v>
       </c>
       <c r="AA300" s="28">
@@ -45822,7 +45850,7 @@
         <v>10</v>
       </c>
       <c r="Y301" s="83"/>
-      <c r="Z301" s="119" t="s">
+      <c r="Z301" s="96" t="s">
         <v>65</v>
       </c>
       <c r="AA301" s="28">
@@ -45963,7 +45991,7 @@
         <v>5</v>
       </c>
       <c r="Y302" s="83"/>
-      <c r="Z302" s="119" t="s">
+      <c r="Z302" s="96" t="s">
         <v>65</v>
       </c>
       <c r="AA302" s="28">
@@ -46035,147 +46063,1005 @@
       <c r="BG302" s="44"/>
     </row>
     <row r="303" spans="1:59" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A303" s="55" t="s">
+      <c r="A303" s="65" t="s">
         <v>61</v>
       </c>
-      <c r="B303" s="88" t="s">
+      <c r="B303" s="100" t="s">
         <v>451</v>
       </c>
-      <c r="C303" s="89">
+      <c r="C303" s="101">
         <v>3</v>
       </c>
-      <c r="D303" s="90">
+      <c r="D303" s="102">
         <v>1303</v>
       </c>
-      <c r="E303" s="91">
+      <c r="E303" s="71">
         <v>0.5</v>
       </c>
-      <c r="F303" s="92">
+      <c r="F303" s="103">
         <v>35301</v>
       </c>
-      <c r="G303" s="91">
+      <c r="G303" s="71">
         <v>28087</v>
       </c>
-      <c r="H303" s="91" t="s">
+      <c r="H303" s="71" t="s">
         <v>446</v>
       </c>
-      <c r="I303" s="32">
+      <c r="I303" s="71">
         <v>80</v>
       </c>
-      <c r="J303" s="32">
+      <c r="J303" s="71">
         <v>67</v>
       </c>
-      <c r="K303" s="91">
+      <c r="K303" s="71">
         <v>60.4</v>
       </c>
-      <c r="L303" s="89">
+      <c r="L303" s="101">
         <v>58.5</v>
       </c>
-      <c r="M303" s="93" t="s">
-        <v>64</v>
-      </c>
-      <c r="N303" s="94" t="s">
-        <v>64</v>
-      </c>
-      <c r="O303" s="94" t="s">
-        <v>64</v>
-      </c>
-      <c r="P303" s="94" t="s">
-        <v>64</v>
-      </c>
-      <c r="Q303" s="95" t="s">
-        <v>64</v>
-      </c>
-      <c r="R303" s="92">
+      <c r="M303" s="60" t="s">
+        <v>64</v>
+      </c>
+      <c r="N303" s="61" t="s">
+        <v>64</v>
+      </c>
+      <c r="O303" s="61" t="s">
+        <v>64</v>
+      </c>
+      <c r="P303" s="61" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q303" s="104" t="s">
+        <v>64</v>
+      </c>
+      <c r="R303" s="103">
         <v>33600</v>
       </c>
-      <c r="S303" s="91" t="s">
-        <v>64</v>
-      </c>
-      <c r="T303" s="91"/>
-      <c r="U303" s="91"/>
-      <c r="V303" s="91" t="s">
-        <v>64</v>
-      </c>
-      <c r="W303" s="117" t="s">
-        <v>64</v>
-      </c>
-      <c r="X303" s="93" t="s">
-        <v>64</v>
-      </c>
-      <c r="Y303" s="124" t="s">
-        <v>64</v>
-      </c>
-      <c r="Z303" s="120" t="s">
-        <v>65</v>
-      </c>
-      <c r="AA303" s="96">
+      <c r="S303" s="71" t="s">
+        <v>64</v>
+      </c>
+      <c r="T303" s="71"/>
+      <c r="U303" s="71"/>
+      <c r="V303" s="71" t="s">
+        <v>64</v>
+      </c>
+      <c r="W303" s="105" t="s">
+        <v>64</v>
+      </c>
+      <c r="X303" s="60" t="s">
+        <v>64</v>
+      </c>
+      <c r="Y303" s="99" t="s">
+        <v>64</v>
+      </c>
+      <c r="Z303" s="106" t="s">
+        <v>65</v>
+      </c>
+      <c r="AA303" s="107">
         <v>1</v>
       </c>
-      <c r="AB303" s="92" t="s">
+      <c r="AB303" s="103" t="s">
         <v>66</v>
       </c>
-      <c r="AC303" s="91">
+      <c r="AC303" s="71">
         <v>0.75</v>
       </c>
-      <c r="AD303" s="91">
+      <c r="AD303" s="71">
         <v>19.899999999999999</v>
       </c>
-      <c r="AE303" s="89">
+      <c r="AE303" s="101">
         <v>30</v>
       </c>
-      <c r="AF303" s="96">
+      <c r="AF303" s="107">
         <v>535</v>
       </c>
-      <c r="AH303" s="97">
+      <c r="AH303" s="66">
         <v>3</v>
       </c>
-      <c r="AI303" s="98" t="s">
+      <c r="AI303" s="67" t="s">
         <v>66</v>
       </c>
-      <c r="AJ303" s="99" t="s">
+      <c r="AJ303" s="68" t="s">
         <v>262</v>
       </c>
-      <c r="AK303" s="98" t="s">
+      <c r="AK303" s="67" t="s">
         <v>68</v>
       </c>
-      <c r="AL303" s="98">
+      <c r="AL303" s="67">
         <v>1</v>
       </c>
-      <c r="AM303" s="42" t="s">
-        <v>64</v>
-      </c>
-      <c r="AN303" s="100" t="s">
-        <v>65</v>
-      </c>
-      <c r="AP303" s="97"/>
-      <c r="AQ303" s="98"/>
-      <c r="AR303" s="98" t="s">
+      <c r="AM303" s="68" t="s">
+        <v>64</v>
+      </c>
+      <c r="AN303" s="70" t="s">
+        <v>65</v>
+      </c>
+      <c r="AP303" s="66"/>
+      <c r="AQ303" s="67"/>
+      <c r="AR303" s="67" t="s">
         <v>455</v>
       </c>
-      <c r="AS303" s="98" t="s">
+      <c r="AS303" s="67" t="s">
         <v>264</v>
       </c>
-      <c r="AT303" s="98"/>
-      <c r="AU303" s="98"/>
-      <c r="AV303" s="98"/>
-      <c r="AW303" s="98"/>
-      <c r="AX303" s="98"/>
-      <c r="AY303" s="98" t="s">
+      <c r="AT303" s="67"/>
+      <c r="AU303" s="67"/>
+      <c r="AV303" s="67"/>
+      <c r="AW303" s="67"/>
+      <c r="AX303" s="67"/>
+      <c r="AY303" s="67" t="s">
         <v>265</v>
       </c>
-      <c r="AZ303" s="98"/>
-      <c r="BA303" s="98"/>
-      <c r="BB303" s="88" t="s">
+      <c r="AZ303" s="67"/>
+      <c r="BA303" s="67"/>
+      <c r="BB303" s="100" t="s">
         <v>451</v>
       </c>
-      <c r="BC303" s="98"/>
-      <c r="BD303" s="98"/>
-      <c r="BE303" s="88" t="s">
+      <c r="BC303" s="67"/>
+      <c r="BD303" s="67"/>
+      <c r="BE303" s="100" t="s">
         <v>451</v>
       </c>
-      <c r="BF303" s="98"/>
-      <c r="BG303" s="100"/>
+      <c r="BF303" s="67"/>
+      <c r="BG303" s="70"/>
+    </row>
+    <row r="304" spans="1:59" x14ac:dyDescent="0.25">
+      <c r="A304" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="B304" s="109" t="s">
+        <v>290</v>
+      </c>
+      <c r="C304" s="11">
+        <v>10</v>
+      </c>
+      <c r="D304" s="11">
+        <v>4120</v>
+      </c>
+      <c r="E304" s="11">
+        <v>1</v>
+      </c>
+      <c r="F304" s="11">
+        <v>128803</v>
+      </c>
+      <c r="G304" s="11">
+        <v>94756</v>
+      </c>
+      <c r="H304" s="11" t="s">
+        <v>291</v>
+      </c>
+      <c r="I304" s="11">
+        <v>80</v>
+      </c>
+      <c r="J304" s="11">
+        <v>67</v>
+      </c>
+      <c r="K304" s="11">
+        <v>59.1</v>
+      </c>
+      <c r="L304" s="11">
+        <v>57.1</v>
+      </c>
+      <c r="M304" s="109" t="s">
+        <v>64</v>
+      </c>
+      <c r="N304" s="109" t="s">
+        <v>64</v>
+      </c>
+      <c r="O304" s="109" t="s">
+        <v>64</v>
+      </c>
+      <c r="P304" s="109" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q304" s="109" t="s">
+        <v>64</v>
+      </c>
+      <c r="R304" s="11">
+        <v>114000</v>
+      </c>
+      <c r="S304" s="11">
+        <v>80000</v>
+      </c>
+      <c r="T304" s="11"/>
+      <c r="U304" s="11"/>
+      <c r="V304" s="11">
+        <v>3.74</v>
+      </c>
+      <c r="W304" s="11">
+        <v>2.5</v>
+      </c>
+      <c r="X304" s="109" t="s">
+        <v>64</v>
+      </c>
+      <c r="Y304" s="109" t="s">
+        <v>64</v>
+      </c>
+      <c r="Z304" s="109" t="s">
+        <v>211</v>
+      </c>
+      <c r="AA304" s="109" t="s">
+        <v>292</v>
+      </c>
+      <c r="AB304" s="109" t="s">
+        <v>77</v>
+      </c>
+      <c r="AC304" s="11">
+        <v>3.5</v>
+      </c>
+      <c r="AD304" s="11">
+        <v>26.5</v>
+      </c>
+      <c r="AE304" s="11">
+        <v>35</v>
+      </c>
+      <c r="AF304" s="75">
+        <v>1293</v>
+      </c>
+      <c r="AH304" s="80">
+        <v>10</v>
+      </c>
+      <c r="AI304" s="81" t="s">
+        <v>77</v>
+      </c>
+      <c r="AJ304" s="21" t="s">
+        <v>262</v>
+      </c>
+      <c r="AK304" s="81" t="s">
+        <v>293</v>
+      </c>
+      <c r="AL304" s="81" t="s">
+        <v>292</v>
+      </c>
+      <c r="AM304" s="112" t="s">
+        <v>64</v>
+      </c>
+      <c r="AN304" s="82" t="s">
+        <v>211</v>
+      </c>
+      <c r="AP304" s="80"/>
+      <c r="AQ304" s="81"/>
+      <c r="AR304" s="132" t="s">
+        <v>468</v>
+      </c>
+      <c r="AS304" s="81" t="s">
+        <v>295</v>
+      </c>
+      <c r="AT304" s="81"/>
+      <c r="AU304" s="81"/>
+      <c r="AV304" s="81"/>
+      <c r="AW304" s="81"/>
+      <c r="AX304" s="81"/>
+      <c r="AY304" s="81" t="s">
+        <v>296</v>
+      </c>
+      <c r="AZ304" s="81"/>
+      <c r="BA304" s="81"/>
+      <c r="BB304" s="81" t="s">
+        <v>290</v>
+      </c>
+      <c r="BC304" s="81"/>
+      <c r="BD304" s="81"/>
+      <c r="BE304" s="81" t="s">
+        <v>290</v>
+      </c>
+      <c r="BF304" s="81"/>
+      <c r="BG304" s="82"/>
+    </row>
+    <row r="305" spans="1:59" x14ac:dyDescent="0.25">
+      <c r="A305" s="31" t="s">
+        <v>61</v>
+      </c>
+      <c r="B305" s="108" t="s">
+        <v>297</v>
+      </c>
+      <c r="C305" s="32">
+        <v>10</v>
+      </c>
+      <c r="D305" s="32">
+        <v>4120</v>
+      </c>
+      <c r="E305" s="32">
+        <v>1</v>
+      </c>
+      <c r="F305" s="32">
+        <v>128803</v>
+      </c>
+      <c r="G305" s="32">
+        <v>94756</v>
+      </c>
+      <c r="H305" s="32" t="s">
+        <v>291</v>
+      </c>
+      <c r="I305" s="32">
+        <v>80</v>
+      </c>
+      <c r="J305" s="32">
+        <v>67</v>
+      </c>
+      <c r="K305" s="32">
+        <v>59.1</v>
+      </c>
+      <c r="L305" s="32">
+        <v>57.1</v>
+      </c>
+      <c r="M305" s="108" t="s">
+        <v>64</v>
+      </c>
+      <c r="N305" s="108" t="s">
+        <v>64</v>
+      </c>
+      <c r="O305" s="108" t="s">
+        <v>64</v>
+      </c>
+      <c r="P305" s="108" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q305" s="108" t="s">
+        <v>64</v>
+      </c>
+      <c r="R305" s="32">
+        <v>114000</v>
+      </c>
+      <c r="S305" s="32">
+        <v>80000</v>
+      </c>
+      <c r="T305" s="32"/>
+      <c r="U305" s="32"/>
+      <c r="V305" s="32">
+        <v>3.74</v>
+      </c>
+      <c r="W305" s="32">
+        <v>2.5</v>
+      </c>
+      <c r="X305" s="108" t="s">
+        <v>64</v>
+      </c>
+      <c r="Y305" s="108" t="s">
+        <v>64</v>
+      </c>
+      <c r="Z305" s="108" t="s">
+        <v>211</v>
+      </c>
+      <c r="AA305" s="108" t="s">
+        <v>292</v>
+      </c>
+      <c r="AB305" s="108" t="s">
+        <v>66</v>
+      </c>
+      <c r="AC305" s="32">
+        <v>3.5</v>
+      </c>
+      <c r="AD305" s="32">
+        <v>54</v>
+      </c>
+      <c r="AE305" s="32">
+        <v>70</v>
+      </c>
+      <c r="AF305" s="83">
+        <v>1293</v>
+      </c>
+      <c r="AH305" s="40">
+        <v>10</v>
+      </c>
+      <c r="AI305" s="41" t="s">
+        <v>66</v>
+      </c>
+      <c r="AJ305" s="42" t="s">
+        <v>262</v>
+      </c>
+      <c r="AK305" s="41" t="s">
+        <v>293</v>
+      </c>
+      <c r="AL305" s="41" t="s">
+        <v>292</v>
+      </c>
+      <c r="AM305" s="111" t="s">
+        <v>64</v>
+      </c>
+      <c r="AN305" s="44" t="s">
+        <v>211</v>
+      </c>
+      <c r="AP305" s="40"/>
+      <c r="AQ305" s="41"/>
+      <c r="AR305" s="133" t="s">
+        <v>469</v>
+      </c>
+      <c r="AS305" s="41" t="s">
+        <v>295</v>
+      </c>
+      <c r="AT305" s="41"/>
+      <c r="AU305" s="41"/>
+      <c r="AV305" s="41"/>
+      <c r="AW305" s="41"/>
+      <c r="AX305" s="41"/>
+      <c r="AY305" s="41" t="s">
+        <v>296</v>
+      </c>
+      <c r="AZ305" s="41"/>
+      <c r="BA305" s="41"/>
+      <c r="BB305" s="41" t="s">
+        <v>297</v>
+      </c>
+      <c r="BC305" s="41"/>
+      <c r="BD305" s="41"/>
+      <c r="BE305" s="41" t="s">
+        <v>297</v>
+      </c>
+      <c r="BF305" s="41"/>
+      <c r="BG305" s="44"/>
+    </row>
+    <row r="306" spans="1:59" x14ac:dyDescent="0.25">
+      <c r="A306" s="31" t="s">
+        <v>61</v>
+      </c>
+      <c r="B306" s="108" t="s">
+        <v>299</v>
+      </c>
+      <c r="C306" s="32">
+        <v>8.5</v>
+      </c>
+      <c r="D306" s="32">
+        <v>3800</v>
+      </c>
+      <c r="E306" s="32">
+        <v>1</v>
+      </c>
+      <c r="F306" s="32">
+        <v>111575</v>
+      </c>
+      <c r="G306" s="32">
+        <v>84874</v>
+      </c>
+      <c r="H306" s="32" t="s">
+        <v>300</v>
+      </c>
+      <c r="I306" s="32">
+        <v>80</v>
+      </c>
+      <c r="J306" s="32">
+        <v>67</v>
+      </c>
+      <c r="K306" s="32">
+        <v>59.7</v>
+      </c>
+      <c r="L306" s="32">
+        <v>57.7</v>
+      </c>
+      <c r="M306" s="108" t="s">
+        <v>64</v>
+      </c>
+      <c r="N306" s="108" t="s">
+        <v>64</v>
+      </c>
+      <c r="O306" s="108" t="s">
+        <v>64</v>
+      </c>
+      <c r="P306" s="108" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q306" s="108" t="s">
+        <v>64</v>
+      </c>
+      <c r="R306" s="32">
+        <v>102000</v>
+      </c>
+      <c r="S306" s="32">
+        <v>72000</v>
+      </c>
+      <c r="T306" s="32"/>
+      <c r="U306" s="32"/>
+      <c r="V306" s="32">
+        <v>3.85</v>
+      </c>
+      <c r="W306" s="32">
+        <v>2.5</v>
+      </c>
+      <c r="X306" s="108" t="s">
+        <v>64</v>
+      </c>
+      <c r="Y306" s="108" t="s">
+        <v>64</v>
+      </c>
+      <c r="Z306" s="108" t="s">
+        <v>211</v>
+      </c>
+      <c r="AA306" s="108" t="s">
+        <v>292</v>
+      </c>
+      <c r="AB306" s="108" t="s">
+        <v>77</v>
+      </c>
+      <c r="AC306" s="32">
+        <v>3.5</v>
+      </c>
+      <c r="AD306" s="32">
+        <v>26</v>
+      </c>
+      <c r="AE306" s="32">
+        <v>30</v>
+      </c>
+      <c r="AF306" s="83">
+        <v>1293</v>
+      </c>
+      <c r="AH306" s="40">
+        <v>8.5</v>
+      </c>
+      <c r="AI306" s="41" t="s">
+        <v>77</v>
+      </c>
+      <c r="AJ306" s="42" t="s">
+        <v>262</v>
+      </c>
+      <c r="AK306" s="41" t="s">
+        <v>293</v>
+      </c>
+      <c r="AL306" s="41" t="s">
+        <v>292</v>
+      </c>
+      <c r="AM306" s="111" t="s">
+        <v>64</v>
+      </c>
+      <c r="AN306" s="44" t="s">
+        <v>211</v>
+      </c>
+      <c r="AP306" s="40"/>
+      <c r="AQ306" s="41"/>
+      <c r="AR306" s="133" t="s">
+        <v>470</v>
+      </c>
+      <c r="AS306" s="41" t="s">
+        <v>295</v>
+      </c>
+      <c r="AT306" s="41"/>
+      <c r="AU306" s="41"/>
+      <c r="AV306" s="41"/>
+      <c r="AW306" s="41"/>
+      <c r="AX306" s="41"/>
+      <c r="AY306" s="41" t="s">
+        <v>296</v>
+      </c>
+      <c r="AZ306" s="41"/>
+      <c r="BA306" s="41"/>
+      <c r="BB306" s="41" t="s">
+        <v>299</v>
+      </c>
+      <c r="BC306" s="41"/>
+      <c r="BD306" s="41"/>
+      <c r="BE306" s="41" t="s">
+        <v>299</v>
+      </c>
+      <c r="BF306" s="41"/>
+      <c r="BG306" s="44"/>
+    </row>
+    <row r="307" spans="1:59" x14ac:dyDescent="0.25">
+      <c r="A307" s="31" t="s">
+        <v>61</v>
+      </c>
+      <c r="B307" s="108" t="s">
+        <v>302</v>
+      </c>
+      <c r="C307" s="32">
+        <v>8.5</v>
+      </c>
+      <c r="D307" s="32">
+        <v>3800</v>
+      </c>
+      <c r="E307" s="32">
+        <v>1</v>
+      </c>
+      <c r="F307" s="32">
+        <v>111575</v>
+      </c>
+      <c r="G307" s="32">
+        <v>84874</v>
+      </c>
+      <c r="H307" s="32" t="s">
+        <v>300</v>
+      </c>
+      <c r="I307" s="32">
+        <v>80</v>
+      </c>
+      <c r="J307" s="32">
+        <v>67</v>
+      </c>
+      <c r="K307" s="32">
+        <v>59.7</v>
+      </c>
+      <c r="L307" s="32">
+        <v>57.7</v>
+      </c>
+      <c r="M307" s="108" t="s">
+        <v>64</v>
+      </c>
+      <c r="N307" s="108" t="s">
+        <v>64</v>
+      </c>
+      <c r="O307" s="108" t="s">
+        <v>64</v>
+      </c>
+      <c r="P307" s="108" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q307" s="108" t="s">
+        <v>64</v>
+      </c>
+      <c r="R307" s="32">
+        <v>102000</v>
+      </c>
+      <c r="S307" s="32">
+        <v>72000</v>
+      </c>
+      <c r="T307" s="32"/>
+      <c r="U307" s="32"/>
+      <c r="V307" s="32">
+        <v>3.85</v>
+      </c>
+      <c r="W307" s="32">
+        <v>2.5</v>
+      </c>
+      <c r="X307" s="108" t="s">
+        <v>64</v>
+      </c>
+      <c r="Y307" s="108" t="s">
+        <v>64</v>
+      </c>
+      <c r="Z307" s="108" t="s">
+        <v>211</v>
+      </c>
+      <c r="AA307" s="108" t="s">
+        <v>292</v>
+      </c>
+      <c r="AB307" s="108" t="s">
+        <v>66</v>
+      </c>
+      <c r="AC307" s="32">
+        <v>3.5</v>
+      </c>
+      <c r="AD307" s="32">
+        <v>52.7</v>
+      </c>
+      <c r="AE307" s="32">
+        <v>60</v>
+      </c>
+      <c r="AF307" s="83">
+        <v>1293</v>
+      </c>
+      <c r="AH307" s="40">
+        <v>8.5</v>
+      </c>
+      <c r="AI307" s="41" t="s">
+        <v>66</v>
+      </c>
+      <c r="AJ307" s="42" t="s">
+        <v>262</v>
+      </c>
+      <c r="AK307" s="41" t="s">
+        <v>293</v>
+      </c>
+      <c r="AL307" s="41" t="s">
+        <v>292</v>
+      </c>
+      <c r="AM307" s="111" t="s">
+        <v>64</v>
+      </c>
+      <c r="AN307" s="44" t="s">
+        <v>211</v>
+      </c>
+      <c r="AP307" s="40"/>
+      <c r="AQ307" s="41"/>
+      <c r="AR307" s="133" t="s">
+        <v>471</v>
+      </c>
+      <c r="AS307" s="41" t="s">
+        <v>295</v>
+      </c>
+      <c r="AT307" s="41"/>
+      <c r="AU307" s="41"/>
+      <c r="AV307" s="41"/>
+      <c r="AW307" s="41"/>
+      <c r="AX307" s="41"/>
+      <c r="AY307" s="41" t="s">
+        <v>296</v>
+      </c>
+      <c r="AZ307" s="41"/>
+      <c r="BA307" s="41"/>
+      <c r="BB307" s="41" t="s">
+        <v>302</v>
+      </c>
+      <c r="BC307" s="41"/>
+      <c r="BD307" s="41"/>
+      <c r="BE307" s="41" t="s">
+        <v>302</v>
+      </c>
+      <c r="BF307" s="41"/>
+      <c r="BG307" s="44"/>
+    </row>
+    <row r="308" spans="1:59" x14ac:dyDescent="0.25">
+      <c r="A308" s="31" t="s">
+        <v>61</v>
+      </c>
+      <c r="B308" s="108" t="s">
+        <v>304</v>
+      </c>
+      <c r="C308" s="32">
+        <v>7.5</v>
+      </c>
+      <c r="D308" s="32">
+        <v>3600</v>
+      </c>
+      <c r="E308" s="32">
+        <v>1</v>
+      </c>
+      <c r="F308" s="32">
+        <v>102928</v>
+      </c>
+      <c r="G308" s="32">
+        <v>79341</v>
+      </c>
+      <c r="H308" s="32" t="s">
+        <v>305</v>
+      </c>
+      <c r="I308" s="32">
+        <v>80</v>
+      </c>
+      <c r="J308" s="32">
+        <v>67</v>
+      </c>
+      <c r="K308" s="32">
+        <v>60</v>
+      </c>
+      <c r="L308" s="32">
+        <v>58</v>
+      </c>
+      <c r="M308" s="108" t="s">
+        <v>64</v>
+      </c>
+      <c r="N308" s="108" t="s">
+        <v>64</v>
+      </c>
+      <c r="O308" s="108" t="s">
+        <v>64</v>
+      </c>
+      <c r="P308" s="108" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q308" s="108" t="s">
+        <v>64</v>
+      </c>
+      <c r="R308" s="32">
+        <v>90000</v>
+      </c>
+      <c r="S308" s="32">
+        <v>63000</v>
+      </c>
+      <c r="T308" s="32"/>
+      <c r="U308" s="32"/>
+      <c r="V308" s="32">
+        <v>3.85</v>
+      </c>
+      <c r="W308" s="32">
+        <v>2.5</v>
+      </c>
+      <c r="X308" s="108" t="s">
+        <v>64</v>
+      </c>
+      <c r="Y308" s="108" t="s">
+        <v>64</v>
+      </c>
+      <c r="Z308" s="108" t="s">
+        <v>211</v>
+      </c>
+      <c r="AA308" s="108" t="s">
+        <v>292</v>
+      </c>
+      <c r="AB308" s="108" t="s">
+        <v>77</v>
+      </c>
+      <c r="AC308" s="32">
+        <v>3.5</v>
+      </c>
+      <c r="AD308" s="32">
+        <v>24.8</v>
+      </c>
+      <c r="AE308" s="32">
+        <v>30</v>
+      </c>
+      <c r="AF308" s="83">
+        <v>1293</v>
+      </c>
+      <c r="AH308" s="40">
+        <v>7.5</v>
+      </c>
+      <c r="AI308" s="41" t="s">
+        <v>77</v>
+      </c>
+      <c r="AJ308" s="42" t="s">
+        <v>262</v>
+      </c>
+      <c r="AK308" s="41" t="s">
+        <v>293</v>
+      </c>
+      <c r="AL308" s="41" t="s">
+        <v>292</v>
+      </c>
+      <c r="AM308" s="111" t="s">
+        <v>64</v>
+      </c>
+      <c r="AN308" s="44" t="s">
+        <v>211</v>
+      </c>
+      <c r="AP308" s="40"/>
+      <c r="AQ308" s="41"/>
+      <c r="AR308" s="133" t="s">
+        <v>472</v>
+      </c>
+      <c r="AS308" s="41" t="s">
+        <v>295</v>
+      </c>
+      <c r="AT308" s="41"/>
+      <c r="AU308" s="41"/>
+      <c r="AV308" s="41"/>
+      <c r="AW308" s="41"/>
+      <c r="AX308" s="41"/>
+      <c r="AY308" s="41" t="s">
+        <v>296</v>
+      </c>
+      <c r="AZ308" s="41"/>
+      <c r="BA308" s="41"/>
+      <c r="BB308" s="41" t="s">
+        <v>304</v>
+      </c>
+      <c r="BC308" s="41"/>
+      <c r="BD308" s="41"/>
+      <c r="BE308" s="41" t="s">
+        <v>304</v>
+      </c>
+      <c r="BF308" s="41"/>
+      <c r="BG308" s="44"/>
+    </row>
+    <row r="309" spans="1:59" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A309" s="90" t="s">
+        <v>61</v>
+      </c>
+      <c r="B309" s="110" t="s">
+        <v>307</v>
+      </c>
+      <c r="C309" s="89">
+        <v>7.5</v>
+      </c>
+      <c r="D309" s="89">
+        <v>3600</v>
+      </c>
+      <c r="E309" s="89">
+        <v>1</v>
+      </c>
+      <c r="F309" s="89">
+        <v>102928</v>
+      </c>
+      <c r="G309" s="89">
+        <v>79341</v>
+      </c>
+      <c r="H309" s="89" t="s">
+        <v>305</v>
+      </c>
+      <c r="I309" s="89">
+        <v>80</v>
+      </c>
+      <c r="J309" s="89">
+        <v>67</v>
+      </c>
+      <c r="K309" s="89">
+        <v>60</v>
+      </c>
+      <c r="L309" s="89">
+        <v>58</v>
+      </c>
+      <c r="M309" s="110" t="s">
+        <v>64</v>
+      </c>
+      <c r="N309" s="110" t="s">
+        <v>64</v>
+      </c>
+      <c r="O309" s="110" t="s">
+        <v>64</v>
+      </c>
+      <c r="P309" s="110" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q309" s="110" t="s">
+        <v>64</v>
+      </c>
+      <c r="R309" s="89">
+        <v>90000</v>
+      </c>
+      <c r="S309" s="89">
+        <v>63000</v>
+      </c>
+      <c r="T309" s="89"/>
+      <c r="U309" s="89"/>
+      <c r="V309" s="89">
+        <v>3.85</v>
+      </c>
+      <c r="W309" s="89">
+        <v>2.5</v>
+      </c>
+      <c r="X309" s="110" t="s">
+        <v>64</v>
+      </c>
+      <c r="Y309" s="110" t="s">
+        <v>64</v>
+      </c>
+      <c r="Z309" s="110" t="s">
+        <v>211</v>
+      </c>
+      <c r="AA309" s="110" t="s">
+        <v>292</v>
+      </c>
+      <c r="AB309" s="110" t="s">
+        <v>66</v>
+      </c>
+      <c r="AC309" s="89">
+        <v>3.5</v>
+      </c>
+      <c r="AD309" s="89">
+        <v>49.9</v>
+      </c>
+      <c r="AE309" s="89">
+        <v>60</v>
+      </c>
+      <c r="AF309" s="88">
+        <v>1293</v>
+      </c>
+      <c r="AH309" s="91">
+        <v>7.5</v>
+      </c>
+      <c r="AI309" s="92" t="s">
+        <v>66</v>
+      </c>
+      <c r="AJ309" s="93" t="s">
+        <v>262</v>
+      </c>
+      <c r="AK309" s="92" t="s">
+        <v>293</v>
+      </c>
+      <c r="AL309" s="92" t="s">
+        <v>292</v>
+      </c>
+      <c r="AM309" s="113" t="s">
+        <v>64</v>
+      </c>
+      <c r="AN309" s="94" t="s">
+        <v>211</v>
+      </c>
+      <c r="AP309" s="91"/>
+      <c r="AQ309" s="92"/>
+      <c r="AR309" s="134" t="s">
+        <v>473</v>
+      </c>
+      <c r="AS309" s="92" t="s">
+        <v>295</v>
+      </c>
+      <c r="AT309" s="92"/>
+      <c r="AU309" s="92"/>
+      <c r="AV309" s="92"/>
+      <c r="AW309" s="92"/>
+      <c r="AX309" s="92"/>
+      <c r="AY309" s="92" t="s">
+        <v>296</v>
+      </c>
+      <c r="AZ309" s="92"/>
+      <c r="BA309" s="92"/>
+      <c r="BB309" s="92" t="s">
+        <v>307</v>
+      </c>
+      <c r="BC309" s="92"/>
+      <c r="BD309" s="92"/>
+      <c r="BE309" s="92" t="s">
+        <v>307</v>
+      </c>
+      <c r="BF309" s="92"/>
+      <c r="BG309" s="94"/>
     </row>
   </sheetData>
   <mergeCells count="41">
@@ -46195,7 +47081,6 @@
     <mergeCell ref="AQ2:AQ4"/>
     <mergeCell ref="AY2:AY4"/>
     <mergeCell ref="A1:AF1"/>
-    <mergeCell ref="BC2:BC4"/>
     <mergeCell ref="AL2:AL4"/>
     <mergeCell ref="A3:A4"/>
     <mergeCell ref="AK2:AK4"/>
@@ -46220,6 +47105,7 @@
     <mergeCell ref="AZ2:AZ4"/>
     <mergeCell ref="AW2:AW4"/>
     <mergeCell ref="R3:W3"/>
+    <mergeCell ref="BC2:BC4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/DATA/DATA FILES/LC RTU DATA.xlsx
+++ b/DATA/DATA FILES/LC RTU DATA.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ericc\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ProgramData\HHpro\DATA\DATA FILES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79390D34-63BC-4EB2-93A3-4391C920E296}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81EA80DC-E917-4FAB-8A2E-489E0CA4BB83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6790" uniqueCount="474">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6768" uniqueCount="474">
   <si>
     <t>SCHEDULE RANGE</t>
   </si>
@@ -2467,48 +2467,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2517,6 +2475,48 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2852,7 +2852,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BG309"/>
+  <dimension ref="A1:BG308"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="2" bestFit="1" customWidth="1"/>
@@ -2905,272 +2905,272 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:59" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="130" t="s">
+      <c r="A1" s="117" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="124"/>
-      <c r="C1" s="124"/>
-      <c r="D1" s="124"/>
-      <c r="E1" s="124"/>
-      <c r="F1" s="124"/>
-      <c r="G1" s="124"/>
-      <c r="H1" s="124"/>
-      <c r="I1" s="124"/>
-      <c r="J1" s="124"/>
-      <c r="K1" s="124"/>
-      <c r="L1" s="124"/>
-      <c r="M1" s="124"/>
-      <c r="N1" s="124"/>
-      <c r="O1" s="124"/>
-      <c r="P1" s="124"/>
-      <c r="Q1" s="124"/>
-      <c r="R1" s="124"/>
-      <c r="S1" s="124"/>
-      <c r="T1" s="124"/>
-      <c r="U1" s="124"/>
-      <c r="V1" s="124"/>
-      <c r="W1" s="124"/>
-      <c r="X1" s="124"/>
-      <c r="Y1" s="124"/>
-      <c r="Z1" s="124"/>
-      <c r="AA1" s="124"/>
-      <c r="AB1" s="124"/>
-      <c r="AC1" s="124"/>
-      <c r="AD1" s="124"/>
-      <c r="AE1" s="124"/>
-      <c r="AF1" s="125"/>
-      <c r="AH1" s="121" t="s">
+      <c r="B1" s="118"/>
+      <c r="C1" s="118"/>
+      <c r="D1" s="118"/>
+      <c r="E1" s="118"/>
+      <c r="F1" s="118"/>
+      <c r="G1" s="118"/>
+      <c r="H1" s="118"/>
+      <c r="I1" s="118"/>
+      <c r="J1" s="118"/>
+      <c r="K1" s="118"/>
+      <c r="L1" s="118"/>
+      <c r="M1" s="118"/>
+      <c r="N1" s="118"/>
+      <c r="O1" s="118"/>
+      <c r="P1" s="118"/>
+      <c r="Q1" s="118"/>
+      <c r="R1" s="118"/>
+      <c r="S1" s="118"/>
+      <c r="T1" s="118"/>
+      <c r="U1" s="118"/>
+      <c r="V1" s="118"/>
+      <c r="W1" s="118"/>
+      <c r="X1" s="118"/>
+      <c r="Y1" s="118"/>
+      <c r="Z1" s="118"/>
+      <c r="AA1" s="118"/>
+      <c r="AB1" s="118"/>
+      <c r="AC1" s="118"/>
+      <c r="AD1" s="118"/>
+      <c r="AE1" s="118"/>
+      <c r="AF1" s="119"/>
+      <c r="AH1" s="124" t="s">
         <v>1</v>
       </c>
-      <c r="AI1" s="124"/>
-      <c r="AJ1" s="124"/>
-      <c r="AK1" s="124"/>
-      <c r="AL1" s="124"/>
-      <c r="AM1" s="124"/>
-      <c r="AN1" s="125"/>
+      <c r="AI1" s="118"/>
+      <c r="AJ1" s="118"/>
+      <c r="AK1" s="118"/>
+      <c r="AL1" s="118"/>
+      <c r="AM1" s="118"/>
+      <c r="AN1" s="119"/>
       <c r="AO1" s="3"/>
-      <c r="AP1" s="130" t="s">
-        <v>2</v>
-      </c>
-      <c r="AQ1" s="124"/>
-      <c r="AR1" s="124"/>
-      <c r="AS1" s="124"/>
-      <c r="AT1" s="124"/>
-      <c r="AU1" s="124"/>
-      <c r="AV1" s="124"/>
-      <c r="AW1" s="124"/>
-      <c r="AX1" s="124"/>
-      <c r="AY1" s="124"/>
-      <c r="AZ1" s="124"/>
-      <c r="BA1" s="124"/>
-      <c r="BB1" s="124"/>
-      <c r="BC1" s="124"/>
-      <c r="BD1" s="124"/>
-      <c r="BE1" s="124"/>
-      <c r="BF1" s="124"/>
-      <c r="BG1" s="125"/>
+      <c r="AP1" s="117" t="s">
+        <v>2</v>
+      </c>
+      <c r="AQ1" s="118"/>
+      <c r="AR1" s="118"/>
+      <c r="AS1" s="118"/>
+      <c r="AT1" s="118"/>
+      <c r="AU1" s="118"/>
+      <c r="AV1" s="118"/>
+      <c r="AW1" s="118"/>
+      <c r="AX1" s="118"/>
+      <c r="AY1" s="118"/>
+      <c r="AZ1" s="118"/>
+      <c r="BA1" s="118"/>
+      <c r="BB1" s="118"/>
+      <c r="BC1" s="118"/>
+      <c r="BD1" s="118"/>
+      <c r="BE1" s="118"/>
+      <c r="BF1" s="118"/>
+      <c r="BG1" s="119"/>
     </row>
     <row r="2" spans="1:59" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="127" t="s">
+      <c r="A2" s="126" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="124"/>
-      <c r="C2" s="124"/>
-      <c r="D2" s="124"/>
-      <c r="E2" s="124"/>
-      <c r="F2" s="124"/>
-      <c r="G2" s="124"/>
-      <c r="H2" s="124"/>
-      <c r="I2" s="124"/>
-      <c r="J2" s="124"/>
-      <c r="K2" s="124"/>
-      <c r="L2" s="124"/>
-      <c r="M2" s="124"/>
-      <c r="N2" s="124"/>
-      <c r="O2" s="124"/>
-      <c r="P2" s="124"/>
-      <c r="Q2" s="124"/>
-      <c r="R2" s="124"/>
-      <c r="S2" s="124"/>
-      <c r="T2" s="124"/>
-      <c r="U2" s="124"/>
-      <c r="V2" s="124"/>
-      <c r="W2" s="124"/>
-      <c r="X2" s="124"/>
-      <c r="Y2" s="124"/>
-      <c r="Z2" s="124"/>
-      <c r="AA2" s="124"/>
-      <c r="AB2" s="124"/>
-      <c r="AC2" s="124"/>
-      <c r="AD2" s="124"/>
-      <c r="AE2" s="124"/>
-      <c r="AF2" s="125"/>
-      <c r="AH2" s="121" t="s">
+      <c r="B2" s="118"/>
+      <c r="C2" s="118"/>
+      <c r="D2" s="118"/>
+      <c r="E2" s="118"/>
+      <c r="F2" s="118"/>
+      <c r="G2" s="118"/>
+      <c r="H2" s="118"/>
+      <c r="I2" s="118"/>
+      <c r="J2" s="118"/>
+      <c r="K2" s="118"/>
+      <c r="L2" s="118"/>
+      <c r="M2" s="118"/>
+      <c r="N2" s="118"/>
+      <c r="O2" s="118"/>
+      <c r="P2" s="118"/>
+      <c r="Q2" s="118"/>
+      <c r="R2" s="118"/>
+      <c r="S2" s="118"/>
+      <c r="T2" s="118"/>
+      <c r="U2" s="118"/>
+      <c r="V2" s="118"/>
+      <c r="W2" s="118"/>
+      <c r="X2" s="118"/>
+      <c r="Y2" s="118"/>
+      <c r="Z2" s="118"/>
+      <c r="AA2" s="118"/>
+      <c r="AB2" s="118"/>
+      <c r="AC2" s="118"/>
+      <c r="AD2" s="118"/>
+      <c r="AE2" s="118"/>
+      <c r="AF2" s="119"/>
+      <c r="AH2" s="124" t="s">
         <v>4</v>
       </c>
-      <c r="AI2" s="121" t="s">
+      <c r="AI2" s="124" t="s">
         <v>5</v>
       </c>
-      <c r="AJ2" s="121" t="s">
+      <c r="AJ2" s="124" t="s">
         <v>6</v>
       </c>
-      <c r="AK2" s="121" t="s">
+      <c r="AK2" s="124" t="s">
         <v>7</v>
       </c>
-      <c r="AL2" s="121" t="s">
+      <c r="AL2" s="124" t="s">
         <v>8</v>
       </c>
-      <c r="AM2" s="121" t="s">
+      <c r="AM2" s="124" t="s">
         <v>9</v>
       </c>
-      <c r="AN2" s="121" t="s">
+      <c r="AN2" s="124" t="s">
         <v>10</v>
       </c>
       <c r="AO2" s="3"/>
-      <c r="AP2" s="114" t="s">
+      <c r="AP2" s="120" t="s">
         <v>11</v>
       </c>
-      <c r="AQ2" s="114" t="s">
+      <c r="AQ2" s="120" t="s">
         <v>12</v>
       </c>
-      <c r="AR2" s="114" t="s">
+      <c r="AR2" s="120" t="s">
         <v>13</v>
       </c>
-      <c r="AS2" s="114" t="s">
+      <c r="AS2" s="120" t="s">
         <v>14</v>
       </c>
-      <c r="AT2" s="114" t="s">
+      <c r="AT2" s="120" t="s">
         <v>15</v>
       </c>
-      <c r="AU2" s="114" t="s">
+      <c r="AU2" s="120" t="s">
         <v>16</v>
       </c>
-      <c r="AV2" s="114" t="s">
+      <c r="AV2" s="120" t="s">
         <v>17</v>
       </c>
-      <c r="AW2" s="114" t="s">
+      <c r="AW2" s="120" t="s">
         <v>18</v>
       </c>
-      <c r="AX2" s="114" t="s">
+      <c r="AX2" s="120" t="s">
         <v>19</v>
       </c>
-      <c r="AY2" s="114" t="s">
+      <c r="AY2" s="120" t="s">
         <v>20</v>
       </c>
-      <c r="AZ2" s="114" t="s">
+      <c r="AZ2" s="120" t="s">
         <v>21</v>
       </c>
-      <c r="BA2" s="114" t="s">
+      <c r="BA2" s="120" t="s">
         <v>22</v>
       </c>
-      <c r="BB2" s="114" t="s">
+      <c r="BB2" s="120" t="s">
         <v>23</v>
       </c>
-      <c r="BC2" s="114" t="s">
+      <c r="BC2" s="120" t="s">
         <v>24</v>
       </c>
-      <c r="BD2" s="114" t="s">
+      <c r="BD2" s="120" t="s">
         <v>25</v>
       </c>
-      <c r="BE2" s="114" t="s">
+      <c r="BE2" s="120" t="s">
         <v>26</v>
       </c>
-      <c r="BF2" s="114" t="s">
+      <c r="BF2" s="120" t="s">
         <v>27</v>
       </c>
-      <c r="BG2" s="114" t="s">
+      <c r="BG2" s="120" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:59" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="126" t="s">
+      <c r="A3" s="125" t="s">
         <v>464</v>
       </c>
-      <c r="B3" s="119" t="s">
+      <c r="B3" s="129" t="s">
         <v>463</v>
       </c>
-      <c r="C3" s="119" t="s">
+      <c r="C3" s="129" t="s">
         <v>29</v>
       </c>
-      <c r="D3" s="116" t="s">
+      <c r="D3" s="127" t="s">
         <v>30</v>
       </c>
-      <c r="E3" s="117"/>
-      <c r="F3" s="116" t="s">
+      <c r="E3" s="128"/>
+      <c r="F3" s="127" t="s">
         <v>31</v>
       </c>
-      <c r="G3" s="117"/>
-      <c r="H3" s="117"/>
-      <c r="I3" s="117"/>
-      <c r="J3" s="117"/>
-      <c r="K3" s="117"/>
-      <c r="L3" s="118"/>
-      <c r="M3" s="116" t="s">
+      <c r="G3" s="128"/>
+      <c r="H3" s="128"/>
+      <c r="I3" s="128"/>
+      <c r="J3" s="128"/>
+      <c r="K3" s="128"/>
+      <c r="L3" s="130"/>
+      <c r="M3" s="127" t="s">
         <v>32</v>
       </c>
-      <c r="N3" s="117"/>
-      <c r="O3" s="117"/>
-      <c r="P3" s="117"/>
-      <c r="Q3" s="118"/>
-      <c r="R3" s="123" t="s">
+      <c r="N3" s="128"/>
+      <c r="O3" s="128"/>
+      <c r="P3" s="128"/>
+      <c r="Q3" s="130"/>
+      <c r="R3" s="134" t="s">
         <v>33</v>
       </c>
-      <c r="S3" s="124"/>
-      <c r="T3" s="124"/>
-      <c r="U3" s="124"/>
-      <c r="V3" s="124"/>
-      <c r="W3" s="125"/>
-      <c r="X3" s="128" t="s">
+      <c r="S3" s="118"/>
+      <c r="T3" s="118"/>
+      <c r="U3" s="118"/>
+      <c r="V3" s="118"/>
+      <c r="W3" s="119"/>
+      <c r="X3" s="131" t="s">
         <v>34</v>
       </c>
-      <c r="Y3" s="129"/>
-      <c r="Z3" s="131" t="s">
+      <c r="Y3" s="132"/>
+      <c r="Z3" s="122" t="s">
         <v>35</v>
       </c>
-      <c r="AA3" s="122" t="s">
+      <c r="AA3" s="133" t="s">
         <v>36</v>
       </c>
-      <c r="AB3" s="116" t="s">
+      <c r="AB3" s="127" t="s">
         <v>37</v>
       </c>
-      <c r="AC3" s="117"/>
-      <c r="AD3" s="117"/>
-      <c r="AE3" s="118"/>
-      <c r="AF3" s="122" t="s">
+      <c r="AC3" s="128"/>
+      <c r="AD3" s="128"/>
+      <c r="AE3" s="130"/>
+      <c r="AF3" s="133" t="s">
         <v>38</v>
       </c>
       <c r="AG3" s="5"/>
-      <c r="AH3" s="115"/>
-      <c r="AI3" s="115"/>
-      <c r="AJ3" s="115"/>
-      <c r="AK3" s="115"/>
-      <c r="AL3" s="115"/>
-      <c r="AM3" s="115"/>
-      <c r="AN3" s="115"/>
+      <c r="AH3" s="121"/>
+      <c r="AI3" s="121"/>
+      <c r="AJ3" s="121"/>
+      <c r="AK3" s="121"/>
+      <c r="AL3" s="121"/>
+      <c r="AM3" s="121"/>
+      <c r="AN3" s="121"/>
       <c r="AO3" s="3"/>
-      <c r="AP3" s="115"/>
-      <c r="AQ3" s="115"/>
-      <c r="AR3" s="115"/>
-      <c r="AS3" s="115"/>
-      <c r="AT3" s="115"/>
-      <c r="AU3" s="115"/>
-      <c r="AV3" s="115"/>
-      <c r="AW3" s="115"/>
-      <c r="AX3" s="115"/>
-      <c r="AY3" s="115"/>
-      <c r="AZ3" s="115"/>
-      <c r="BA3" s="115"/>
-      <c r="BB3" s="115"/>
-      <c r="BC3" s="115"/>
-      <c r="BD3" s="115"/>
-      <c r="BE3" s="115"/>
-      <c r="BF3" s="115"/>
-      <c r="BG3" s="115"/>
+      <c r="AP3" s="121"/>
+      <c r="AQ3" s="121"/>
+      <c r="AR3" s="121"/>
+      <c r="AS3" s="121"/>
+      <c r="AT3" s="121"/>
+      <c r="AU3" s="121"/>
+      <c r="AV3" s="121"/>
+      <c r="AW3" s="121"/>
+      <c r="AX3" s="121"/>
+      <c r="AY3" s="121"/>
+      <c r="AZ3" s="121"/>
+      <c r="BA3" s="121"/>
+      <c r="BB3" s="121"/>
+      <c r="BC3" s="121"/>
+      <c r="BD3" s="121"/>
+      <c r="BE3" s="121"/>
+      <c r="BF3" s="121"/>
+      <c r="BG3" s="121"/>
     </row>
     <row r="4" spans="1:59" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="120"/>
-      <c r="B4" s="120"/>
-      <c r="C4" s="120"/>
+      <c r="A4" s="123"/>
+      <c r="B4" s="123"/>
+      <c r="C4" s="123"/>
       <c r="D4" s="6" t="s">
         <v>39</v>
       </c>
@@ -3237,8 +3237,8 @@
       <c r="Y4" s="4" t="s">
         <v>466</v>
       </c>
-      <c r="Z4" s="120"/>
-      <c r="AA4" s="120"/>
+      <c r="Z4" s="123"/>
+      <c r="AA4" s="123"/>
       <c r="AB4" s="4" t="s">
         <v>57</v>
       </c>
@@ -3251,33 +3251,33 @@
       <c r="AE4" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="AF4" s="120"/>
-      <c r="AH4" s="120"/>
-      <c r="AI4" s="120"/>
-      <c r="AJ4" s="120"/>
-      <c r="AK4" s="120"/>
-      <c r="AL4" s="120"/>
-      <c r="AM4" s="120"/>
-      <c r="AN4" s="120"/>
+      <c r="AF4" s="123"/>
+      <c r="AH4" s="123"/>
+      <c r="AI4" s="123"/>
+      <c r="AJ4" s="123"/>
+      <c r="AK4" s="123"/>
+      <c r="AL4" s="123"/>
+      <c r="AM4" s="123"/>
+      <c r="AN4" s="123"/>
       <c r="AO4" s="3"/>
-      <c r="AP4" s="115"/>
-      <c r="AQ4" s="115"/>
-      <c r="AR4" s="115"/>
-      <c r="AS4" s="115"/>
-      <c r="AT4" s="115"/>
-      <c r="AU4" s="115"/>
-      <c r="AV4" s="115"/>
-      <c r="AW4" s="115"/>
-      <c r="AX4" s="115"/>
-      <c r="AY4" s="115"/>
-      <c r="AZ4" s="115"/>
-      <c r="BA4" s="115"/>
-      <c r="BB4" s="115"/>
-      <c r="BC4" s="115"/>
-      <c r="BD4" s="115"/>
-      <c r="BE4" s="115"/>
-      <c r="BF4" s="115"/>
-      <c r="BG4" s="115"/>
+      <c r="AP4" s="121"/>
+      <c r="AQ4" s="121"/>
+      <c r="AR4" s="121"/>
+      <c r="AS4" s="121"/>
+      <c r="AT4" s="121"/>
+      <c r="AU4" s="121"/>
+      <c r="AV4" s="121"/>
+      <c r="AW4" s="121"/>
+      <c r="AX4" s="121"/>
+      <c r="AY4" s="121"/>
+      <c r="AZ4" s="121"/>
+      <c r="BA4" s="121"/>
+      <c r="BB4" s="121"/>
+      <c r="BC4" s="121"/>
+      <c r="BD4" s="121"/>
+      <c r="BE4" s="121"/>
+      <c r="BF4" s="121"/>
+      <c r="BG4" s="121"/>
     </row>
     <row r="5" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
@@ -3320,7 +3320,7 @@
         <v>70</v>
       </c>
       <c r="N5" s="11">
-        <v>56.7</v>
+        <v>56</v>
       </c>
       <c r="O5" s="11">
         <v>2</v>
@@ -3466,7 +3466,7 @@
         <v>45</v>
       </c>
       <c r="N6" s="32">
-        <v>36.450000000000003</v>
+        <v>36</v>
       </c>
       <c r="O6" s="32">
         <v>2</v>
@@ -3611,7 +3611,7 @@
         <v>90</v>
       </c>
       <c r="N7" s="32">
-        <v>72.900000000000006</v>
+        <v>72</v>
       </c>
       <c r="O7" s="32">
         <v>2</v>
@@ -3756,7 +3756,7 @@
         <v>45</v>
       </c>
       <c r="N8" s="32">
-        <v>36.450000000000003</v>
+        <v>36</v>
       </c>
       <c r="O8" s="32">
         <v>2</v>
@@ -3901,7 +3901,7 @@
         <v>70</v>
       </c>
       <c r="N9" s="32">
-        <v>56.7</v>
+        <v>56</v>
       </c>
       <c r="O9" s="32">
         <v>2</v>
@@ -4046,7 +4046,7 @@
         <v>90</v>
       </c>
       <c r="N10" s="32">
-        <v>72.900000000000006</v>
+        <v>72</v>
       </c>
       <c r="O10" s="32">
         <v>2</v>
@@ -4451,7 +4451,7 @@
         <v>3</v>
       </c>
       <c r="D13" s="31">
-        <v>1267</v>
+        <v>1747</v>
       </c>
       <c r="E13" s="32">
         <v>0.5</v>
@@ -5061,7 +5061,7 @@
         <v>70</v>
       </c>
       <c r="N17" s="32">
-        <v>56.7</v>
+        <v>56</v>
       </c>
       <c r="O17" s="32">
         <v>2</v>
@@ -5206,7 +5206,7 @@
         <v>90</v>
       </c>
       <c r="N18" s="32">
-        <v>72.900000000000006</v>
+        <v>72</v>
       </c>
       <c r="O18" s="32">
         <v>2</v>
@@ -5351,7 +5351,7 @@
         <v>115</v>
       </c>
       <c r="N19" s="32">
-        <v>93.15</v>
+        <v>92</v>
       </c>
       <c r="O19" s="32">
         <v>2</v>
@@ -5496,7 +5496,7 @@
         <v>70</v>
       </c>
       <c r="N20" s="32">
-        <v>56.7</v>
+        <v>56</v>
       </c>
       <c r="O20" s="32">
         <v>2</v>
@@ -5641,7 +5641,7 @@
         <v>90</v>
       </c>
       <c r="N21" s="32">
-        <v>72.900000000000006</v>
+        <v>72</v>
       </c>
       <c r="O21" s="32">
         <v>2</v>
@@ -5786,7 +5786,7 @@
         <v>115</v>
       </c>
       <c r="N22" s="32">
-        <v>93.15</v>
+        <v>92</v>
       </c>
       <c r="O22" s="32">
         <v>2</v>
@@ -6801,7 +6801,7 @@
         <v>90</v>
       </c>
       <c r="N29" s="32">
-        <v>72.900000000000006</v>
+        <v>72</v>
       </c>
       <c r="O29" s="32">
         <v>2</v>
@@ -6946,7 +6946,7 @@
         <v>115</v>
       </c>
       <c r="N30" s="32">
-        <v>93.15</v>
+        <v>92</v>
       </c>
       <c r="O30" s="32">
         <v>2</v>
@@ -7091,7 +7091,7 @@
         <v>140</v>
       </c>
       <c r="N31" s="32">
-        <v>113.4</v>
+        <v>112</v>
       </c>
       <c r="O31" s="32">
         <v>2</v>
@@ -7236,7 +7236,7 @@
         <v>90</v>
       </c>
       <c r="N32" s="32">
-        <v>72.900000000000006</v>
+        <v>72</v>
       </c>
       <c r="O32" s="32">
         <v>2</v>
@@ -7381,7 +7381,7 @@
         <v>115</v>
       </c>
       <c r="N33" s="32">
-        <v>93.15</v>
+        <v>92</v>
       </c>
       <c r="O33" s="32">
         <v>2</v>
@@ -7526,7 +7526,7 @@
         <v>140</v>
       </c>
       <c r="N34" s="32">
-        <v>113.4</v>
+        <v>112</v>
       </c>
       <c r="O34" s="32">
         <v>2</v>
@@ -8541,7 +8541,7 @@
         <v>90</v>
       </c>
       <c r="N41" s="32">
-        <v>72.900000000000006</v>
+        <v>72</v>
       </c>
       <c r="O41" s="32">
         <v>2</v>
@@ -8686,7 +8686,7 @@
         <v>115</v>
       </c>
       <c r="N42" s="32">
-        <v>93.15</v>
+        <v>92</v>
       </c>
       <c r="O42" s="32">
         <v>2</v>
@@ -8831,7 +8831,7 @@
         <v>140</v>
       </c>
       <c r="N43" s="32">
-        <v>113.4</v>
+        <v>112</v>
       </c>
       <c r="O43" s="32">
         <v>2</v>
@@ -8976,7 +8976,7 @@
         <v>90</v>
       </c>
       <c r="N44" s="32">
-        <v>72.900000000000006</v>
+        <v>72</v>
       </c>
       <c r="O44" s="32">
         <v>2</v>
@@ -9121,7 +9121,7 @@
         <v>115</v>
       </c>
       <c r="N45" s="32">
-        <v>93.15</v>
+        <v>92</v>
       </c>
       <c r="O45" s="32">
         <v>2</v>
@@ -9266,7 +9266,7 @@
         <v>140</v>
       </c>
       <c r="N46" s="32">
-        <v>113.4</v>
+        <v>112</v>
       </c>
       <c r="O46" s="32">
         <v>2</v>
@@ -38570,7 +38570,7 @@
         <v>61</v>
       </c>
       <c r="B250" s="29" t="s">
-        <v>376</v>
+        <v>385</v>
       </c>
       <c r="C250" s="83">
         <v>10</v>
@@ -38631,12 +38631,10 @@
       <c r="W250" s="30">
         <v>2.25</v>
       </c>
-      <c r="X250" s="35" t="s">
-        <v>64</v>
-      </c>
-      <c r="Y250" s="98" t="s">
-        <v>64</v>
-      </c>
+      <c r="X250" s="31">
+        <v>15</v>
+      </c>
+      <c r="Y250" s="83"/>
       <c r="Z250" s="96" t="s">
         <v>65</v>
       </c>
@@ -38644,16 +38642,16 @@
         <v>2</v>
       </c>
       <c r="AB250" s="31" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="AC250" s="32">
         <v>3.5</v>
       </c>
       <c r="AD250" s="32">
-        <v>27.3</v>
+        <v>94.3</v>
       </c>
       <c r="AE250" s="83">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="AF250" s="28">
         <v>1169</v>
@@ -38662,7 +38660,7 @@
         <v>10</v>
       </c>
       <c r="AI250" s="41" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="AJ250" s="42" t="s">
         <v>262</v>
@@ -38682,7 +38680,7 @@
       <c r="AP250" s="40"/>
       <c r="AQ250" s="41"/>
       <c r="AR250" s="41" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="AS250" s="41" t="s">
         <v>269</v>
@@ -38698,12 +38696,12 @@
       <c r="AZ250" s="41"/>
       <c r="BA250" s="41"/>
       <c r="BB250" s="29" t="s">
-        <v>376</v>
+        <v>385</v>
       </c>
       <c r="BC250" s="41"/>
       <c r="BD250" s="41"/>
       <c r="BE250" s="29" t="s">
-        <v>376</v>
+        <v>385</v>
       </c>
       <c r="BF250" s="41"/>
       <c r="BG250" s="44"/>
@@ -38774,10 +38772,12 @@
       <c r="W251" s="30">
         <v>2.25</v>
       </c>
-      <c r="X251" s="31">
-        <v>15</v>
-      </c>
-      <c r="Y251" s="83"/>
+      <c r="X251" s="35" t="s">
+        <v>64</v>
+      </c>
+      <c r="Y251" s="98" t="s">
+        <v>64</v>
+      </c>
       <c r="Z251" s="96" t="s">
         <v>65</v>
       </c>
@@ -38791,10 +38791,10 @@
         <v>3.5</v>
       </c>
       <c r="AD251" s="32">
-        <v>94.3</v>
+        <v>55.2</v>
       </c>
       <c r="AE251" s="83">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="AF251" s="28">
         <v>1169</v>
@@ -38823,7 +38823,7 @@
       <c r="AP251" s="40"/>
       <c r="AQ251" s="41"/>
       <c r="AR251" s="41" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AS251" s="41" t="s">
         <v>269</v>
@@ -38854,25 +38854,25 @@
         <v>61</v>
       </c>
       <c r="B252" s="29" t="s">
-        <v>385</v>
+        <v>392</v>
       </c>
       <c r="C252" s="83">
-        <v>10</v>
+        <v>8.5</v>
       </c>
       <c r="D252" s="84">
-        <v>4153</v>
+        <v>3438</v>
       </c>
       <c r="E252" s="32">
         <v>0.5</v>
       </c>
       <c r="F252" s="31">
-        <v>117158</v>
+        <v>99572</v>
       </c>
       <c r="G252" s="32">
-        <v>94737</v>
+        <v>80653</v>
       </c>
       <c r="H252" s="32" t="s">
-        <v>162</v>
+        <v>149</v>
       </c>
       <c r="I252" s="32">
         <v>80</v>
@@ -38881,10 +38881,10 @@
         <v>67</v>
       </c>
       <c r="K252" s="32">
-        <v>59.3</v>
+        <v>58.7</v>
       </c>
       <c r="L252" s="83">
-        <v>58.1</v>
+        <v>57.9</v>
       </c>
       <c r="M252" s="35" t="s">
         <v>64</v>
@@ -38902,10 +38902,10 @@
         <v>64</v>
       </c>
       <c r="R252" s="31">
-        <v>116000</v>
+        <v>97000</v>
       </c>
       <c r="S252" s="32">
-        <v>66000</v>
+        <v>56000</v>
       </c>
       <c r="T252" s="32"/>
       <c r="U252" s="32"/>
@@ -38915,12 +38915,10 @@
       <c r="W252" s="30">
         <v>2.25</v>
       </c>
-      <c r="X252" s="35" t="s">
-        <v>64</v>
-      </c>
-      <c r="Y252" s="98" t="s">
-        <v>64</v>
-      </c>
+      <c r="X252" s="31">
+        <v>45</v>
+      </c>
+      <c r="Y252" s="83"/>
       <c r="Z252" s="96" t="s">
         <v>65</v>
       </c>
@@ -38928,25 +38926,25 @@
         <v>2</v>
       </c>
       <c r="AB252" s="31" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="AC252" s="32">
-        <v>3.5</v>
+        <v>2.4</v>
       </c>
       <c r="AD252" s="32">
-        <v>55.2</v>
+        <v>89.2</v>
       </c>
       <c r="AE252" s="83">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="AF252" s="28">
-        <v>1169</v>
+        <v>1157</v>
       </c>
       <c r="AH252" s="40">
-        <v>10</v>
+        <v>8.5</v>
       </c>
       <c r="AI252" s="41" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="AJ252" s="42" t="s">
         <v>262</v>
@@ -38966,7 +38964,7 @@
       <c r="AP252" s="40"/>
       <c r="AQ252" s="41"/>
       <c r="AR252" s="41" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="AS252" s="41" t="s">
         <v>269</v>
@@ -38982,12 +38980,12 @@
       <c r="AZ252" s="41"/>
       <c r="BA252" s="41"/>
       <c r="BB252" s="29" t="s">
-        <v>385</v>
+        <v>392</v>
       </c>
       <c r="BC252" s="41"/>
       <c r="BD252" s="41"/>
       <c r="BE252" s="29" t="s">
-        <v>385</v>
+        <v>392</v>
       </c>
       <c r="BF252" s="41"/>
       <c r="BG252" s="44"/>
@@ -39059,7 +39057,7 @@
         <v>2.25</v>
       </c>
       <c r="X253" s="31">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="Y253" s="83"/>
       <c r="Z253" s="96" t="s">
@@ -39075,10 +39073,10 @@
         <v>2.4</v>
       </c>
       <c r="AD253" s="32">
-        <v>89.2</v>
+        <v>66.599999999999994</v>
       </c>
       <c r="AE253" s="83">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="AF253" s="28">
         <v>1157</v>
@@ -39107,7 +39105,7 @@
       <c r="AP253" s="40"/>
       <c r="AQ253" s="41"/>
       <c r="AR253" s="41" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AS253" s="41" t="s">
         <v>269</v>
@@ -39200,7 +39198,7 @@
         <v>2.25</v>
       </c>
       <c r="X254" s="31">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="Y254" s="83"/>
       <c r="Z254" s="96" t="s">
@@ -39216,10 +39214,10 @@
         <v>2.4</v>
       </c>
       <c r="AD254" s="32">
-        <v>66.599999999999994</v>
+        <v>44.1</v>
       </c>
       <c r="AE254" s="83">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="AF254" s="28">
         <v>1157</v>
@@ -39248,7 +39246,7 @@
       <c r="AP254" s="40"/>
       <c r="AQ254" s="41"/>
       <c r="AR254" s="41" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AS254" s="41" t="s">
         <v>269</v>
@@ -39340,10 +39338,12 @@
       <c r="W255" s="30">
         <v>2.25</v>
       </c>
-      <c r="X255" s="31">
-        <v>15</v>
-      </c>
-      <c r="Y255" s="83"/>
+      <c r="X255" s="35" t="s">
+        <v>64</v>
+      </c>
+      <c r="Y255" s="98" t="s">
+        <v>64</v>
+      </c>
       <c r="Z255" s="96" t="s">
         <v>65</v>
       </c>
@@ -39357,10 +39357,10 @@
         <v>2.4</v>
       </c>
       <c r="AD255" s="32">
-        <v>44.1</v>
+        <v>21.5</v>
       </c>
       <c r="AE255" s="83">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="AF255" s="28">
         <v>1157</v>
@@ -39389,7 +39389,7 @@
       <c r="AP255" s="40"/>
       <c r="AQ255" s="41"/>
       <c r="AR255" s="41" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AS255" s="41" t="s">
         <v>269</v>
@@ -39420,7 +39420,7 @@
         <v>61</v>
       </c>
       <c r="B256" s="29" t="s">
-        <v>392</v>
+        <v>383</v>
       </c>
       <c r="C256" s="83">
         <v>8.5</v>
@@ -39481,12 +39481,10 @@
       <c r="W256" s="30">
         <v>2.25</v>
       </c>
-      <c r="X256" s="35" t="s">
-        <v>64</v>
-      </c>
-      <c r="Y256" s="98" t="s">
-        <v>64</v>
-      </c>
+      <c r="X256" s="31">
+        <v>45</v>
+      </c>
+      <c r="Y256" s="83"/>
       <c r="Z256" s="96" t="s">
         <v>65</v>
       </c>
@@ -39494,16 +39492,16 @@
         <v>2</v>
       </c>
       <c r="AB256" s="31" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="AC256" s="32">
         <v>2.4</v>
       </c>
       <c r="AD256" s="32">
-        <v>21.5</v>
+        <v>161</v>
       </c>
       <c r="AE256" s="83">
-        <v>25</v>
+        <v>175</v>
       </c>
       <c r="AF256" s="28">
         <v>1157</v>
@@ -39512,7 +39510,7 @@
         <v>8.5</v>
       </c>
       <c r="AI256" s="41" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="AJ256" s="42" t="s">
         <v>262</v>
@@ -39532,7 +39530,7 @@
       <c r="AP256" s="40"/>
       <c r="AQ256" s="41"/>
       <c r="AR256" s="41" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AS256" s="41" t="s">
         <v>269</v>
@@ -39548,12 +39546,12 @@
       <c r="AZ256" s="41"/>
       <c r="BA256" s="41"/>
       <c r="BB256" s="29" t="s">
-        <v>392</v>
+        <v>383</v>
       </c>
       <c r="BC256" s="41"/>
       <c r="BD256" s="41"/>
       <c r="BE256" s="29" t="s">
-        <v>392</v>
+        <v>383</v>
       </c>
       <c r="BF256" s="41"/>
       <c r="BG256" s="44"/>
@@ -39625,7 +39623,7 @@
         <v>2.25</v>
       </c>
       <c r="X257" s="31">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="Y257" s="83"/>
       <c r="Z257" s="96" t="s">
@@ -39641,10 +39639,10 @@
         <v>2.4</v>
       </c>
       <c r="AD257" s="32">
-        <v>161</v>
+        <v>122</v>
       </c>
       <c r="AE257" s="83">
-        <v>175</v>
+        <v>125</v>
       </c>
       <c r="AF257" s="28">
         <v>1157</v>
@@ -39673,7 +39671,7 @@
       <c r="AP257" s="40"/>
       <c r="AQ257" s="41"/>
       <c r="AR257" s="41" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AS257" s="41" t="s">
         <v>269</v>
@@ -39766,7 +39764,7 @@
         <v>2.25</v>
       </c>
       <c r="X258" s="31">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="Y258" s="83"/>
       <c r="Z258" s="96" t="s">
@@ -39782,10 +39780,10 @@
         <v>2.4</v>
       </c>
       <c r="AD258" s="32">
-        <v>122</v>
+        <v>82.8</v>
       </c>
       <c r="AE258" s="83">
-        <v>125</v>
+        <v>90</v>
       </c>
       <c r="AF258" s="28">
         <v>1157</v>
@@ -39814,7 +39812,7 @@
       <c r="AP258" s="40"/>
       <c r="AQ258" s="41"/>
       <c r="AR258" s="41" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AS258" s="41" t="s">
         <v>269</v>
@@ -39845,25 +39843,25 @@
         <v>61</v>
       </c>
       <c r="B259" s="29" t="s">
-        <v>383</v>
+        <v>400</v>
       </c>
       <c r="C259" s="83">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="D259" s="84">
-        <v>3438</v>
+        <v>3133</v>
       </c>
       <c r="E259" s="32">
         <v>0.5</v>
       </c>
       <c r="F259" s="31">
-        <v>99572</v>
+        <v>86489</v>
       </c>
       <c r="G259" s="32">
-        <v>80653</v>
+        <v>69011</v>
       </c>
       <c r="H259" s="32" t="s">
-        <v>149</v>
+        <v>401</v>
       </c>
       <c r="I259" s="32">
         <v>80</v>
@@ -39872,10 +39870,10 @@
         <v>67</v>
       </c>
       <c r="K259" s="32">
-        <v>58.7</v>
+        <v>60</v>
       </c>
       <c r="L259" s="83">
-        <v>57.9</v>
+        <v>58.3</v>
       </c>
       <c r="M259" s="35" t="s">
         <v>64</v>
@@ -39893,10 +39891,10 @@
         <v>64</v>
       </c>
       <c r="R259" s="31">
-        <v>97000</v>
+        <v>86000</v>
       </c>
       <c r="S259" s="32">
-        <v>56000</v>
+        <v>50000</v>
       </c>
       <c r="T259" s="32"/>
       <c r="U259" s="32"/>
@@ -39907,7 +39905,7 @@
         <v>2.25</v>
       </c>
       <c r="X259" s="31">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="Y259" s="83"/>
       <c r="Z259" s="96" t="s">
@@ -39917,13 +39915,13 @@
         <v>2</v>
       </c>
       <c r="AB259" s="31" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="AC259" s="32">
         <v>2.4</v>
       </c>
       <c r="AD259" s="32">
-        <v>82.8</v>
+        <v>87.7</v>
       </c>
       <c r="AE259" s="83">
         <v>90</v>
@@ -39932,10 +39930,10 @@
         <v>1157</v>
       </c>
       <c r="AH259" s="40">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="AI259" s="41" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="AJ259" s="42" t="s">
         <v>262</v>
@@ -39955,7 +39953,7 @@
       <c r="AP259" s="40"/>
       <c r="AQ259" s="41"/>
       <c r="AR259" s="41" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="AS259" s="41" t="s">
         <v>269</v>
@@ -39971,12 +39969,12 @@
       <c r="AZ259" s="41"/>
       <c r="BA259" s="41"/>
       <c r="BB259" s="29" t="s">
-        <v>383</v>
+        <v>400</v>
       </c>
       <c r="BC259" s="41"/>
       <c r="BD259" s="41"/>
       <c r="BE259" s="29" t="s">
-        <v>383</v>
+        <v>400</v>
       </c>
       <c r="BF259" s="41"/>
       <c r="BG259" s="44"/>
@@ -40048,7 +40046,7 @@
         <v>2.25</v>
       </c>
       <c r="X260" s="31">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="Y260" s="83"/>
       <c r="Z260" s="96" t="s">
@@ -40064,10 +40062,10 @@
         <v>2.4</v>
       </c>
       <c r="AD260" s="32">
-        <v>87.7</v>
+        <v>65.2</v>
       </c>
       <c r="AE260" s="83">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="AF260" s="28">
         <v>1157</v>
@@ -40096,7 +40094,7 @@
       <c r="AP260" s="40"/>
       <c r="AQ260" s="41"/>
       <c r="AR260" s="41" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AS260" s="41" t="s">
         <v>269</v>
@@ -40189,7 +40187,7 @@
         <v>2.25</v>
       </c>
       <c r="X261" s="31">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="Y261" s="83"/>
       <c r="Z261" s="96" t="s">
@@ -40205,10 +40203,10 @@
         <v>2.4</v>
       </c>
       <c r="AD261" s="32">
-        <v>65.2</v>
+        <v>42.6</v>
       </c>
       <c r="AE261" s="83">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="AF261" s="28">
         <v>1157</v>
@@ -40237,7 +40235,7 @@
       <c r="AP261" s="40"/>
       <c r="AQ261" s="41"/>
       <c r="AR261" s="41" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AS261" s="41" t="s">
         <v>269</v>
@@ -40329,10 +40327,12 @@
       <c r="W262" s="30">
         <v>2.25</v>
       </c>
-      <c r="X262" s="31">
-        <v>15</v>
-      </c>
-      <c r="Y262" s="83"/>
+      <c r="X262" s="35" t="s">
+        <v>64</v>
+      </c>
+      <c r="Y262" s="98" t="s">
+        <v>64</v>
+      </c>
       <c r="Z262" s="96" t="s">
         <v>65</v>
       </c>
@@ -40346,10 +40346,10 @@
         <v>2.4</v>
       </c>
       <c r="AD262" s="32">
-        <v>42.6</v>
+        <v>20.100000000000001</v>
       </c>
       <c r="AE262" s="83">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="AF262" s="28">
         <v>1157</v>
@@ -40378,7 +40378,7 @@
       <c r="AP262" s="40"/>
       <c r="AQ262" s="41"/>
       <c r="AR262" s="41" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AS262" s="41" t="s">
         <v>269</v>
@@ -40409,7 +40409,7 @@
         <v>61</v>
       </c>
       <c r="B263" s="29" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="C263" s="83">
         <v>7.5</v>
@@ -40470,12 +40470,10 @@
       <c r="W263" s="30">
         <v>2.25</v>
       </c>
-      <c r="X263" s="35" t="s">
-        <v>64</v>
-      </c>
-      <c r="Y263" s="98" t="s">
-        <v>64</v>
-      </c>
+      <c r="X263" s="31">
+        <v>45</v>
+      </c>
+      <c r="Y263" s="83"/>
       <c r="Z263" s="96" t="s">
         <v>65</v>
       </c>
@@ -40483,16 +40481,16 @@
         <v>2</v>
       </c>
       <c r="AB263" s="31" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="AC263" s="32">
         <v>2.4</v>
       </c>
       <c r="AD263" s="32">
-        <v>20.100000000000001</v>
+        <v>157</v>
       </c>
       <c r="AE263" s="83">
-        <v>25</v>
+        <v>175</v>
       </c>
       <c r="AF263" s="28">
         <v>1157</v>
@@ -40501,7 +40499,7 @@
         <v>7.5</v>
       </c>
       <c r="AI263" s="41" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="AJ263" s="42" t="s">
         <v>262</v>
@@ -40521,7 +40519,7 @@
       <c r="AP263" s="40"/>
       <c r="AQ263" s="41"/>
       <c r="AR263" s="41" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="AS263" s="41" t="s">
         <v>269</v>
@@ -40537,12 +40535,12 @@
       <c r="AZ263" s="41"/>
       <c r="BA263" s="41"/>
       <c r="BB263" s="29" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="BC263" s="41"/>
       <c r="BD263" s="41"/>
       <c r="BE263" s="29" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="BF263" s="41"/>
       <c r="BG263" s="44"/>
@@ -40614,7 +40612,7 @@
         <v>2.25</v>
       </c>
       <c r="X264" s="31">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="Y264" s="83"/>
       <c r="Z264" s="96" t="s">
@@ -40630,10 +40628,10 @@
         <v>2.4</v>
       </c>
       <c r="AD264" s="32">
-        <v>157</v>
+        <v>118</v>
       </c>
       <c r="AE264" s="83">
-        <v>175</v>
+        <v>125</v>
       </c>
       <c r="AF264" s="28">
         <v>1157</v>
@@ -40662,7 +40660,7 @@
       <c r="AP264" s="40"/>
       <c r="AQ264" s="41"/>
       <c r="AR264" s="41" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AS264" s="41" t="s">
         <v>269</v>
@@ -40755,7 +40753,7 @@
         <v>2.25</v>
       </c>
       <c r="X265" s="31">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="Y265" s="83"/>
       <c r="Z265" s="96" t="s">
@@ -40771,10 +40769,10 @@
         <v>2.4</v>
       </c>
       <c r="AD265" s="32">
-        <v>118</v>
+        <v>78.5</v>
       </c>
       <c r="AE265" s="83">
-        <v>125</v>
+        <v>80</v>
       </c>
       <c r="AF265" s="28">
         <v>1157</v>
@@ -40803,7 +40801,7 @@
       <c r="AP265" s="40"/>
       <c r="AQ265" s="41"/>
       <c r="AR265" s="41" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AS265" s="41" t="s">
         <v>269</v>
@@ -40895,10 +40893,12 @@
       <c r="W266" s="30">
         <v>2.25</v>
       </c>
-      <c r="X266" s="31">
-        <v>15</v>
-      </c>
-      <c r="Y266" s="83"/>
+      <c r="X266" s="35" t="s">
+        <v>64</v>
+      </c>
+      <c r="Y266" s="98" t="s">
+        <v>64</v>
+      </c>
       <c r="Z266" s="96" t="s">
         <v>65</v>
       </c>
@@ -40912,10 +40912,10 @@
         <v>2.4</v>
       </c>
       <c r="AD266" s="32">
-        <v>78.5</v>
+        <v>39.4</v>
       </c>
       <c r="AE266" s="83">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="AF266" s="28">
         <v>1157</v>
@@ -40944,7 +40944,7 @@
       <c r="AP266" s="40"/>
       <c r="AQ266" s="41"/>
       <c r="AR266" s="41" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AS266" s="41" t="s">
         <v>269</v>
@@ -40975,25 +40975,25 @@
         <v>61</v>
       </c>
       <c r="B267" s="29" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="C267" s="83">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="D267" s="84">
-        <v>3133</v>
+        <v>2183</v>
       </c>
       <c r="E267" s="32">
         <v>0.5</v>
       </c>
       <c r="F267" s="31">
-        <v>86489</v>
+        <v>67442</v>
       </c>
       <c r="G267" s="32">
-        <v>69011</v>
+        <v>50799</v>
       </c>
       <c r="H267" s="32" t="s">
-        <v>401</v>
+        <v>261</v>
       </c>
       <c r="I267" s="32">
         <v>80</v>
@@ -41002,10 +41002,10 @@
         <v>67</v>
       </c>
       <c r="K267" s="32">
-        <v>60</v>
+        <v>58.8</v>
       </c>
       <c r="L267" s="83">
-        <v>58.3</v>
+        <v>57.2</v>
       </c>
       <c r="M267" s="35" t="s">
         <v>64</v>
@@ -41023,10 +41023,10 @@
         <v>64</v>
       </c>
       <c r="R267" s="31">
-        <v>86000</v>
-      </c>
-      <c r="S267" s="32">
-        <v>50000</v>
+        <v>67000</v>
+      </c>
+      <c r="S267" s="32" t="s">
+        <v>64</v>
       </c>
       <c r="T267" s="32"/>
       <c r="U267" s="32"/>
@@ -41036,12 +41036,10 @@
       <c r="W267" s="30">
         <v>2.25</v>
       </c>
-      <c r="X267" s="35" t="s">
-        <v>64</v>
-      </c>
-      <c r="Y267" s="98" t="s">
-        <v>64</v>
-      </c>
+      <c r="X267" s="31">
+        <v>5</v>
+      </c>
+      <c r="Y267" s="83"/>
       <c r="Z267" s="96" t="s">
         <v>65</v>
       </c>
@@ -41052,19 +41050,19 @@
         <v>66</v>
       </c>
       <c r="AC267" s="32">
-        <v>2.4</v>
+        <v>1.2</v>
       </c>
       <c r="AD267" s="32">
-        <v>39.4</v>
+        <v>40.9</v>
       </c>
       <c r="AE267" s="83">
         <v>50</v>
       </c>
       <c r="AF267" s="28">
-        <v>1157</v>
+        <v>645</v>
       </c>
       <c r="AH267" s="40">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="AI267" s="41" t="s">
         <v>66</v>
@@ -41087,10 +41085,10 @@
       <c r="AP267" s="40"/>
       <c r="AQ267" s="41"/>
       <c r="AR267" s="41" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="AS267" s="41" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="AT267" s="41"/>
       <c r="AU267" s="41"/>
@@ -41098,17 +41096,17 @@
       <c r="AW267" s="41"/>
       <c r="AX267" s="41"/>
       <c r="AY267" s="41" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="AZ267" s="41"/>
       <c r="BA267" s="41"/>
       <c r="BB267" s="29" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="BC267" s="41"/>
       <c r="BD267" s="41"/>
       <c r="BE267" s="29" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="BF267" s="41"/>
       <c r="BG267" s="44"/>
@@ -41118,7 +41116,7 @@
         <v>61</v>
       </c>
       <c r="B268" s="29" t="s">
-        <v>411</v>
+        <v>260</v>
       </c>
       <c r="C268" s="83">
         <v>6</v>
@@ -41180,7 +41178,7 @@
         <v>2.25</v>
       </c>
       <c r="X268" s="31">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="Y268" s="83"/>
       <c r="Z268" s="96" t="s">
@@ -41190,16 +41188,16 @@
         <v>2</v>
       </c>
       <c r="AB268" s="31" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="AC268" s="32">
         <v>1.2</v>
       </c>
       <c r="AD268" s="32">
-        <v>40.9</v>
+        <v>57.8</v>
       </c>
       <c r="AE268" s="83">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AF268" s="28">
         <v>645</v>
@@ -41208,7 +41206,7 @@
         <v>6</v>
       </c>
       <c r="AI268" s="41" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="AJ268" s="42" t="s">
         <v>262</v>
@@ -41228,7 +41226,7 @@
       <c r="AP268" s="40"/>
       <c r="AQ268" s="41"/>
       <c r="AR268" s="41" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AS268" s="41" t="s">
         <v>264</v>
@@ -41244,12 +41242,12 @@
       <c r="AZ268" s="41"/>
       <c r="BA268" s="41"/>
       <c r="BB268" s="29" t="s">
-        <v>411</v>
+        <v>260</v>
       </c>
       <c r="BC268" s="41"/>
       <c r="BD268" s="41"/>
       <c r="BE268" s="29" t="s">
-        <v>411</v>
+        <v>260</v>
       </c>
       <c r="BF268" s="41"/>
       <c r="BG268" s="44"/>
@@ -41321,7 +41319,7 @@
         <v>2.25</v>
       </c>
       <c r="X269" s="31">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="Y269" s="83"/>
       <c r="Z269" s="96" t="s">
@@ -41337,10 +41335,10 @@
         <v>1.2</v>
       </c>
       <c r="AD269" s="32">
-        <v>57.8</v>
+        <v>35.299999999999997</v>
       </c>
       <c r="AE269" s="83">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="AF269" s="28">
         <v>645</v>
@@ -41369,7 +41367,7 @@
       <c r="AP269" s="40"/>
       <c r="AQ269" s="41"/>
       <c r="AR269" s="41" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AS269" s="41" t="s">
         <v>264</v>
@@ -41462,7 +41460,7 @@
         <v>2.25</v>
       </c>
       <c r="X270" s="31">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Y270" s="83"/>
       <c r="Z270" s="96" t="s">
@@ -41478,10 +41476,10 @@
         <v>1.2</v>
       </c>
       <c r="AD270" s="32">
-        <v>35.299999999999997</v>
+        <v>27.7</v>
       </c>
       <c r="AE270" s="83">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="AF270" s="28">
         <v>645</v>
@@ -41510,7 +41508,7 @@
       <c r="AP270" s="40"/>
       <c r="AQ270" s="41"/>
       <c r="AR270" s="41" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AS270" s="41" t="s">
         <v>264</v>
@@ -41602,10 +41600,12 @@
       <c r="W271" s="30">
         <v>2.25</v>
       </c>
-      <c r="X271" s="31">
-        <v>10</v>
-      </c>
-      <c r="Y271" s="83"/>
+      <c r="X271" s="35" t="s">
+        <v>64</v>
+      </c>
+      <c r="Y271" s="98" t="s">
+        <v>64</v>
+      </c>
       <c r="Z271" s="96" t="s">
         <v>65</v>
       </c>
@@ -41619,10 +41619,10 @@
         <v>1.2</v>
       </c>
       <c r="AD271" s="32">
-        <v>27.7</v>
+        <v>12.7</v>
       </c>
       <c r="AE271" s="83">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="AF271" s="28">
         <v>645</v>
@@ -41651,7 +41651,7 @@
       <c r="AP271" s="40"/>
       <c r="AQ271" s="41"/>
       <c r="AR271" s="41" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AS271" s="41" t="s">
         <v>264</v>
@@ -41682,7 +41682,7 @@
         <v>61</v>
       </c>
       <c r="B272" s="29" t="s">
-        <v>260</v>
+        <v>411</v>
       </c>
       <c r="C272" s="83">
         <v>6</v>
@@ -41743,12 +41743,10 @@
       <c r="W272" s="30">
         <v>2.25</v>
       </c>
-      <c r="X272" s="35" t="s">
-        <v>64</v>
-      </c>
-      <c r="Y272" s="98" t="s">
-        <v>64</v>
-      </c>
+      <c r="X272" s="31">
+        <v>30</v>
+      </c>
+      <c r="Y272" s="83"/>
       <c r="Z272" s="96" t="s">
         <v>65</v>
       </c>
@@ -41756,16 +41754,16 @@
         <v>2</v>
       </c>
       <c r="AB272" s="31" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="AC272" s="32">
         <v>1.2</v>
       </c>
       <c r="AD272" s="32">
-        <v>12.7</v>
+        <v>106</v>
       </c>
       <c r="AE272" s="83">
-        <v>15</v>
+        <v>110</v>
       </c>
       <c r="AF272" s="28">
         <v>645</v>
@@ -41774,7 +41772,7 @@
         <v>6</v>
       </c>
       <c r="AI272" s="41" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="AJ272" s="42" t="s">
         <v>262</v>
@@ -41794,7 +41792,7 @@
       <c r="AP272" s="40"/>
       <c r="AQ272" s="41"/>
       <c r="AR272" s="41" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AS272" s="41" t="s">
         <v>264</v>
@@ -41810,12 +41808,12 @@
       <c r="AZ272" s="41"/>
       <c r="BA272" s="41"/>
       <c r="BB272" s="29" t="s">
-        <v>260</v>
+        <v>411</v>
       </c>
       <c r="BC272" s="41"/>
       <c r="BD272" s="41"/>
       <c r="BE272" s="29" t="s">
-        <v>260</v>
+        <v>411</v>
       </c>
       <c r="BF272" s="41"/>
       <c r="BG272" s="44"/>
@@ -41887,7 +41885,7 @@
         <v>2.25</v>
       </c>
       <c r="X273" s="31">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="Y273" s="83"/>
       <c r="Z273" s="96" t="s">
@@ -41903,10 +41901,10 @@
         <v>1.2</v>
       </c>
       <c r="AD273" s="32">
-        <v>106</v>
+        <v>79.7</v>
       </c>
       <c r="AE273" s="83">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="AF273" s="28">
         <v>645</v>
@@ -41935,7 +41933,7 @@
       <c r="AP273" s="40"/>
       <c r="AQ273" s="41"/>
       <c r="AR273" s="41" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AS273" s="41" t="s">
         <v>264</v>
@@ -42028,7 +42026,7 @@
         <v>2.25</v>
       </c>
       <c r="X274" s="31">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="Y274" s="83"/>
       <c r="Z274" s="96" t="s">
@@ -42044,10 +42042,10 @@
         <v>1.2</v>
       </c>
       <c r="AD274" s="32">
-        <v>79.7</v>
+        <v>67</v>
       </c>
       <c r="AE274" s="83">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AF274" s="28">
         <v>645</v>
@@ -42076,7 +42074,7 @@
       <c r="AP274" s="40"/>
       <c r="AQ274" s="41"/>
       <c r="AR274" s="41" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AS274" s="41" t="s">
         <v>264</v>
@@ -42169,7 +42167,7 @@
         <v>2.25</v>
       </c>
       <c r="X275" s="31">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Y275" s="83"/>
       <c r="Z275" s="96" t="s">
@@ -42185,10 +42183,10 @@
         <v>1.2</v>
       </c>
       <c r="AD275" s="32">
-        <v>67</v>
+        <v>53.8</v>
       </c>
       <c r="AE275" s="83">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AF275" s="28">
         <v>645</v>
@@ -42217,7 +42215,7 @@
       <c r="AP275" s="40"/>
       <c r="AQ275" s="41"/>
       <c r="AR275" s="41" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AS275" s="41" t="s">
         <v>264</v>
@@ -42309,10 +42307,12 @@
       <c r="W276" s="30">
         <v>2.25</v>
       </c>
-      <c r="X276" s="31">
-        <v>10</v>
-      </c>
-      <c r="Y276" s="83"/>
+      <c r="X276" s="35" t="s">
+        <v>64</v>
+      </c>
+      <c r="Y276" s="98" t="s">
+        <v>64</v>
+      </c>
       <c r="Z276" s="96" t="s">
         <v>65</v>
       </c>
@@ -42326,10 +42326,10 @@
         <v>1.2</v>
       </c>
       <c r="AD276" s="32">
-        <v>53.8</v>
+        <v>27.9</v>
       </c>
       <c r="AE276" s="83">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="AF276" s="28">
         <v>645</v>
@@ -42358,7 +42358,7 @@
       <c r="AP276" s="40"/>
       <c r="AQ276" s="41"/>
       <c r="AR276" s="41" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AS276" s="41" t="s">
         <v>264</v>
@@ -42389,25 +42389,25 @@
         <v>61</v>
       </c>
       <c r="B277" s="29" t="s">
-        <v>411</v>
+        <v>422</v>
       </c>
       <c r="C277" s="83">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D277" s="84">
-        <v>2183</v>
+        <v>2071</v>
       </c>
       <c r="E277" s="32">
         <v>0.5</v>
       </c>
       <c r="F277" s="31">
-        <v>67442</v>
+        <v>58342</v>
       </c>
       <c r="G277" s="32">
-        <v>50799</v>
+        <v>47695</v>
       </c>
       <c r="H277" s="32" t="s">
-        <v>261</v>
+        <v>423</v>
       </c>
       <c r="I277" s="32">
         <v>80</v>
@@ -42416,10 +42416,10 @@
         <v>67</v>
       </c>
       <c r="K277" s="32">
-        <v>58.8</v>
+        <v>59.1</v>
       </c>
       <c r="L277" s="83">
-        <v>57.2</v>
+        <v>58.1</v>
       </c>
       <c r="M277" s="35" t="s">
         <v>64</v>
@@ -42437,51 +42437,49 @@
         <v>64</v>
       </c>
       <c r="R277" s="31">
-        <v>67000</v>
+        <v>55000</v>
       </c>
       <c r="S277" s="32" t="s">
         <v>64</v>
       </c>
       <c r="T277" s="32"/>
       <c r="U277" s="32"/>
-      <c r="V277" s="32">
-        <v>3.4</v>
-      </c>
-      <c r="W277" s="30">
-        <v>2.25</v>
-      </c>
-      <c r="X277" s="35" t="s">
-        <v>64</v>
-      </c>
-      <c r="Y277" s="98" t="s">
-        <v>64</v>
-      </c>
+      <c r="V277" s="32" t="s">
+        <v>64</v>
+      </c>
+      <c r="W277" s="30" t="s">
+        <v>64</v>
+      </c>
+      <c r="X277" s="31">
+        <v>15</v>
+      </c>
+      <c r="Y277" s="83"/>
       <c r="Z277" s="96" t="s">
         <v>65</v>
       </c>
       <c r="AA277" s="28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB277" s="31" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="AC277" s="32">
         <v>1.2</v>
       </c>
       <c r="AD277" s="32">
-        <v>27.9</v>
+        <v>35.5</v>
       </c>
       <c r="AE277" s="83">
         <v>40</v>
       </c>
       <c r="AF277" s="28">
-        <v>645</v>
+        <v>600</v>
       </c>
       <c r="AH277" s="40">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AI277" s="41" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="AJ277" s="42" t="s">
         <v>262</v>
@@ -42490,7 +42488,7 @@
         <v>68</v>
       </c>
       <c r="AL277" s="41">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AM277" s="42" t="s">
         <v>64</v>
@@ -42501,7 +42499,7 @@
       <c r="AP277" s="40"/>
       <c r="AQ277" s="41"/>
       <c r="AR277" s="41" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="AS277" s="41" t="s">
         <v>264</v>
@@ -42517,12 +42515,12 @@
       <c r="AZ277" s="41"/>
       <c r="BA277" s="41"/>
       <c r="BB277" s="29" t="s">
-        <v>411</v>
+        <v>422</v>
       </c>
       <c r="BC277" s="41"/>
       <c r="BD277" s="41"/>
       <c r="BE277" s="29" t="s">
-        <v>411</v>
+        <v>422</v>
       </c>
       <c r="BF277" s="41"/>
       <c r="BG277" s="44"/>
@@ -42594,7 +42592,7 @@
         <v>64</v>
       </c>
       <c r="X278" s="31">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Y278" s="83"/>
       <c r="Z278" s="96" t="s">
@@ -42610,10 +42608,10 @@
         <v>1.2</v>
       </c>
       <c r="AD278" s="32">
-        <v>35.5</v>
+        <v>28</v>
       </c>
       <c r="AE278" s="83">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="AF278" s="28">
         <v>600</v>
@@ -42642,7 +42640,7 @@
       <c r="AP278" s="40"/>
       <c r="AQ278" s="41"/>
       <c r="AR278" s="41" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AS278" s="41" t="s">
         <v>264</v>
@@ -42669,7 +42667,7 @@
       <c r="BG278" s="44"/>
     </row>
     <row r="279" spans="1:59" x14ac:dyDescent="0.25">
-      <c r="A279" s="28" t="s">
+      <c r="A279" s="48" t="s">
         <v>61</v>
       </c>
       <c r="B279" s="29" t="s">
@@ -42735,7 +42733,7 @@
         <v>64</v>
       </c>
       <c r="X279" s="31">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Y279" s="83"/>
       <c r="Z279" s="96" t="s">
@@ -42751,10 +42749,10 @@
         <v>1.2</v>
       </c>
       <c r="AD279" s="32">
-        <v>28</v>
+        <v>20.5</v>
       </c>
       <c r="AE279" s="83">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="AF279" s="28">
         <v>600</v>
@@ -42783,7 +42781,7 @@
       <c r="AP279" s="40"/>
       <c r="AQ279" s="41"/>
       <c r="AR279" s="41" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AS279" s="41" t="s">
         <v>264</v>
@@ -42875,10 +42873,12 @@
       <c r="W280" s="30" t="s">
         <v>64</v>
       </c>
-      <c r="X280" s="31">
-        <v>5</v>
-      </c>
-      <c r="Y280" s="83"/>
+      <c r="X280" s="35" t="s">
+        <v>64</v>
+      </c>
+      <c r="Y280" s="98" t="s">
+        <v>64</v>
+      </c>
       <c r="Z280" s="96" t="s">
         <v>65</v>
       </c>
@@ -42892,10 +42892,10 @@
         <v>1.2</v>
       </c>
       <c r="AD280" s="32">
-        <v>20.5</v>
+        <v>13</v>
       </c>
       <c r="AE280" s="83">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="AF280" s="28">
         <v>600</v>
@@ -42924,7 +42924,7 @@
       <c r="AP280" s="40"/>
       <c r="AQ280" s="41"/>
       <c r="AR280" s="41" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AS280" s="41" t="s">
         <v>264</v>
@@ -42955,22 +42955,22 @@
         <v>61</v>
       </c>
       <c r="B281" s="29" t="s">
-        <v>422</v>
+        <v>428</v>
       </c>
       <c r="C281" s="83">
         <v>5</v>
       </c>
       <c r="D281" s="84">
-        <v>2071</v>
+        <v>2060</v>
       </c>
       <c r="E281" s="32">
         <v>0.5</v>
       </c>
       <c r="F281" s="31">
-        <v>58342</v>
+        <v>58296</v>
       </c>
       <c r="G281" s="32">
-        <v>47695</v>
+        <v>47539</v>
       </c>
       <c r="H281" s="32" t="s">
         <v>423</v>
@@ -42982,7 +42982,7 @@
         <v>67</v>
       </c>
       <c r="K281" s="32">
-        <v>59.1</v>
+        <v>59</v>
       </c>
       <c r="L281" s="83">
         <v>58.1</v>
@@ -43016,12 +43016,10 @@
       <c r="W281" s="30" t="s">
         <v>64</v>
       </c>
-      <c r="X281" s="35" t="s">
-        <v>64</v>
-      </c>
-      <c r="Y281" s="98" t="s">
-        <v>64</v>
-      </c>
+      <c r="X281" s="31">
+        <v>20</v>
+      </c>
+      <c r="Y281" s="83"/>
       <c r="Z281" s="96" t="s">
         <v>65</v>
       </c>
@@ -43029,25 +43027,25 @@
         <v>1</v>
       </c>
       <c r="AB281" s="31" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="AC281" s="32">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="AD281" s="32">
-        <v>13</v>
+        <v>82.4</v>
       </c>
       <c r="AE281" s="83">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="AF281" s="28">
-        <v>600</v>
+        <v>596</v>
       </c>
       <c r="AH281" s="40">
         <v>5</v>
       </c>
       <c r="AI281" s="41" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="AJ281" s="42" t="s">
         <v>262</v>
@@ -43067,7 +43065,7 @@
       <c r="AP281" s="40"/>
       <c r="AQ281" s="41"/>
       <c r="AR281" s="41" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="AS281" s="41" t="s">
         <v>264</v>
@@ -43083,12 +43081,12 @@
       <c r="AZ281" s="41"/>
       <c r="BA281" s="41"/>
       <c r="BB281" s="29" t="s">
-        <v>422</v>
+        <v>428</v>
       </c>
       <c r="BC281" s="41"/>
       <c r="BD281" s="41"/>
       <c r="BE281" s="29" t="s">
-        <v>422</v>
+        <v>428</v>
       </c>
       <c r="BF281" s="41"/>
       <c r="BG281" s="44"/>
@@ -43160,7 +43158,7 @@
         <v>64</v>
       </c>
       <c r="X282" s="31">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="Y282" s="83"/>
       <c r="Z282" s="96" t="s">
@@ -43176,10 +43174,10 @@
         <v>1</v>
       </c>
       <c r="AD282" s="32">
-        <v>82.4</v>
+        <v>69.599999999999994</v>
       </c>
       <c r="AE282" s="83">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="AF282" s="28">
         <v>596</v>
@@ -43208,7 +43206,7 @@
       <c r="AP282" s="40"/>
       <c r="AQ282" s="41"/>
       <c r="AR282" s="41" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AS282" s="41" t="s">
         <v>264</v>
@@ -43301,7 +43299,7 @@
         <v>64</v>
       </c>
       <c r="X283" s="31">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="Y283" s="83"/>
       <c r="Z283" s="96" t="s">
@@ -43317,10 +43315,10 @@
         <v>1</v>
       </c>
       <c r="AD283" s="32">
-        <v>69.599999999999994</v>
+        <v>43.5</v>
       </c>
       <c r="AE283" s="83">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="AF283" s="28">
         <v>596</v>
@@ -43349,7 +43347,7 @@
       <c r="AP283" s="40"/>
       <c r="AQ283" s="41"/>
       <c r="AR283" s="41" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AS283" s="41" t="s">
         <v>264</v>
@@ -43441,10 +43439,12 @@
       <c r="W284" s="30" t="s">
         <v>64</v>
       </c>
-      <c r="X284" s="31">
-        <v>5</v>
-      </c>
-      <c r="Y284" s="83"/>
+      <c r="X284" s="35" t="s">
+        <v>64</v>
+      </c>
+      <c r="Y284" s="98" t="s">
+        <v>64</v>
+      </c>
       <c r="Z284" s="96" t="s">
         <v>65</v>
       </c>
@@ -43458,10 +43458,10 @@
         <v>1</v>
       </c>
       <c r="AD284" s="32">
-        <v>43.5</v>
+        <v>30.5</v>
       </c>
       <c r="AE284" s="83">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="AF284" s="28">
         <v>596</v>
@@ -43490,7 +43490,7 @@
       <c r="AP284" s="40"/>
       <c r="AQ284" s="41"/>
       <c r="AR284" s="41" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AS284" s="41" t="s">
         <v>264</v>
@@ -43521,22 +43521,22 @@
         <v>61</v>
       </c>
       <c r="B285" s="29" t="s">
-        <v>428</v>
+        <v>433</v>
       </c>
       <c r="C285" s="83">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D285" s="84">
-        <v>2060</v>
+        <v>1604</v>
       </c>
       <c r="E285" s="32">
         <v>0.5</v>
       </c>
       <c r="F285" s="31">
-        <v>58296</v>
+        <v>46090</v>
       </c>
       <c r="G285" s="32">
-        <v>47539</v>
+        <v>36667</v>
       </c>
       <c r="H285" s="32" t="s">
         <v>423</v>
@@ -43548,10 +43548,10 @@
         <v>67</v>
       </c>
       <c r="K285" s="32">
-        <v>59</v>
+        <v>59.2</v>
       </c>
       <c r="L285" s="83">
-        <v>58.1</v>
+        <v>58</v>
       </c>
       <c r="M285" s="35" t="s">
         <v>64</v>
@@ -43569,7 +43569,7 @@
         <v>64</v>
       </c>
       <c r="R285" s="31">
-        <v>55000</v>
+        <v>45000</v>
       </c>
       <c r="S285" s="32" t="s">
         <v>64</v>
@@ -43582,12 +43582,10 @@
       <c r="W285" s="30" t="s">
         <v>64</v>
       </c>
-      <c r="X285" s="35" t="s">
-        <v>64</v>
-      </c>
-      <c r="Y285" s="98" t="s">
-        <v>64</v>
-      </c>
+      <c r="X285" s="31">
+        <v>20</v>
+      </c>
+      <c r="Y285" s="83"/>
       <c r="Z285" s="96" t="s">
         <v>65</v>
       </c>
@@ -43595,25 +43593,25 @@
         <v>1</v>
       </c>
       <c r="AB285" s="31" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="AC285" s="32">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AD285" s="32">
-        <v>30.5</v>
+        <v>40.5</v>
       </c>
       <c r="AE285" s="83">
         <v>45</v>
       </c>
       <c r="AF285" s="28">
-        <v>596</v>
+        <v>586</v>
       </c>
       <c r="AH285" s="40">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AI285" s="41" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="AJ285" s="42" t="s">
         <v>262</v>
@@ -43633,7 +43631,7 @@
       <c r="AP285" s="40"/>
       <c r="AQ285" s="41"/>
       <c r="AR285" s="41" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="AS285" s="41" t="s">
         <v>264</v>
@@ -43649,12 +43647,12 @@
       <c r="AZ285" s="41"/>
       <c r="BA285" s="41"/>
       <c r="BB285" s="29" t="s">
-        <v>428</v>
+        <v>433</v>
       </c>
       <c r="BC285" s="41"/>
       <c r="BD285" s="41"/>
       <c r="BE285" s="29" t="s">
-        <v>428</v>
+        <v>433</v>
       </c>
       <c r="BF285" s="41"/>
       <c r="BG285" s="44"/>
@@ -43726,7 +43724,7 @@
         <v>64</v>
       </c>
       <c r="X286" s="31">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="Y286" s="83"/>
       <c r="Z286" s="96" t="s">
@@ -43742,10 +43740,10 @@
         <v>1.2</v>
       </c>
       <c r="AD286" s="32">
-        <v>40.5</v>
+        <v>33</v>
       </c>
       <c r="AE286" s="83">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="AF286" s="28">
         <v>586</v>
@@ -43774,7 +43772,7 @@
       <c r="AP286" s="40"/>
       <c r="AQ286" s="41"/>
       <c r="AR286" s="41" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AS286" s="41" t="s">
         <v>264</v>
@@ -43867,7 +43865,7 @@
         <v>64</v>
       </c>
       <c r="X287" s="31">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Y287" s="83"/>
       <c r="Z287" s="96" t="s">
@@ -43883,10 +43881,10 @@
         <v>1.2</v>
       </c>
       <c r="AD287" s="32">
-        <v>33</v>
+        <v>25.4</v>
       </c>
       <c r="AE287" s="83">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="AF287" s="28">
         <v>586</v>
@@ -43915,7 +43913,7 @@
       <c r="AP287" s="40"/>
       <c r="AQ287" s="41"/>
       <c r="AR287" s="41" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AS287" s="41" t="s">
         <v>264</v>
@@ -44008,7 +44006,7 @@
         <v>64</v>
       </c>
       <c r="X288" s="31">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Y288" s="83"/>
       <c r="Z288" s="96" t="s">
@@ -44024,10 +44022,10 @@
         <v>1.2</v>
       </c>
       <c r="AD288" s="32">
-        <v>25.4</v>
+        <v>17.899999999999999</v>
       </c>
       <c r="AE288" s="83">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="AF288" s="28">
         <v>586</v>
@@ -44056,7 +44054,7 @@
       <c r="AP288" s="40"/>
       <c r="AQ288" s="41"/>
       <c r="AR288" s="41" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AS288" s="41" t="s">
         <v>264</v>
@@ -44148,10 +44146,12 @@
       <c r="W289" s="30" t="s">
         <v>64</v>
       </c>
-      <c r="X289" s="31">
-        <v>5</v>
-      </c>
-      <c r="Y289" s="83"/>
+      <c r="X289" s="35" t="s">
+        <v>64</v>
+      </c>
+      <c r="Y289" s="98" t="s">
+        <v>64</v>
+      </c>
       <c r="Z289" s="96" t="s">
         <v>65</v>
       </c>
@@ -44165,10 +44165,10 @@
         <v>1.2</v>
       </c>
       <c r="AD289" s="32">
-        <v>17.899999999999999</v>
+        <v>10.4</v>
       </c>
       <c r="AE289" s="83">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="AF289" s="28">
         <v>586</v>
@@ -44197,7 +44197,7 @@
       <c r="AP289" s="40"/>
       <c r="AQ289" s="41"/>
       <c r="AR289" s="41" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AS289" s="41" t="s">
         <v>264</v>
@@ -44228,7 +44228,7 @@
         <v>61</v>
       </c>
       <c r="B290" s="29" t="s">
-        <v>433</v>
+        <v>439</v>
       </c>
       <c r="C290" s="83">
         <v>4</v>
@@ -44289,12 +44289,10 @@
       <c r="W290" s="30" t="s">
         <v>64</v>
       </c>
-      <c r="X290" s="35" t="s">
-        <v>64</v>
-      </c>
-      <c r="Y290" s="98" t="s">
-        <v>64</v>
-      </c>
+      <c r="X290" s="31">
+        <v>20</v>
+      </c>
+      <c r="Y290" s="83"/>
       <c r="Z290" s="96" t="s">
         <v>65</v>
       </c>
@@ -44302,25 +44300,25 @@
         <v>1</v>
       </c>
       <c r="AB290" s="31" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="AC290" s="32">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="AD290" s="32">
-        <v>10.4</v>
+        <v>75.400000000000006</v>
       </c>
       <c r="AE290" s="83">
-        <v>15</v>
+        <v>80</v>
       </c>
       <c r="AF290" s="28">
-        <v>586</v>
+        <v>582</v>
       </c>
       <c r="AH290" s="40">
         <v>4</v>
       </c>
       <c r="AI290" s="41" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="AJ290" s="42" t="s">
         <v>262</v>
@@ -44340,7 +44338,7 @@
       <c r="AP290" s="40"/>
       <c r="AQ290" s="41"/>
       <c r="AR290" s="41" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="AS290" s="41" t="s">
         <v>264</v>
@@ -44356,12 +44354,12 @@
       <c r="AZ290" s="41"/>
       <c r="BA290" s="41"/>
       <c r="BB290" s="29" t="s">
-        <v>433</v>
+        <v>439</v>
       </c>
       <c r="BC290" s="41"/>
       <c r="BD290" s="41"/>
       <c r="BE290" s="29" t="s">
-        <v>433</v>
+        <v>439</v>
       </c>
       <c r="BF290" s="41"/>
       <c r="BG290" s="44"/>
@@ -44433,7 +44431,7 @@
         <v>64</v>
       </c>
       <c r="X291" s="31">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="Y291" s="83"/>
       <c r="Z291" s="96" t="s">
@@ -44449,10 +44447,10 @@
         <v>1</v>
       </c>
       <c r="AD291" s="32">
-        <v>75.400000000000006</v>
+        <v>62.6</v>
       </c>
       <c r="AE291" s="83">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AF291" s="28">
         <v>582</v>
@@ -44481,7 +44479,7 @@
       <c r="AP291" s="40"/>
       <c r="AQ291" s="41"/>
       <c r="AR291" s="41" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AS291" s="41" t="s">
         <v>264</v>
@@ -44574,7 +44572,7 @@
         <v>64</v>
       </c>
       <c r="X292" s="31">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Y292" s="83"/>
       <c r="Z292" s="96" t="s">
@@ -44590,10 +44588,10 @@
         <v>1</v>
       </c>
       <c r="AD292" s="32">
-        <v>62.6</v>
+        <v>49.5</v>
       </c>
       <c r="AE292" s="83">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="AF292" s="28">
         <v>582</v>
@@ -44622,7 +44620,7 @@
       <c r="AP292" s="40"/>
       <c r="AQ292" s="41"/>
       <c r="AR292" s="41" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AS292" s="41" t="s">
         <v>264</v>
@@ -44715,7 +44713,7 @@
         <v>64</v>
       </c>
       <c r="X293" s="31">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Y293" s="83"/>
       <c r="Z293" s="96" t="s">
@@ -44731,10 +44729,10 @@
         <v>1</v>
       </c>
       <c r="AD293" s="32">
-        <v>49.5</v>
+        <v>36.5</v>
       </c>
       <c r="AE293" s="83">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="AF293" s="28">
         <v>582</v>
@@ -44763,7 +44761,7 @@
       <c r="AP293" s="40"/>
       <c r="AQ293" s="41"/>
       <c r="AR293" s="41" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AS293" s="41" t="s">
         <v>264</v>
@@ -44855,10 +44853,12 @@
       <c r="W294" s="30" t="s">
         <v>64</v>
       </c>
-      <c r="X294" s="31">
-        <v>5</v>
-      </c>
-      <c r="Y294" s="83"/>
+      <c r="X294" s="35" t="s">
+        <v>64</v>
+      </c>
+      <c r="Y294" s="98" t="s">
+        <v>64</v>
+      </c>
       <c r="Z294" s="96" t="s">
         <v>65</v>
       </c>
@@ -44872,10 +44872,10 @@
         <v>1</v>
       </c>
       <c r="AD294" s="32">
-        <v>36.5</v>
+        <v>23.5</v>
       </c>
       <c r="AE294" s="83">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="AF294" s="28">
         <v>582</v>
@@ -44904,7 +44904,7 @@
       <c r="AP294" s="40"/>
       <c r="AQ294" s="41"/>
       <c r="AR294" s="41" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AS294" s="41" t="s">
         <v>264</v>
@@ -44935,25 +44935,25 @@
         <v>61</v>
       </c>
       <c r="B295" s="29" t="s">
-        <v>439</v>
+        <v>445</v>
       </c>
       <c r="C295" s="83">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D295" s="84">
-        <v>1604</v>
+        <v>1272</v>
       </c>
       <c r="E295" s="32">
         <v>0.5</v>
       </c>
       <c r="F295" s="31">
-        <v>46090</v>
+        <v>35188</v>
       </c>
       <c r="G295" s="32">
-        <v>36667</v>
+        <v>27662</v>
       </c>
       <c r="H295" s="32" t="s">
-        <v>423</v>
+        <v>446</v>
       </c>
       <c r="I295" s="32">
         <v>80</v>
@@ -44962,10 +44962,10 @@
         <v>67</v>
       </c>
       <c r="K295" s="32">
-        <v>59.2</v>
+        <v>60.2</v>
       </c>
       <c r="L295" s="83">
-        <v>58</v>
+        <v>58.3</v>
       </c>
       <c r="M295" s="35" t="s">
         <v>64</v>
@@ -44983,7 +44983,7 @@
         <v>64</v>
       </c>
       <c r="R295" s="31">
-        <v>45000</v>
+        <v>33600</v>
       </c>
       <c r="S295" s="32" t="s">
         <v>64</v>
@@ -44996,12 +44996,10 @@
       <c r="W295" s="30" t="s">
         <v>64</v>
       </c>
-      <c r="X295" s="35" t="s">
-        <v>64</v>
-      </c>
-      <c r="Y295" s="98" t="s">
-        <v>64</v>
-      </c>
+      <c r="X295" s="31">
+        <v>15</v>
+      </c>
+      <c r="Y295" s="83"/>
       <c r="Z295" s="96" t="s">
         <v>65</v>
       </c>
@@ -45009,25 +45007,25 @@
         <v>1</v>
       </c>
       <c r="AB295" s="31" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="AC295" s="32">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AD295" s="32">
-        <v>23.5</v>
+        <v>31.6</v>
       </c>
       <c r="AE295" s="83">
         <v>35</v>
       </c>
       <c r="AF295" s="28">
-        <v>582</v>
+        <v>543</v>
       </c>
       <c r="AH295" s="40">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AI295" s="41" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="AJ295" s="42" t="s">
         <v>262</v>
@@ -45047,7 +45045,7 @@
       <c r="AP295" s="40"/>
       <c r="AQ295" s="41"/>
       <c r="AR295" s="41" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="AS295" s="41" t="s">
         <v>264</v>
@@ -45063,12 +45061,12 @@
       <c r="AZ295" s="41"/>
       <c r="BA295" s="41"/>
       <c r="BB295" s="29" t="s">
-        <v>439</v>
+        <v>445</v>
       </c>
       <c r="BC295" s="41"/>
       <c r="BD295" s="41"/>
       <c r="BE295" s="29" t="s">
-        <v>439</v>
+        <v>445</v>
       </c>
       <c r="BF295" s="41"/>
       <c r="BG295" s="44"/>
@@ -45140,7 +45138,7 @@
         <v>64</v>
       </c>
       <c r="X296" s="31">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Y296" s="83"/>
       <c r="Z296" s="96" t="s">
@@ -45156,10 +45154,10 @@
         <v>1.2</v>
       </c>
       <c r="AD296" s="32">
-        <v>31.6</v>
+        <v>24.1</v>
       </c>
       <c r="AE296" s="83">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="AF296" s="28">
         <v>543</v>
@@ -45188,7 +45186,7 @@
       <c r="AP296" s="40"/>
       <c r="AQ296" s="41"/>
       <c r="AR296" s="41" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AS296" s="41" t="s">
         <v>264</v>
@@ -45281,7 +45279,7 @@
         <v>64</v>
       </c>
       <c r="X297" s="31">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Y297" s="83"/>
       <c r="Z297" s="96" t="s">
@@ -45297,10 +45295,10 @@
         <v>1.2</v>
       </c>
       <c r="AD297" s="32">
-        <v>24.1</v>
+        <v>16.600000000000001</v>
       </c>
       <c r="AE297" s="83">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="AF297" s="28">
         <v>543</v>
@@ -45329,7 +45327,7 @@
       <c r="AP297" s="40"/>
       <c r="AQ297" s="41"/>
       <c r="AR297" s="41" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AS297" s="41" t="s">
         <v>264</v>
@@ -45421,10 +45419,12 @@
       <c r="W298" s="30" t="s">
         <v>64</v>
       </c>
-      <c r="X298" s="31">
-        <v>5</v>
-      </c>
-      <c r="Y298" s="83"/>
+      <c r="X298" s="35" t="s">
+        <v>64</v>
+      </c>
+      <c r="Y298" s="98" t="s">
+        <v>64</v>
+      </c>
       <c r="Z298" s="96" t="s">
         <v>65</v>
       </c>
@@ -45438,10 +45438,10 @@
         <v>1.2</v>
       </c>
       <c r="AD298" s="32">
-        <v>16.600000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="AE298" s="83">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="AF298" s="28">
         <v>543</v>
@@ -45470,7 +45470,7 @@
       <c r="AP298" s="40"/>
       <c r="AQ298" s="41"/>
       <c r="AR298" s="41" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AS298" s="41" t="s">
         <v>264</v>
@@ -45501,22 +45501,22 @@
         <v>61</v>
       </c>
       <c r="B299" s="29" t="s">
-        <v>445</v>
+        <v>451</v>
       </c>
       <c r="C299" s="83">
         <v>3</v>
       </c>
       <c r="D299" s="84">
-        <v>1272</v>
+        <v>1303</v>
       </c>
       <c r="E299" s="32">
         <v>0.5</v>
       </c>
       <c r="F299" s="31">
-        <v>35188</v>
+        <v>35301</v>
       </c>
       <c r="G299" s="32">
-        <v>27662</v>
+        <v>28087</v>
       </c>
       <c r="H299" s="32" t="s">
         <v>446</v>
@@ -45528,10 +45528,10 @@
         <v>67</v>
       </c>
       <c r="K299" s="32">
-        <v>60.2</v>
+        <v>60.4</v>
       </c>
       <c r="L299" s="83">
-        <v>58.3</v>
+        <v>58.5</v>
       </c>
       <c r="M299" s="35" t="s">
         <v>64</v>
@@ -45562,12 +45562,10 @@
       <c r="W299" s="30" t="s">
         <v>64</v>
       </c>
-      <c r="X299" s="35" t="s">
-        <v>64</v>
-      </c>
-      <c r="Y299" s="98" t="s">
-        <v>64</v>
-      </c>
+      <c r="X299" s="31">
+        <v>15</v>
+      </c>
+      <c r="Y299" s="83"/>
       <c r="Z299" s="96" t="s">
         <v>65</v>
       </c>
@@ -45575,25 +45573,25 @@
         <v>1</v>
       </c>
       <c r="AB299" s="31" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="AC299" s="32">
-        <v>1.2</v>
+        <v>0.75</v>
       </c>
       <c r="AD299" s="32">
-        <v>9.1</v>
+        <v>58.9</v>
       </c>
       <c r="AE299" s="83">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="AF299" s="28">
-        <v>543</v>
+        <v>535</v>
       </c>
       <c r="AH299" s="40">
         <v>3</v>
       </c>
       <c r="AI299" s="41" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="AJ299" s="42" t="s">
         <v>262</v>
@@ -45613,7 +45611,7 @@
       <c r="AP299" s="40"/>
       <c r="AQ299" s="41"/>
       <c r="AR299" s="41" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="AS299" s="41" t="s">
         <v>264</v>
@@ -45629,12 +45627,12 @@
       <c r="AZ299" s="41"/>
       <c r="BA299" s="41"/>
       <c r="BB299" s="29" t="s">
-        <v>445</v>
+        <v>451</v>
       </c>
       <c r="BC299" s="41"/>
       <c r="BD299" s="41"/>
       <c r="BE299" s="29" t="s">
-        <v>445</v>
+        <v>451</v>
       </c>
       <c r="BF299" s="41"/>
       <c r="BG299" s="44"/>
@@ -45706,7 +45704,7 @@
         <v>64</v>
       </c>
       <c r="X300" s="31">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Y300" s="83"/>
       <c r="Z300" s="96" t="s">
@@ -45722,10 +45720,10 @@
         <v>0.75</v>
       </c>
       <c r="AD300" s="32">
-        <v>58.9</v>
+        <v>45.8</v>
       </c>
       <c r="AE300" s="83">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AF300" s="28">
         <v>535</v>
@@ -45754,7 +45752,7 @@
       <c r="AP300" s="40"/>
       <c r="AQ300" s="41"/>
       <c r="AR300" s="41" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AS300" s="41" t="s">
         <v>264</v>
@@ -45847,7 +45845,7 @@
         <v>64</v>
       </c>
       <c r="X301" s="31">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Y301" s="83"/>
       <c r="Z301" s="96" t="s">
@@ -45863,10 +45861,10 @@
         <v>0.75</v>
       </c>
       <c r="AD301" s="32">
-        <v>45.8</v>
+        <v>32.9</v>
       </c>
       <c r="AE301" s="83">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="AF301" s="28">
         <v>535</v>
@@ -45895,7 +45893,7 @@
       <c r="AP301" s="40"/>
       <c r="AQ301" s="41"/>
       <c r="AR301" s="41" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AS301" s="41" t="s">
         <v>264</v>
@@ -45921,457 +45919,459 @@
       <c r="BF301" s="41"/>
       <c r="BG301" s="44"/>
     </row>
-    <row r="302" spans="1:59" x14ac:dyDescent="0.25">
-      <c r="A302" s="48" t="s">
+    <row r="302" spans="1:59" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A302" s="65" t="s">
         <v>61</v>
       </c>
-      <c r="B302" s="29" t="s">
+      <c r="B302" s="100" t="s">
         <v>451</v>
       </c>
-      <c r="C302" s="83">
+      <c r="C302" s="101">
         <v>3</v>
       </c>
-      <c r="D302" s="84">
+      <c r="D302" s="102">
         <v>1303</v>
       </c>
-      <c r="E302" s="32">
+      <c r="E302" s="71">
         <v>0.5</v>
       </c>
-      <c r="F302" s="31">
+      <c r="F302" s="103">
         <v>35301</v>
       </c>
-      <c r="G302" s="32">
+      <c r="G302" s="71">
         <v>28087</v>
       </c>
-      <c r="H302" s="32" t="s">
+      <c r="H302" s="71" t="s">
         <v>446</v>
       </c>
-      <c r="I302" s="32">
+      <c r="I302" s="71">
         <v>80</v>
       </c>
-      <c r="J302" s="32">
+      <c r="J302" s="71">
         <v>67</v>
       </c>
-      <c r="K302" s="32">
+      <c r="K302" s="71">
         <v>60.4</v>
       </c>
-      <c r="L302" s="83">
+      <c r="L302" s="101">
         <v>58.5</v>
       </c>
-      <c r="M302" s="35" t="s">
-        <v>64</v>
-      </c>
-      <c r="N302" s="36" t="s">
-        <v>64</v>
-      </c>
-      <c r="O302" s="36" t="s">
-        <v>64</v>
-      </c>
-      <c r="P302" s="36" t="s">
-        <v>64</v>
-      </c>
-      <c r="Q302" s="85" t="s">
-        <v>64</v>
-      </c>
-      <c r="R302" s="31">
+      <c r="M302" s="60" t="s">
+        <v>64</v>
+      </c>
+      <c r="N302" s="61" t="s">
+        <v>64</v>
+      </c>
+      <c r="O302" s="61" t="s">
+        <v>64</v>
+      </c>
+      <c r="P302" s="61" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q302" s="104" t="s">
+        <v>64</v>
+      </c>
+      <c r="R302" s="103">
         <v>33600</v>
       </c>
-      <c r="S302" s="32" t="s">
-        <v>64</v>
-      </c>
-      <c r="T302" s="32"/>
-      <c r="U302" s="32"/>
-      <c r="V302" s="32" t="s">
-        <v>64</v>
-      </c>
-      <c r="W302" s="30" t="s">
-        <v>64</v>
-      </c>
-      <c r="X302" s="31">
-        <v>5</v>
-      </c>
-      <c r="Y302" s="83"/>
-      <c r="Z302" s="96" t="s">
-        <v>65</v>
-      </c>
-      <c r="AA302" s="28">
+      <c r="S302" s="71" t="s">
+        <v>64</v>
+      </c>
+      <c r="T302" s="71"/>
+      <c r="U302" s="71"/>
+      <c r="V302" s="71" t="s">
+        <v>64</v>
+      </c>
+      <c r="W302" s="105" t="s">
+        <v>64</v>
+      </c>
+      <c r="X302" s="60" t="s">
+        <v>64</v>
+      </c>
+      <c r="Y302" s="99" t="s">
+        <v>64</v>
+      </c>
+      <c r="Z302" s="106" t="s">
+        <v>65</v>
+      </c>
+      <c r="AA302" s="107">
         <v>1</v>
       </c>
-      <c r="AB302" s="31" t="s">
+      <c r="AB302" s="103" t="s">
         <v>66</v>
       </c>
-      <c r="AC302" s="32">
+      <c r="AC302" s="71">
         <v>0.75</v>
       </c>
-      <c r="AD302" s="32">
-        <v>32.9</v>
-      </c>
-      <c r="AE302" s="83">
-        <v>40</v>
-      </c>
-      <c r="AF302" s="28">
+      <c r="AD302" s="71">
+        <v>19.899999999999999</v>
+      </c>
+      <c r="AE302" s="101">
+        <v>30</v>
+      </c>
+      <c r="AF302" s="107">
         <v>535</v>
       </c>
-      <c r="AH302" s="40">
+      <c r="AH302" s="66">
         <v>3</v>
       </c>
-      <c r="AI302" s="41" t="s">
+      <c r="AI302" s="67" t="s">
         <v>66</v>
       </c>
-      <c r="AJ302" s="42" t="s">
+      <c r="AJ302" s="68" t="s">
         <v>262</v>
       </c>
-      <c r="AK302" s="41" t="s">
+      <c r="AK302" s="67" t="s">
         <v>68</v>
       </c>
-      <c r="AL302" s="41">
+      <c r="AL302" s="67">
         <v>1</v>
       </c>
-      <c r="AM302" s="42" t="s">
-        <v>64</v>
-      </c>
-      <c r="AN302" s="44" t="s">
-        <v>65</v>
-      </c>
-      <c r="AP302" s="40"/>
-      <c r="AQ302" s="41"/>
-      <c r="AR302" s="41" t="s">
-        <v>454</v>
-      </c>
-      <c r="AS302" s="41" t="s">
+      <c r="AM302" s="68" t="s">
+        <v>64</v>
+      </c>
+      <c r="AN302" s="70" t="s">
+        <v>65</v>
+      </c>
+      <c r="AP302" s="66"/>
+      <c r="AQ302" s="67"/>
+      <c r="AR302" s="67" t="s">
+        <v>455</v>
+      </c>
+      <c r="AS302" s="67" t="s">
         <v>264</v>
       </c>
-      <c r="AT302" s="41"/>
-      <c r="AU302" s="41"/>
-      <c r="AV302" s="41"/>
-      <c r="AW302" s="41"/>
-      <c r="AX302" s="41"/>
-      <c r="AY302" s="41" t="s">
+      <c r="AT302" s="67"/>
+      <c r="AU302" s="67"/>
+      <c r="AV302" s="67"/>
+      <c r="AW302" s="67"/>
+      <c r="AX302" s="67"/>
+      <c r="AY302" s="67" t="s">
         <v>265</v>
       </c>
-      <c r="AZ302" s="41"/>
-      <c r="BA302" s="41"/>
-      <c r="BB302" s="29" t="s">
+      <c r="AZ302" s="67"/>
+      <c r="BA302" s="67"/>
+      <c r="BB302" s="100" t="s">
         <v>451</v>
       </c>
-      <c r="BC302" s="41"/>
-      <c r="BD302" s="41"/>
-      <c r="BE302" s="29" t="s">
+      <c r="BC302" s="67"/>
+      <c r="BD302" s="67"/>
+      <c r="BE302" s="100" t="s">
         <v>451</v>
       </c>
-      <c r="BF302" s="41"/>
-      <c r="BG302" s="44"/>
+      <c r="BF302" s="67"/>
+      <c r="BG302" s="70"/>
     </row>
-    <row r="303" spans="1:59" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A303" s="65" t="s">
+    <row r="303" spans="1:59" x14ac:dyDescent="0.25">
+      <c r="A303" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="B303" s="100" t="s">
-        <v>451</v>
-      </c>
-      <c r="C303" s="101">
-        <v>3</v>
-      </c>
-      <c r="D303" s="102">
-        <v>1303</v>
-      </c>
-      <c r="E303" s="71">
-        <v>0.5</v>
-      </c>
-      <c r="F303" s="103">
-        <v>35301</v>
-      </c>
-      <c r="G303" s="71">
-        <v>28087</v>
-      </c>
-      <c r="H303" s="71" t="s">
-        <v>446</v>
-      </c>
-      <c r="I303" s="71">
+      <c r="B303" s="109" t="s">
+        <v>290</v>
+      </c>
+      <c r="C303" s="11">
+        <v>10</v>
+      </c>
+      <c r="D303" s="11">
+        <v>4120</v>
+      </c>
+      <c r="E303" s="11">
+        <v>1</v>
+      </c>
+      <c r="F303" s="11">
+        <v>128803</v>
+      </c>
+      <c r="G303" s="11">
+        <v>94756</v>
+      </c>
+      <c r="H303" s="11" t="s">
+        <v>291</v>
+      </c>
+      <c r="I303" s="11">
         <v>80</v>
       </c>
-      <c r="J303" s="71">
+      <c r="J303" s="11">
         <v>67</v>
       </c>
-      <c r="K303" s="71">
-        <v>60.4</v>
-      </c>
-      <c r="L303" s="101">
-        <v>58.5</v>
-      </c>
-      <c r="M303" s="60" t="s">
-        <v>64</v>
-      </c>
-      <c r="N303" s="61" t="s">
-        <v>64</v>
-      </c>
-      <c r="O303" s="61" t="s">
-        <v>64</v>
-      </c>
-      <c r="P303" s="61" t="s">
-        <v>64</v>
-      </c>
-      <c r="Q303" s="104" t="s">
-        <v>64</v>
-      </c>
-      <c r="R303" s="103">
-        <v>33600</v>
-      </c>
-      <c r="S303" s="71" t="s">
-        <v>64</v>
-      </c>
-      <c r="T303" s="71"/>
-      <c r="U303" s="71"/>
-      <c r="V303" s="71" t="s">
-        <v>64</v>
-      </c>
-      <c r="W303" s="105" t="s">
-        <v>64</v>
-      </c>
-      <c r="X303" s="60" t="s">
-        <v>64</v>
-      </c>
-      <c r="Y303" s="99" t="s">
-        <v>64</v>
-      </c>
-      <c r="Z303" s="106" t="s">
-        <v>65</v>
-      </c>
-      <c r="AA303" s="107">
-        <v>1</v>
-      </c>
-      <c r="AB303" s="103" t="s">
-        <v>66</v>
-      </c>
-      <c r="AC303" s="71">
-        <v>0.75</v>
-      </c>
-      <c r="AD303" s="71">
-        <v>19.899999999999999</v>
-      </c>
-      <c r="AE303" s="101">
-        <v>30</v>
-      </c>
-      <c r="AF303" s="107">
-        <v>535</v>
-      </c>
-      <c r="AH303" s="66">
-        <v>3</v>
-      </c>
-      <c r="AI303" s="67" t="s">
-        <v>66</v>
-      </c>
-      <c r="AJ303" s="68" t="s">
+      <c r="K303" s="11">
+        <v>59.1</v>
+      </c>
+      <c r="L303" s="11">
+        <v>57.1</v>
+      </c>
+      <c r="M303" s="109" t="s">
+        <v>64</v>
+      </c>
+      <c r="N303" s="109" t="s">
+        <v>64</v>
+      </c>
+      <c r="O303" s="109" t="s">
+        <v>64</v>
+      </c>
+      <c r="P303" s="109" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q303" s="109" t="s">
+        <v>64</v>
+      </c>
+      <c r="R303" s="11">
+        <v>114000</v>
+      </c>
+      <c r="S303" s="11">
+        <v>80000</v>
+      </c>
+      <c r="T303" s="11"/>
+      <c r="U303" s="11"/>
+      <c r="V303" s="11">
+        <v>3.74</v>
+      </c>
+      <c r="W303" s="11">
+        <v>2.5</v>
+      </c>
+      <c r="X303" s="109" t="s">
+        <v>64</v>
+      </c>
+      <c r="Y303" s="109" t="s">
+        <v>64</v>
+      </c>
+      <c r="Z303" s="109" t="s">
+        <v>211</v>
+      </c>
+      <c r="AA303" s="109" t="s">
+        <v>292</v>
+      </c>
+      <c r="AB303" s="109" t="s">
+        <v>77</v>
+      </c>
+      <c r="AC303" s="11">
+        <v>3.5</v>
+      </c>
+      <c r="AD303" s="11">
+        <v>26.5</v>
+      </c>
+      <c r="AE303" s="11">
+        <v>35</v>
+      </c>
+      <c r="AF303" s="75">
+        <v>1293</v>
+      </c>
+      <c r="AH303" s="80">
+        <v>10</v>
+      </c>
+      <c r="AI303" s="81" t="s">
+        <v>77</v>
+      </c>
+      <c r="AJ303" s="21" t="s">
         <v>262</v>
       </c>
-      <c r="AK303" s="67" t="s">
-        <v>68</v>
-      </c>
-      <c r="AL303" s="67">
-        <v>1</v>
-      </c>
-      <c r="AM303" s="68" t="s">
-        <v>64</v>
-      </c>
-      <c r="AN303" s="70" t="s">
-        <v>65</v>
-      </c>
-      <c r="AP303" s="66"/>
-      <c r="AQ303" s="67"/>
-      <c r="AR303" s="67" t="s">
-        <v>455</v>
-      </c>
-      <c r="AS303" s="67" t="s">
-        <v>264</v>
-      </c>
-      <c r="AT303" s="67"/>
-      <c r="AU303" s="67"/>
-      <c r="AV303" s="67"/>
-      <c r="AW303" s="67"/>
-      <c r="AX303" s="67"/>
-      <c r="AY303" s="67" t="s">
-        <v>265</v>
-      </c>
-      <c r="AZ303" s="67"/>
-      <c r="BA303" s="67"/>
-      <c r="BB303" s="100" t="s">
-        <v>451</v>
-      </c>
-      <c r="BC303" s="67"/>
-      <c r="BD303" s="67"/>
-      <c r="BE303" s="100" t="s">
-        <v>451</v>
-      </c>
-      <c r="BF303" s="67"/>
-      <c r="BG303" s="70"/>
+      <c r="AK303" s="81" t="s">
+        <v>293</v>
+      </c>
+      <c r="AL303" s="81" t="s">
+        <v>292</v>
+      </c>
+      <c r="AM303" s="112" t="s">
+        <v>64</v>
+      </c>
+      <c r="AN303" s="82" t="s">
+        <v>211</v>
+      </c>
+      <c r="AP303" s="80"/>
+      <c r="AQ303" s="81"/>
+      <c r="AR303" s="114" t="s">
+        <v>468</v>
+      </c>
+      <c r="AS303" s="81" t="s">
+        <v>295</v>
+      </c>
+      <c r="AT303" s="81"/>
+      <c r="AU303" s="81"/>
+      <c r="AV303" s="81"/>
+      <c r="AW303" s="81"/>
+      <c r="AX303" s="81"/>
+      <c r="AY303" s="81" t="s">
+        <v>296</v>
+      </c>
+      <c r="AZ303" s="81"/>
+      <c r="BA303" s="81"/>
+      <c r="BB303" s="81" t="s">
+        <v>290</v>
+      </c>
+      <c r="BC303" s="81"/>
+      <c r="BD303" s="81"/>
+      <c r="BE303" s="81" t="s">
+        <v>290</v>
+      </c>
+      <c r="BF303" s="81"/>
+      <c r="BG303" s="82"/>
     </row>
     <row r="304" spans="1:59" x14ac:dyDescent="0.25">
-      <c r="A304" s="10" t="s">
+      <c r="A304" s="31" t="s">
         <v>61</v>
       </c>
-      <c r="B304" s="109" t="s">
-        <v>290</v>
-      </c>
-      <c r="C304" s="11">
+      <c r="B304" s="108" t="s">
+        <v>297</v>
+      </c>
+      <c r="C304" s="32">
         <v>10</v>
       </c>
-      <c r="D304" s="11">
+      <c r="D304" s="32">
         <v>4120</v>
       </c>
-      <c r="E304" s="11">
+      <c r="E304" s="32">
         <v>1</v>
       </c>
-      <c r="F304" s="11">
+      <c r="F304" s="32">
         <v>128803</v>
       </c>
-      <c r="G304" s="11">
+      <c r="G304" s="32">
         <v>94756</v>
       </c>
-      <c r="H304" s="11" t="s">
+      <c r="H304" s="32" t="s">
         <v>291</v>
       </c>
-      <c r="I304" s="11">
+      <c r="I304" s="32">
         <v>80</v>
       </c>
-      <c r="J304" s="11">
+      <c r="J304" s="32">
         <v>67</v>
       </c>
-      <c r="K304" s="11">
+      <c r="K304" s="32">
         <v>59.1</v>
       </c>
-      <c r="L304" s="11">
+      <c r="L304" s="32">
         <v>57.1</v>
       </c>
-      <c r="M304" s="109" t="s">
-        <v>64</v>
-      </c>
-      <c r="N304" s="109" t="s">
-        <v>64</v>
-      </c>
-      <c r="O304" s="109" t="s">
-        <v>64</v>
-      </c>
-      <c r="P304" s="109" t="s">
-        <v>64</v>
-      </c>
-      <c r="Q304" s="109" t="s">
-        <v>64</v>
-      </c>
-      <c r="R304" s="11">
+      <c r="M304" s="108" t="s">
+        <v>64</v>
+      </c>
+      <c r="N304" s="108" t="s">
+        <v>64</v>
+      </c>
+      <c r="O304" s="108" t="s">
+        <v>64</v>
+      </c>
+      <c r="P304" s="108" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q304" s="108" t="s">
+        <v>64</v>
+      </c>
+      <c r="R304" s="32">
         <v>114000</v>
       </c>
-      <c r="S304" s="11">
+      <c r="S304" s="32">
         <v>80000</v>
       </c>
-      <c r="T304" s="11"/>
-      <c r="U304" s="11"/>
-      <c r="V304" s="11">
+      <c r="T304" s="32"/>
+      <c r="U304" s="32"/>
+      <c r="V304" s="32">
         <v>3.74</v>
       </c>
-      <c r="W304" s="11">
+      <c r="W304" s="32">
         <v>2.5</v>
       </c>
-      <c r="X304" s="109" t="s">
-        <v>64</v>
-      </c>
-      <c r="Y304" s="109" t="s">
-        <v>64</v>
-      </c>
-      <c r="Z304" s="109" t="s">
+      <c r="X304" s="108" t="s">
+        <v>64</v>
+      </c>
+      <c r="Y304" s="108" t="s">
+        <v>64</v>
+      </c>
+      <c r="Z304" s="108" t="s">
         <v>211</v>
       </c>
-      <c r="AA304" s="109" t="s">
+      <c r="AA304" s="108" t="s">
         <v>292</v>
       </c>
-      <c r="AB304" s="109" t="s">
-        <v>77</v>
-      </c>
-      <c r="AC304" s="11">
+      <c r="AB304" s="108" t="s">
+        <v>66</v>
+      </c>
+      <c r="AC304" s="32">
         <v>3.5</v>
       </c>
-      <c r="AD304" s="11">
-        <v>26.5</v>
-      </c>
-      <c r="AE304" s="11">
-        <v>35</v>
-      </c>
-      <c r="AF304" s="75">
+      <c r="AD304" s="32">
+        <v>54</v>
+      </c>
+      <c r="AE304" s="32">
+        <v>70</v>
+      </c>
+      <c r="AF304" s="83">
         <v>1293</v>
       </c>
-      <c r="AH304" s="80">
+      <c r="AH304" s="40">
         <v>10</v>
       </c>
-      <c r="AI304" s="81" t="s">
-        <v>77</v>
-      </c>
-      <c r="AJ304" s="21" t="s">
+      <c r="AI304" s="41" t="s">
+        <v>66</v>
+      </c>
+      <c r="AJ304" s="42" t="s">
         <v>262</v>
       </c>
-      <c r="AK304" s="81" t="s">
+      <c r="AK304" s="41" t="s">
         <v>293</v>
       </c>
-      <c r="AL304" s="81" t="s">
+      <c r="AL304" s="41" t="s">
         <v>292</v>
       </c>
-      <c r="AM304" s="112" t="s">
-        <v>64</v>
-      </c>
-      <c r="AN304" s="82" t="s">
+      <c r="AM304" s="111" t="s">
+        <v>64</v>
+      </c>
+      <c r="AN304" s="44" t="s">
         <v>211</v>
       </c>
-      <c r="AP304" s="80"/>
-      <c r="AQ304" s="81"/>
-      <c r="AR304" s="132" t="s">
-        <v>468</v>
-      </c>
-      <c r="AS304" s="81" t="s">
+      <c r="AP304" s="40"/>
+      <c r="AQ304" s="41"/>
+      <c r="AR304" s="115" t="s">
+        <v>469</v>
+      </c>
+      <c r="AS304" s="41" t="s">
         <v>295</v>
       </c>
-      <c r="AT304" s="81"/>
-      <c r="AU304" s="81"/>
-      <c r="AV304" s="81"/>
-      <c r="AW304" s="81"/>
-      <c r="AX304" s="81"/>
-      <c r="AY304" s="81" t="s">
+      <c r="AT304" s="41"/>
+      <c r="AU304" s="41"/>
+      <c r="AV304" s="41"/>
+      <c r="AW304" s="41"/>
+      <c r="AX304" s="41"/>
+      <c r="AY304" s="41" t="s">
         <v>296</v>
       </c>
-      <c r="AZ304" s="81"/>
-      <c r="BA304" s="81"/>
-      <c r="BB304" s="81" t="s">
-        <v>290</v>
-      </c>
-      <c r="BC304" s="81"/>
-      <c r="BD304" s="81"/>
-      <c r="BE304" s="81" t="s">
-        <v>290</v>
-      </c>
-      <c r="BF304" s="81"/>
-      <c r="BG304" s="82"/>
+      <c r="AZ304" s="41"/>
+      <c r="BA304" s="41"/>
+      <c r="BB304" s="41" t="s">
+        <v>297</v>
+      </c>
+      <c r="BC304" s="41"/>
+      <c r="BD304" s="41"/>
+      <c r="BE304" s="41" t="s">
+        <v>297</v>
+      </c>
+      <c r="BF304" s="41"/>
+      <c r="BG304" s="44"/>
     </row>
     <row r="305" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A305" s="31" t="s">
         <v>61</v>
       </c>
       <c r="B305" s="108" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="C305" s="32">
-        <v>10</v>
+        <v>8.5</v>
       </c>
       <c r="D305" s="32">
-        <v>4120</v>
+        <v>3800</v>
       </c>
       <c r="E305" s="32">
         <v>1</v>
       </c>
       <c r="F305" s="32">
-        <v>128803</v>
+        <v>111575</v>
       </c>
       <c r="G305" s="32">
-        <v>94756</v>
+        <v>84874</v>
       </c>
       <c r="H305" s="32" t="s">
-        <v>291</v>
+        <v>300</v>
       </c>
       <c r="I305" s="32">
         <v>80</v>
@@ -46380,10 +46380,10 @@
         <v>67</v>
       </c>
       <c r="K305" s="32">
-        <v>59.1</v>
+        <v>59.7</v>
       </c>
       <c r="L305" s="32">
-        <v>57.1</v>
+        <v>57.7</v>
       </c>
       <c r="M305" s="108" t="s">
         <v>64</v>
@@ -46401,15 +46401,15 @@
         <v>64</v>
       </c>
       <c r="R305" s="32">
-        <v>114000</v>
+        <v>102000</v>
       </c>
       <c r="S305" s="32">
-        <v>80000</v>
+        <v>72000</v>
       </c>
       <c r="T305" s="32"/>
       <c r="U305" s="32"/>
       <c r="V305" s="32">
-        <v>3.74</v>
+        <v>3.85</v>
       </c>
       <c r="W305" s="32">
         <v>2.5</v>
@@ -46427,25 +46427,25 @@
         <v>292</v>
       </c>
       <c r="AB305" s="108" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="AC305" s="32">
         <v>3.5</v>
       </c>
       <c r="AD305" s="32">
-        <v>54</v>
+        <v>26</v>
       </c>
       <c r="AE305" s="32">
-        <v>70</v>
+        <v>30</v>
       </c>
       <c r="AF305" s="83">
         <v>1293</v>
       </c>
       <c r="AH305" s="40">
-        <v>10</v>
+        <v>8.5</v>
       </c>
       <c r="AI305" s="41" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="AJ305" s="42" t="s">
         <v>262</v>
@@ -46464,8 +46464,8 @@
       </c>
       <c r="AP305" s="40"/>
       <c r="AQ305" s="41"/>
-      <c r="AR305" s="133" t="s">
-        <v>469</v>
+      <c r="AR305" s="115" t="s">
+        <v>470</v>
       </c>
       <c r="AS305" s="41" t="s">
         <v>295</v>
@@ -46481,12 +46481,12 @@
       <c r="AZ305" s="41"/>
       <c r="BA305" s="41"/>
       <c r="BB305" s="41" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="BC305" s="41"/>
       <c r="BD305" s="41"/>
       <c r="BE305" s="41" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="BF305" s="41"/>
       <c r="BG305" s="44"/>
@@ -46496,7 +46496,7 @@
         <v>61</v>
       </c>
       <c r="B306" s="108" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="C306" s="32">
         <v>8.5</v>
@@ -46570,16 +46570,16 @@
         <v>292</v>
       </c>
       <c r="AB306" s="108" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="AC306" s="32">
         <v>3.5</v>
       </c>
       <c r="AD306" s="32">
-        <v>26</v>
+        <v>52.7</v>
       </c>
       <c r="AE306" s="32">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="AF306" s="83">
         <v>1293</v>
@@ -46588,7 +46588,7 @@
         <v>8.5</v>
       </c>
       <c r="AI306" s="41" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="AJ306" s="42" t="s">
         <v>262</v>
@@ -46607,8 +46607,8 @@
       </c>
       <c r="AP306" s="40"/>
       <c r="AQ306" s="41"/>
-      <c r="AR306" s="133" t="s">
-        <v>470</v>
+      <c r="AR306" s="115" t="s">
+        <v>471</v>
       </c>
       <c r="AS306" s="41" t="s">
         <v>295</v>
@@ -46624,12 +46624,12 @@
       <c r="AZ306" s="41"/>
       <c r="BA306" s="41"/>
       <c r="BB306" s="41" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="BC306" s="41"/>
       <c r="BD306" s="41"/>
       <c r="BE306" s="41" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="BF306" s="41"/>
       <c r="BG306" s="44"/>
@@ -46639,25 +46639,25 @@
         <v>61</v>
       </c>
       <c r="B307" s="108" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="C307" s="32">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="D307" s="32">
-        <v>3800</v>
+        <v>3600</v>
       </c>
       <c r="E307" s="32">
         <v>1</v>
       </c>
       <c r="F307" s="32">
-        <v>111575</v>
+        <v>102928</v>
       </c>
       <c r="G307" s="32">
-        <v>84874</v>
+        <v>79341</v>
       </c>
       <c r="H307" s="32" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="I307" s="32">
         <v>80</v>
@@ -46666,10 +46666,10 @@
         <v>67</v>
       </c>
       <c r="K307" s="32">
-        <v>59.7</v>
+        <v>60</v>
       </c>
       <c r="L307" s="32">
-        <v>57.7</v>
+        <v>58</v>
       </c>
       <c r="M307" s="108" t="s">
         <v>64</v>
@@ -46687,10 +46687,10 @@
         <v>64</v>
       </c>
       <c r="R307" s="32">
-        <v>102000</v>
+        <v>90000</v>
       </c>
       <c r="S307" s="32">
-        <v>72000</v>
+        <v>63000</v>
       </c>
       <c r="T307" s="32"/>
       <c r="U307" s="32"/>
@@ -46713,25 +46713,25 @@
         <v>292</v>
       </c>
       <c r="AB307" s="108" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="AC307" s="32">
         <v>3.5</v>
       </c>
       <c r="AD307" s="32">
-        <v>52.7</v>
+        <v>24.8</v>
       </c>
       <c r="AE307" s="32">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="AF307" s="83">
         <v>1293</v>
       </c>
       <c r="AH307" s="40">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="AI307" s="41" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="AJ307" s="42" t="s">
         <v>262</v>
@@ -46750,8 +46750,8 @@
       </c>
       <c r="AP307" s="40"/>
       <c r="AQ307" s="41"/>
-      <c r="AR307" s="133" t="s">
-        <v>471</v>
+      <c r="AR307" s="115" t="s">
+        <v>472</v>
       </c>
       <c r="AS307" s="41" t="s">
         <v>295</v>
@@ -46767,304 +46767,186 @@
       <c r="AZ307" s="41"/>
       <c r="BA307" s="41"/>
       <c r="BB307" s="41" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="BC307" s="41"/>
       <c r="BD307" s="41"/>
       <c r="BE307" s="41" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="BF307" s="41"/>
       <c r="BG307" s="44"/>
     </row>
-    <row r="308" spans="1:59" x14ac:dyDescent="0.25">
-      <c r="A308" s="31" t="s">
+    <row r="308" spans="1:59" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A308" s="90" t="s">
         <v>61</v>
       </c>
-      <c r="B308" s="108" t="s">
-        <v>304</v>
-      </c>
-      <c r="C308" s="32">
+      <c r="B308" s="110" t="s">
+        <v>307</v>
+      </c>
+      <c r="C308" s="89">
         <v>7.5</v>
       </c>
-      <c r="D308" s="32">
+      <c r="D308" s="89">
         <v>3600</v>
       </c>
-      <c r="E308" s="32">
+      <c r="E308" s="89">
         <v>1</v>
       </c>
-      <c r="F308" s="32">
+      <c r="F308" s="89">
         <v>102928</v>
       </c>
-      <c r="G308" s="32">
+      <c r="G308" s="89">
         <v>79341</v>
       </c>
-      <c r="H308" s="32" t="s">
+      <c r="H308" s="89" t="s">
         <v>305</v>
       </c>
-      <c r="I308" s="32">
+      <c r="I308" s="89">
         <v>80</v>
       </c>
-      <c r="J308" s="32">
+      <c r="J308" s="89">
         <v>67</v>
       </c>
-      <c r="K308" s="32">
+      <c r="K308" s="89">
         <v>60</v>
       </c>
-      <c r="L308" s="32">
+      <c r="L308" s="89">
         <v>58</v>
       </c>
-      <c r="M308" s="108" t="s">
-        <v>64</v>
-      </c>
-      <c r="N308" s="108" t="s">
-        <v>64</v>
-      </c>
-      <c r="O308" s="108" t="s">
-        <v>64</v>
-      </c>
-      <c r="P308" s="108" t="s">
-        <v>64</v>
-      </c>
-      <c r="Q308" s="108" t="s">
-        <v>64</v>
-      </c>
-      <c r="R308" s="32">
+      <c r="M308" s="110" t="s">
+        <v>64</v>
+      </c>
+      <c r="N308" s="110" t="s">
+        <v>64</v>
+      </c>
+      <c r="O308" s="110" t="s">
+        <v>64</v>
+      </c>
+      <c r="P308" s="110" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q308" s="110" t="s">
+        <v>64</v>
+      </c>
+      <c r="R308" s="89">
         <v>90000</v>
       </c>
-      <c r="S308" s="32">
+      <c r="S308" s="89">
         <v>63000</v>
       </c>
-      <c r="T308" s="32"/>
-      <c r="U308" s="32"/>
-      <c r="V308" s="32">
+      <c r="T308" s="89"/>
+      <c r="U308" s="89"/>
+      <c r="V308" s="89">
         <v>3.85</v>
       </c>
-      <c r="W308" s="32">
+      <c r="W308" s="89">
         <v>2.5</v>
       </c>
-      <c r="X308" s="108" t="s">
-        <v>64</v>
-      </c>
-      <c r="Y308" s="108" t="s">
-        <v>64</v>
-      </c>
-      <c r="Z308" s="108" t="s">
+      <c r="X308" s="110" t="s">
+        <v>64</v>
+      </c>
+      <c r="Y308" s="110" t="s">
+        <v>64</v>
+      </c>
+      <c r="Z308" s="110" t="s">
         <v>211</v>
       </c>
-      <c r="AA308" s="108" t="s">
+      <c r="AA308" s="110" t="s">
         <v>292</v>
       </c>
-      <c r="AB308" s="108" t="s">
-        <v>77</v>
-      </c>
-      <c r="AC308" s="32">
+      <c r="AB308" s="110" t="s">
+        <v>66</v>
+      </c>
+      <c r="AC308" s="89">
         <v>3.5</v>
       </c>
-      <c r="AD308" s="32">
-        <v>24.8</v>
-      </c>
-      <c r="AE308" s="32">
-        <v>30</v>
-      </c>
-      <c r="AF308" s="83">
+      <c r="AD308" s="89">
+        <v>49.9</v>
+      </c>
+      <c r="AE308" s="89">
+        <v>60</v>
+      </c>
+      <c r="AF308" s="88">
         <v>1293</v>
       </c>
-      <c r="AH308" s="40">
+      <c r="AH308" s="91">
         <v>7.5</v>
       </c>
-      <c r="AI308" s="41" t="s">
-        <v>77</v>
-      </c>
-      <c r="AJ308" s="42" t="s">
+      <c r="AI308" s="92" t="s">
+        <v>66</v>
+      </c>
+      <c r="AJ308" s="93" t="s">
         <v>262</v>
       </c>
-      <c r="AK308" s="41" t="s">
+      <c r="AK308" s="92" t="s">
         <v>293</v>
       </c>
-      <c r="AL308" s="41" t="s">
+      <c r="AL308" s="92" t="s">
         <v>292</v>
       </c>
-      <c r="AM308" s="111" t="s">
-        <v>64</v>
-      </c>
-      <c r="AN308" s="44" t="s">
+      <c r="AM308" s="113" t="s">
+        <v>64</v>
+      </c>
+      <c r="AN308" s="94" t="s">
         <v>211</v>
       </c>
-      <c r="AP308" s="40"/>
-      <c r="AQ308" s="41"/>
-      <c r="AR308" s="133" t="s">
-        <v>472</v>
-      </c>
-      <c r="AS308" s="41" t="s">
+      <c r="AP308" s="91"/>
+      <c r="AQ308" s="92"/>
+      <c r="AR308" s="116" t="s">
+        <v>473</v>
+      </c>
+      <c r="AS308" s="92" t="s">
         <v>295</v>
       </c>
-      <c r="AT308" s="41"/>
-      <c r="AU308" s="41"/>
-      <c r="AV308" s="41"/>
-      <c r="AW308" s="41"/>
-      <c r="AX308" s="41"/>
-      <c r="AY308" s="41" t="s">
+      <c r="AT308" s="92"/>
+      <c r="AU308" s="92"/>
+      <c r="AV308" s="92"/>
+      <c r="AW308" s="92"/>
+      <c r="AX308" s="92"/>
+      <c r="AY308" s="92" t="s">
         <v>296</v>
       </c>
-      <c r="AZ308" s="41"/>
-      <c r="BA308" s="41"/>
-      <c r="BB308" s="41" t="s">
-        <v>304</v>
-      </c>
-      <c r="BC308" s="41"/>
-      <c r="BD308" s="41"/>
-      <c r="BE308" s="41" t="s">
-        <v>304</v>
-      </c>
-      <c r="BF308" s="41"/>
-      <c r="BG308" s="44"/>
-    </row>
-    <row r="309" spans="1:59" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A309" s="90" t="s">
-        <v>61</v>
-      </c>
-      <c r="B309" s="110" t="s">
+      <c r="AZ308" s="92"/>
+      <c r="BA308" s="92"/>
+      <c r="BB308" s="92" t="s">
         <v>307</v>
       </c>
-      <c r="C309" s="89">
-        <v>7.5</v>
-      </c>
-      <c r="D309" s="89">
-        <v>3600</v>
-      </c>
-      <c r="E309" s="89">
-        <v>1</v>
-      </c>
-      <c r="F309" s="89">
-        <v>102928</v>
-      </c>
-      <c r="G309" s="89">
-        <v>79341</v>
-      </c>
-      <c r="H309" s="89" t="s">
-        <v>305</v>
-      </c>
-      <c r="I309" s="89">
-        <v>80</v>
-      </c>
-      <c r="J309" s="89">
-        <v>67</v>
-      </c>
-      <c r="K309" s="89">
-        <v>60</v>
-      </c>
-      <c r="L309" s="89">
-        <v>58</v>
-      </c>
-      <c r="M309" s="110" t="s">
-        <v>64</v>
-      </c>
-      <c r="N309" s="110" t="s">
-        <v>64</v>
-      </c>
-      <c r="O309" s="110" t="s">
-        <v>64</v>
-      </c>
-      <c r="P309" s="110" t="s">
-        <v>64</v>
-      </c>
-      <c r="Q309" s="110" t="s">
-        <v>64</v>
-      </c>
-      <c r="R309" s="89">
-        <v>90000</v>
-      </c>
-      <c r="S309" s="89">
-        <v>63000</v>
-      </c>
-      <c r="T309" s="89"/>
-      <c r="U309" s="89"/>
-      <c r="V309" s="89">
-        <v>3.85</v>
-      </c>
-      <c r="W309" s="89">
-        <v>2.5</v>
-      </c>
-      <c r="X309" s="110" t="s">
-        <v>64</v>
-      </c>
-      <c r="Y309" s="110" t="s">
-        <v>64</v>
-      </c>
-      <c r="Z309" s="110" t="s">
-        <v>211</v>
-      </c>
-      <c r="AA309" s="110" t="s">
-        <v>292</v>
-      </c>
-      <c r="AB309" s="110" t="s">
-        <v>66</v>
-      </c>
-      <c r="AC309" s="89">
-        <v>3.5</v>
-      </c>
-      <c r="AD309" s="89">
-        <v>49.9</v>
-      </c>
-      <c r="AE309" s="89">
-        <v>60</v>
-      </c>
-      <c r="AF309" s="88">
-        <v>1293</v>
-      </c>
-      <c r="AH309" s="91">
-        <v>7.5</v>
-      </c>
-      <c r="AI309" s="92" t="s">
-        <v>66</v>
-      </c>
-      <c r="AJ309" s="93" t="s">
-        <v>262</v>
-      </c>
-      <c r="AK309" s="92" t="s">
-        <v>293</v>
-      </c>
-      <c r="AL309" s="92" t="s">
-        <v>292</v>
-      </c>
-      <c r="AM309" s="113" t="s">
-        <v>64</v>
-      </c>
-      <c r="AN309" s="94" t="s">
-        <v>211</v>
-      </c>
-      <c r="AP309" s="91"/>
-      <c r="AQ309" s="92"/>
-      <c r="AR309" s="134" t="s">
-        <v>473</v>
-      </c>
-      <c r="AS309" s="92" t="s">
-        <v>295</v>
-      </c>
-      <c r="AT309" s="92"/>
-      <c r="AU309" s="92"/>
-      <c r="AV309" s="92"/>
-      <c r="AW309" s="92"/>
-      <c r="AX309" s="92"/>
-      <c r="AY309" s="92" t="s">
-        <v>296</v>
-      </c>
-      <c r="AZ309" s="92"/>
-      <c r="BA309" s="92"/>
-      <c r="BB309" s="92" t="s">
+      <c r="BC308" s="92"/>
+      <c r="BD308" s="92"/>
+      <c r="BE308" s="92" t="s">
         <v>307</v>
       </c>
-      <c r="BC309" s="92"/>
-      <c r="BD309" s="92"/>
-      <c r="BE309" s="92" t="s">
-        <v>307</v>
-      </c>
-      <c r="BF309" s="92"/>
-      <c r="BG309" s="94"/>
+      <c r="BF308" s="92"/>
+      <c r="BG308" s="94"/>
     </row>
   </sheetData>
   <mergeCells count="41">
+    <mergeCell ref="BF2:BF4"/>
+    <mergeCell ref="AB3:AE3"/>
+    <mergeCell ref="F3:L3"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="AI2:AI4"/>
+    <mergeCell ref="AA3:AA4"/>
+    <mergeCell ref="AS2:AS4"/>
+    <mergeCell ref="AU2:AU4"/>
+    <mergeCell ref="BE2:BE4"/>
+    <mergeCell ref="AN2:AN4"/>
+    <mergeCell ref="AX2:AX4"/>
+    <mergeCell ref="AF3:AF4"/>
+    <mergeCell ref="AZ2:AZ4"/>
+    <mergeCell ref="AW2:AW4"/>
+    <mergeCell ref="R3:W3"/>
+    <mergeCell ref="BC2:BC4"/>
+    <mergeCell ref="AL2:AL4"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="AK2:AK4"/>
+    <mergeCell ref="AM2:AM4"/>
+    <mergeCell ref="A2:AF2"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="M3:Q3"/>
+    <mergeCell ref="X3:Y3"/>
     <mergeCell ref="AP1:BG1"/>
     <mergeCell ref="BA2:BA4"/>
     <mergeCell ref="BG2:BG4"/>
@@ -47081,31 +46963,6 @@
     <mergeCell ref="AQ2:AQ4"/>
     <mergeCell ref="AY2:AY4"/>
     <mergeCell ref="A1:AF1"/>
-    <mergeCell ref="AL2:AL4"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="AK2:AK4"/>
-    <mergeCell ref="AM2:AM4"/>
-    <mergeCell ref="A2:AF2"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="M3:Q3"/>
-    <mergeCell ref="X3:Y3"/>
-    <mergeCell ref="BF2:BF4"/>
-    <mergeCell ref="AB3:AE3"/>
-    <mergeCell ref="F3:L3"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="AI2:AI4"/>
-    <mergeCell ref="AA3:AA4"/>
-    <mergeCell ref="AS2:AS4"/>
-    <mergeCell ref="AU2:AU4"/>
-    <mergeCell ref="BE2:BE4"/>
-    <mergeCell ref="AN2:AN4"/>
-    <mergeCell ref="AX2:AX4"/>
-    <mergeCell ref="AF3:AF4"/>
-    <mergeCell ref="AZ2:AZ4"/>
-    <mergeCell ref="AW2:AW4"/>
-    <mergeCell ref="R3:W3"/>
-    <mergeCell ref="BC2:BC4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/DATA/DATA FILES/LC RTU DATA.xlsx
+++ b/DATA/DATA FILES/LC RTU DATA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ProgramData\HHpro\DATA\DATA FILES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81EA80DC-E917-4FAB-8A2E-489E0CA4BB83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{790421D8-524D-4243-9181-F5308DCBD504}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1088,371 +1088,378 @@
     <t>14.35 IEER/10.6 EER</t>
   </si>
   <si>
+    <t>DSH2403</t>
+  </si>
+  <si>
+    <t>20-Ton - SE - 208/3 - 75kW</t>
+  </si>
+  <si>
+    <t>20-Ton - SE - 208/3 - 60kW</t>
+  </si>
+  <si>
+    <t>20-Ton - SE - 208/3 - 45kW</t>
+  </si>
+  <si>
+    <t>20-Ton - SE - 208/3 - 30kW</t>
+  </si>
+  <si>
+    <t>20-Ton - SE - 208/3 - 0kW</t>
+  </si>
+  <si>
+    <t>15.0-Ton - SE - 460/3 - 0kW</t>
+  </si>
+  <si>
+    <t>DSH1803</t>
+  </si>
+  <si>
+    <t>15.0-Ton - SE - 208/3 - 60kW</t>
+  </si>
+  <si>
+    <t>15.0-Ton - SE - 208/3 - 45kW</t>
+  </si>
+  <si>
+    <t>15.0-Ton - SE - 208/3 - 30kW</t>
+  </si>
+  <si>
+    <t>15.0-Ton - SE - 208/3 - 0kW</t>
+  </si>
+  <si>
+    <t>12.5-Ton - SE - 460/3 - 30kW</t>
+  </si>
+  <si>
+    <t>12.5-Ton - SE - 460/3 - 0kW</t>
+  </si>
+  <si>
+    <t>DSH1503</t>
+  </si>
+  <si>
+    <t>12.5-Ton - SE - 208/3 - 60kW</t>
+  </si>
+  <si>
+    <t>DSH1204</t>
+  </si>
+  <si>
+    <t>10-Ton - SE - 460/3 - 30kW</t>
+  </si>
+  <si>
+    <t>12.5-Ton - SE - 208/3 - 45kW</t>
+  </si>
+  <si>
+    <t>12.5-Ton - SE - 208/3 - 30kW</t>
+  </si>
+  <si>
+    <t>12.5-Ton - SE - 208/3 - 15kW</t>
+  </si>
+  <si>
+    <t>12.5-Ton - SE - 208/3 - 0kW</t>
+  </si>
+  <si>
+    <t>10-Ton - SE - 460/3 - 45kW</t>
+  </si>
+  <si>
+    <t>DSH1023</t>
+  </si>
+  <si>
+    <t>8.5-Ton - SE - 208/3 - 0kW</t>
+  </si>
+  <si>
+    <t>DSH1203</t>
+  </si>
+  <si>
+    <t>10-Ton - SE - 208/3 - 45kW</t>
+  </si>
+  <si>
+    <t>10-Ton - SE - 208/3 - 30kW</t>
+  </si>
+  <si>
+    <t>10-Ton - SE - 460/3 - 15kW</t>
+  </si>
+  <si>
+    <t>10-Ton - SE - 460/3 - 0kW</t>
+  </si>
+  <si>
+    <t>10-Ton - SE - 208/3 - 15kW</t>
+  </si>
+  <si>
+    <t>10-Ton - SE - 208/3 - 0kW</t>
+  </si>
+  <si>
+    <t>DSH1024</t>
+  </si>
+  <si>
+    <t>8.5-Ton - SE - 460/3 - 45kW</t>
+  </si>
+  <si>
+    <t>8.5-Ton - SE - 460/3 - 30kW</t>
+  </si>
+  <si>
+    <t>8.5-Ton - SE - 460/3 - 15kW</t>
+  </si>
+  <si>
+    <t>8.5-Ton - SE - 460/3 - 0kW</t>
+  </si>
+  <si>
+    <t>8.5-Ton - SE - 208/3 - 45kW</t>
+  </si>
+  <si>
+    <t>8.5-Ton - SE - 208/3 - 30kW</t>
+  </si>
+  <si>
+    <t>8.5-Ton - SE - 208/3 - 15kW</t>
+  </si>
+  <si>
+    <t>DSH0904</t>
+  </si>
+  <si>
+    <t>16 IEER/11.4 EER</t>
+  </si>
+  <si>
+    <t>7.5-Ton - SE - 460/3 - 45kW</t>
+  </si>
+  <si>
+    <t>7.5-Ton - SE - 460/3 - 30kW</t>
+  </si>
+  <si>
+    <t>7.5-Ton - SE - 460/3 - 15kW</t>
+  </si>
+  <si>
+    <t>7.5-Ton - SE - 460/3 - 0kW</t>
+  </si>
+  <si>
+    <t>DSH0903</t>
+  </si>
+  <si>
+    <t>7.5-Ton - SE - 208/3 - 45kW</t>
+  </si>
+  <si>
+    <t>7.5-Ton - SE - 208/3 - 30kW</t>
+  </si>
+  <si>
+    <t>7.5-Ton - SE - 208/3 - 15kW</t>
+  </si>
+  <si>
+    <t>7.5-Ton - SE - 208/3 - 0kW</t>
+  </si>
+  <si>
+    <t>DSH0723</t>
+  </si>
+  <si>
+    <t>6-Ton - SE - 208/3 - 5kW</t>
+  </si>
+  <si>
+    <t>6-Ton - SE - 460/3 - 30kW</t>
+  </si>
+  <si>
+    <t>6-Ton - SE - 460/3 - 15kW</t>
+  </si>
+  <si>
+    <t>6-Ton - SE - 460/3 - 10kW</t>
+  </si>
+  <si>
+    <t>6-Ton - SE - 460/3 - 0kW</t>
+  </si>
+  <si>
+    <t>6-Ton - SE - 208/3 - 30kW</t>
+  </si>
+  <si>
+    <t>6-Ton - SE - 208/3 - 20kW</t>
+  </si>
+  <si>
+    <t>6-Ton - SE - 208/3 - 15kW</t>
+  </si>
+  <si>
+    <t>6-Ton - SE - 208/3 - 10kW</t>
+  </si>
+  <si>
+    <t>6-Ton - SE - 208/3 - 0kW</t>
+  </si>
+  <si>
+    <t>DSH0604</t>
+  </si>
+  <si>
+    <t>13.70 SEER2/11.80 EER2</t>
+  </si>
+  <si>
+    <t>5-Ton - SE - 460/3 - 15kW</t>
+  </si>
+  <si>
+    <t>5-Ton - SE - 460/3 - 10kW</t>
+  </si>
+  <si>
+    <t>5-Ton - SE - 460/3 - 5kW</t>
+  </si>
+  <si>
+    <t>5-Ton - SE - 460/3 - 0kW</t>
+  </si>
+  <si>
+    <t>DSH0603</t>
+  </si>
+  <si>
+    <t>5-Ton - SE - 208/3 - 20kW</t>
+  </si>
+  <si>
+    <t>5-Ton - SE - 208/3 - 15kW</t>
+  </si>
+  <si>
+    <t>5-Ton - SE - 208/3 - 5kW</t>
+  </si>
+  <si>
+    <t>5-Ton - SE - 208/3 - 0kW</t>
+  </si>
+  <si>
+    <t>DSH0484</t>
+  </si>
+  <si>
+    <t>4-Ton - SE - 460/3 - 20kW</t>
+  </si>
+  <si>
+    <t>4-Ton - SE - 460/3 - 15kW</t>
+  </si>
+  <si>
+    <t>4-Ton - SE - 460/3 - 10kW</t>
+  </si>
+  <si>
+    <t>4-Ton - SE - 460/3 - 5kW</t>
+  </si>
+  <si>
+    <t>4-Ton - SE - 460/3 - 0kW</t>
+  </si>
+  <si>
+    <t>DSH0483</t>
+  </si>
+  <si>
+    <t>4-Ton - SE - 208/3 - 20kW</t>
+  </si>
+  <si>
+    <t>4-Ton - SE - 208/3 - 15kW</t>
+  </si>
+  <si>
+    <t>4-Ton - SE - 208/3 - 10kW</t>
+  </si>
+  <si>
+    <t>4-Ton - SE - 208/3 - 5kW</t>
+  </si>
+  <si>
+    <t>4-Ton - SE - 208/3 - 0kW</t>
+  </si>
+  <si>
+    <t>DSH0364</t>
+  </si>
+  <si>
+    <t>14.0 SEER2/12.00 EER2</t>
+  </si>
+  <si>
+    <t>3-Ton - SE - 460/3 - 15kW</t>
+  </si>
+  <si>
+    <t>3-Ton - SE - 460/3 - 10kW</t>
+  </si>
+  <si>
+    <t>3-Ton - SE - 460/3 - 5kW</t>
+  </si>
+  <si>
+    <t>3-Ton - SE - 460/3 - 0kW</t>
+  </si>
+  <si>
+    <t>DSH0363</t>
+  </si>
+  <si>
+    <t>3-Ton - SE - 208/3 - 15kW</t>
+  </si>
+  <si>
+    <t>3-Ton - SE - 208/3 - 10kW</t>
+  </si>
+  <si>
+    <t>3-Ton - SE - 208/3 - 5kW</t>
+  </si>
+  <si>
+    <t>3-Ton - SE - 208/3 - 0kW</t>
+  </si>
+  <si>
+    <t>Provide with economizer with enthalpy sensor</t>
+  </si>
+  <si>
+    <t>Provide with factory installed disconnect</t>
+  </si>
+  <si>
+    <t>Provide with factory installed, field powered 115V GFCI outlet</t>
+  </si>
+  <si>
+    <t>Provide with 7-day programmable thermostat</t>
+  </si>
+  <si>
+    <t>Provide with 7-day programmable BACnet thermostat</t>
+  </si>
+  <si>
+    <t>Provide with factory installed DDC controller with BAS input and 7-day programmable thermostat</t>
+  </si>
+  <si>
+    <t>Provide with 24" factory roofcurb</t>
+  </si>
+  <si>
+    <t>Model Number</t>
+  </si>
+  <si>
+    <t>Make</t>
+  </si>
+  <si>
+    <t>BTU/h (70°F Indoor DB)</t>
+  </si>
+  <si>
+    <t>Temperature Rise (°F)</t>
+  </si>
+  <si>
+    <t>kW</t>
+  </si>
+  <si>
+    <t>10-Ton - MZVAV - HGRH - 460-3 - 0kW</t>
+  </si>
+  <si>
+    <t>10-Ton - MZVAV - HGRH - 208-3 - 0kW</t>
+  </si>
+  <si>
+    <t>8.5-Ton - MZVAV - HGRH - 460-3 - 0kW</t>
+  </si>
+  <si>
+    <t>8.5-Ton - MZVAV - HGRH - 208-3 - 0kW</t>
+  </si>
+  <si>
+    <t>7.5-Ton - MZVAV - HGRH - 460-3 - 0kW</t>
+  </si>
+  <si>
+    <t>7.5-Ton - MZVAV - HGRH - 208-3 - 0kW</t>
+  </si>
+  <si>
+    <t>20-Ton - SE - 460/3 - 60kW</t>
+  </si>
+  <si>
     <t>20-Ton - SE - 460/3 - 0kW</t>
   </si>
   <si>
-    <t>20-Ton - SE - 460/3 - 60kW</t>
+    <t>20-Ton - SE - 460/3 - 45kW</t>
   </si>
   <si>
     <t>20-Ton - SE - 460/3 - 75kW</t>
   </si>
   <si>
-    <t>20-Ton - SE - 460/3 - 45kW</t>
-  </si>
-  <si>
     <t>20-Ton - SE - 460/3 - 30kW</t>
-  </si>
-  <si>
-    <t>DSH2403</t>
-  </si>
-  <si>
-    <t>20-Ton - SE - 208/3 - 75kW</t>
-  </si>
-  <si>
-    <t>20-Ton - SE - 208/3 - 60kW</t>
-  </si>
-  <si>
-    <t>20-Ton - SE - 208/3 - 45kW</t>
-  </si>
-  <si>
-    <t>20-Ton - SE - 208/3 - 30kW</t>
-  </si>
-  <si>
-    <t>20-Ton - SE - 208/3 - 0kW</t>
-  </si>
-  <si>
-    <t>15.0-Ton - SE - 460/3 - 0kW</t>
-  </si>
-  <si>
-    <t>DSH1803</t>
-  </si>
-  <si>
-    <t>15.0-Ton - SE - 208/3 - 60kW</t>
-  </si>
-  <si>
-    <t>15.0-Ton - SE - 208/3 - 45kW</t>
-  </si>
-  <si>
-    <t>15.0-Ton - SE - 208/3 - 30kW</t>
-  </si>
-  <si>
-    <t>15.0-Ton - SE - 208/3 - 0kW</t>
-  </si>
-  <si>
-    <t>12.5-Ton - SE - 460/3 - 30kW</t>
-  </si>
-  <si>
-    <t>12.5-Ton - SE - 460/3 - 0kW</t>
-  </si>
-  <si>
-    <t>DSH1503</t>
-  </si>
-  <si>
-    <t>12.5-Ton - SE - 208/3 - 60kW</t>
-  </si>
-  <si>
-    <t>DSH1204</t>
-  </si>
-  <si>
-    <t>10-Ton - SE - 460/3 - 30kW</t>
-  </si>
-  <si>
-    <t>12.5-Ton - SE - 208/3 - 45kW</t>
-  </si>
-  <si>
-    <t>12.5-Ton - SE - 208/3 - 30kW</t>
-  </si>
-  <si>
-    <t>12.5-Ton - SE - 208/3 - 15kW</t>
-  </si>
-  <si>
-    <t>12.5-Ton - SE - 208/3 - 0kW</t>
-  </si>
-  <si>
-    <t>10-Ton - SE - 460/3 - 45kW</t>
-  </si>
-  <si>
-    <t>DSH1023</t>
-  </si>
-  <si>
-    <t>8.5-Ton - SE - 208/3 - 0kW</t>
-  </si>
-  <si>
-    <t>DSH1203</t>
-  </si>
-  <si>
-    <t>10-Ton - SE - 208/3 - 45kW</t>
-  </si>
-  <si>
-    <t>10-Ton - SE - 208/3 - 30kW</t>
-  </si>
-  <si>
-    <t>10-Ton - SE - 460/3 - 15kW</t>
-  </si>
-  <si>
-    <t>10-Ton - SE - 460/3 - 0kW</t>
-  </si>
-  <si>
-    <t>10-Ton - SE - 208/3 - 15kW</t>
-  </si>
-  <si>
-    <t>10-Ton - SE - 208/3 - 0kW</t>
-  </si>
-  <si>
-    <t>DSH1024</t>
-  </si>
-  <si>
-    <t>8.5-Ton - SE - 460/3 - 45kW</t>
-  </si>
-  <si>
-    <t>8.5-Ton - SE - 460/3 - 30kW</t>
-  </si>
-  <si>
-    <t>8.5-Ton - SE - 460/3 - 15kW</t>
-  </si>
-  <si>
-    <t>8.5-Ton - SE - 460/3 - 0kW</t>
-  </si>
-  <si>
-    <t>8.5-Ton - SE - 208/3 - 45kW</t>
-  </si>
-  <si>
-    <t>8.5-Ton - SE - 208/3 - 30kW</t>
-  </si>
-  <si>
-    <t>8.5-Ton - SE - 208/3 - 15kW</t>
-  </si>
-  <si>
-    <t>DSH0904</t>
-  </si>
-  <si>
-    <t>16 IEER/11.4 EER</t>
-  </si>
-  <si>
-    <t>7.5-Ton - SE - 460/3 - 45kW</t>
-  </si>
-  <si>
-    <t>7.5-Ton - SE - 460/3 - 30kW</t>
-  </si>
-  <si>
-    <t>7.5-Ton - SE - 460/3 - 15kW</t>
-  </si>
-  <si>
-    <t>7.5-Ton - SE - 460/3 - 0kW</t>
-  </si>
-  <si>
-    <t>DSH0903</t>
-  </si>
-  <si>
-    <t>7.5-Ton - SE - 208/3 - 45kW</t>
-  </si>
-  <si>
-    <t>7.5-Ton - SE - 208/3 - 30kW</t>
-  </si>
-  <si>
-    <t>7.5-Ton - SE - 208/3 - 15kW</t>
-  </si>
-  <si>
-    <t>7.5-Ton - SE - 208/3 - 0kW</t>
-  </si>
-  <si>
-    <t>DSH0723</t>
-  </si>
-  <si>
-    <t>6-Ton - SE - 208/3 - 5kW</t>
-  </si>
-  <si>
-    <t>6-Ton - SE - 460/3 - 30kW</t>
-  </si>
-  <si>
-    <t>6-Ton - SE - 460/3 - 15kW</t>
-  </si>
-  <si>
-    <t>6-Ton - SE - 460/3 - 10kW</t>
-  </si>
-  <si>
-    <t>6-Ton - SE - 460/3 - 0kW</t>
-  </si>
-  <si>
-    <t>6-Ton - SE - 208/3 - 30kW</t>
-  </si>
-  <si>
-    <t>6-Ton - SE - 208/3 - 20kW</t>
-  </si>
-  <si>
-    <t>6-Ton - SE - 208/3 - 15kW</t>
-  </si>
-  <si>
-    <t>6-Ton - SE - 208/3 - 10kW</t>
-  </si>
-  <si>
-    <t>6-Ton - SE - 208/3 - 0kW</t>
-  </si>
-  <si>
-    <t>DSH0604</t>
-  </si>
-  <si>
-    <t>13.70 SEER2/11.80 EER2</t>
-  </si>
-  <si>
-    <t>5-Ton - SE - 460/3 - 15kW</t>
-  </si>
-  <si>
-    <t>5-Ton - SE - 460/3 - 10kW</t>
-  </si>
-  <si>
-    <t>5-Ton - SE - 460/3 - 5kW</t>
-  </si>
-  <si>
-    <t>5-Ton - SE - 460/3 - 0kW</t>
-  </si>
-  <si>
-    <t>DSH0603</t>
-  </si>
-  <si>
-    <t>5-Ton - SE - 208/3 - 20kW</t>
-  </si>
-  <si>
-    <t>5-Ton - SE - 208/3 - 15kW</t>
-  </si>
-  <si>
-    <t>5-Ton - SE - 208/3 - 5kW</t>
-  </si>
-  <si>
-    <t>5-Ton - SE - 208/3 - 0kW</t>
-  </si>
-  <si>
-    <t>DSH0484</t>
-  </si>
-  <si>
-    <t>4-Ton - SE - 460/3 - 20kW</t>
-  </si>
-  <si>
-    <t>4-Ton - SE - 460/3 - 15kW</t>
-  </si>
-  <si>
-    <t>4-Ton - SE - 460/3 - 10kW</t>
-  </si>
-  <si>
-    <t>4-Ton - SE - 460/3 - 5kW</t>
-  </si>
-  <si>
-    <t>4-Ton - SE - 460/3 - 0kW</t>
-  </si>
-  <si>
-    <t>DSH0483</t>
-  </si>
-  <si>
-    <t>4-Ton - SE - 208/3 - 20kW</t>
-  </si>
-  <si>
-    <t>4-Ton - SE - 208/3 - 15kW</t>
-  </si>
-  <si>
-    <t>4-Ton - SE - 208/3 - 10kW</t>
-  </si>
-  <si>
-    <t>4-Ton - SE - 208/3 - 5kW</t>
-  </si>
-  <si>
-    <t>4-Ton - SE - 208/3 - 0kW</t>
-  </si>
-  <si>
-    <t>DSH0364</t>
-  </si>
-  <si>
-    <t>14.0 SEER2/12.00 EER2</t>
-  </si>
-  <si>
-    <t>3-Ton - SE - 460/3 - 15kW</t>
-  </si>
-  <si>
-    <t>3-Ton - SE - 460/3 - 10kW</t>
-  </si>
-  <si>
-    <t>3-Ton - SE - 460/3 - 5kW</t>
-  </si>
-  <si>
-    <t>3-Ton - SE - 460/3 - 0kW</t>
-  </si>
-  <si>
-    <t>DSH0363</t>
-  </si>
-  <si>
-    <t>3-Ton - SE - 208/3 - 15kW</t>
-  </si>
-  <si>
-    <t>3-Ton - SE - 208/3 - 10kW</t>
-  </si>
-  <si>
-    <t>3-Ton - SE - 208/3 - 5kW</t>
-  </si>
-  <si>
-    <t>3-Ton - SE - 208/3 - 0kW</t>
-  </si>
-  <si>
-    <t>Provide with economizer with enthalpy sensor</t>
-  </si>
-  <si>
-    <t>Provide with factory installed disconnect</t>
-  </si>
-  <si>
-    <t>Provide with factory installed, field powered 115V GFCI outlet</t>
-  </si>
-  <si>
-    <t>Provide with 7-day programmable thermostat</t>
-  </si>
-  <si>
-    <t>Provide with 7-day programmable BACnet thermostat</t>
-  </si>
-  <si>
-    <t>Provide with factory installed DDC controller with BAS input and 7-day programmable thermostat</t>
-  </si>
-  <si>
-    <t>Provide with 24" factory roofcurb</t>
-  </si>
-  <si>
-    <t>Model Number</t>
-  </si>
-  <si>
-    <t>Make</t>
-  </si>
-  <si>
-    <t>BTU/h (70°F Indoor DB)</t>
-  </si>
-  <si>
-    <t>Temperature Rise (°F)</t>
-  </si>
-  <si>
-    <t>kW</t>
-  </si>
-  <si>
-    <t>10-Ton - MZVAV - HGRH - 460-3 - 0kW</t>
-  </si>
-  <si>
-    <t>10-Ton - MZVAV - HGRH - 208-3 - 0kW</t>
-  </si>
-  <si>
-    <t>8.5-Ton - MZVAV - HGRH - 460-3 - 0kW</t>
-  </si>
-  <si>
-    <t>8.5-Ton - MZVAV - HGRH - 208-3 - 0kW</t>
-  </si>
-  <si>
-    <t>7.5-Ton - MZVAV - HGRH - 460-3 - 0kW</t>
-  </si>
-  <si>
-    <t>7.5-Ton - MZVAV - HGRH - 208-3 - 0kW</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -2126,147 +2133,147 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="135">
+  <cellXfs count="138">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="13" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="13" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="13" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="13" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="12" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="12" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="12" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="12" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2305,13 +2312,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2323,199 +2330,208 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="12" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="13" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="3" fontId="12" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="12" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="13" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="12" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="13" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -2905,272 +2921,272 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:59" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="117" t="s">
+      <c r="A1" s="120" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="118"/>
-      <c r="C1" s="118"/>
-      <c r="D1" s="118"/>
-      <c r="E1" s="118"/>
-      <c r="F1" s="118"/>
-      <c r="G1" s="118"/>
-      <c r="H1" s="118"/>
-      <c r="I1" s="118"/>
-      <c r="J1" s="118"/>
-      <c r="K1" s="118"/>
-      <c r="L1" s="118"/>
-      <c r="M1" s="118"/>
-      <c r="N1" s="118"/>
-      <c r="O1" s="118"/>
-      <c r="P1" s="118"/>
-      <c r="Q1" s="118"/>
-      <c r="R1" s="118"/>
-      <c r="S1" s="118"/>
-      <c r="T1" s="118"/>
-      <c r="U1" s="118"/>
-      <c r="V1" s="118"/>
-      <c r="W1" s="118"/>
-      <c r="X1" s="118"/>
-      <c r="Y1" s="118"/>
-      <c r="Z1" s="118"/>
-      <c r="AA1" s="118"/>
-      <c r="AB1" s="118"/>
-      <c r="AC1" s="118"/>
-      <c r="AD1" s="118"/>
-      <c r="AE1" s="118"/>
-      <c r="AF1" s="119"/>
-      <c r="AH1" s="124" t="s">
+      <c r="B1" s="121"/>
+      <c r="C1" s="121"/>
+      <c r="D1" s="121"/>
+      <c r="E1" s="121"/>
+      <c r="F1" s="121"/>
+      <c r="G1" s="121"/>
+      <c r="H1" s="121"/>
+      <c r="I1" s="121"/>
+      <c r="J1" s="121"/>
+      <c r="K1" s="121"/>
+      <c r="L1" s="121"/>
+      <c r="M1" s="121"/>
+      <c r="N1" s="121"/>
+      <c r="O1" s="121"/>
+      <c r="P1" s="121"/>
+      <c r="Q1" s="121"/>
+      <c r="R1" s="121"/>
+      <c r="S1" s="121"/>
+      <c r="T1" s="121"/>
+      <c r="U1" s="121"/>
+      <c r="V1" s="121"/>
+      <c r="W1" s="121"/>
+      <c r="X1" s="121"/>
+      <c r="Y1" s="121"/>
+      <c r="Z1" s="121"/>
+      <c r="AA1" s="121"/>
+      <c r="AB1" s="121"/>
+      <c r="AC1" s="121"/>
+      <c r="AD1" s="121"/>
+      <c r="AE1" s="121"/>
+      <c r="AF1" s="122"/>
+      <c r="AH1" s="127" t="s">
         <v>1</v>
       </c>
-      <c r="AI1" s="118"/>
-      <c r="AJ1" s="118"/>
-      <c r="AK1" s="118"/>
-      <c r="AL1" s="118"/>
-      <c r="AM1" s="118"/>
-      <c r="AN1" s="119"/>
+      <c r="AI1" s="121"/>
+      <c r="AJ1" s="121"/>
+      <c r="AK1" s="121"/>
+      <c r="AL1" s="121"/>
+      <c r="AM1" s="121"/>
+      <c r="AN1" s="122"/>
       <c r="AO1" s="3"/>
-      <c r="AP1" s="117" t="s">
-        <v>2</v>
-      </c>
-      <c r="AQ1" s="118"/>
-      <c r="AR1" s="118"/>
-      <c r="AS1" s="118"/>
-      <c r="AT1" s="118"/>
-      <c r="AU1" s="118"/>
-      <c r="AV1" s="118"/>
-      <c r="AW1" s="118"/>
-      <c r="AX1" s="118"/>
-      <c r="AY1" s="118"/>
-      <c r="AZ1" s="118"/>
-      <c r="BA1" s="118"/>
-      <c r="BB1" s="118"/>
-      <c r="BC1" s="118"/>
-      <c r="BD1" s="118"/>
-      <c r="BE1" s="118"/>
-      <c r="BF1" s="118"/>
-      <c r="BG1" s="119"/>
+      <c r="AP1" s="120" t="s">
+        <v>2</v>
+      </c>
+      <c r="AQ1" s="121"/>
+      <c r="AR1" s="121"/>
+      <c r="AS1" s="121"/>
+      <c r="AT1" s="121"/>
+      <c r="AU1" s="121"/>
+      <c r="AV1" s="121"/>
+      <c r="AW1" s="121"/>
+      <c r="AX1" s="121"/>
+      <c r="AY1" s="121"/>
+      <c r="AZ1" s="121"/>
+      <c r="BA1" s="121"/>
+      <c r="BB1" s="121"/>
+      <c r="BC1" s="121"/>
+      <c r="BD1" s="121"/>
+      <c r="BE1" s="121"/>
+      <c r="BF1" s="121"/>
+      <c r="BG1" s="122"/>
     </row>
     <row r="2" spans="1:59" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="126" t="s">
+      <c r="A2" s="129" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="118"/>
-      <c r="C2" s="118"/>
-      <c r="D2" s="118"/>
-      <c r="E2" s="118"/>
-      <c r="F2" s="118"/>
-      <c r="G2" s="118"/>
-      <c r="H2" s="118"/>
-      <c r="I2" s="118"/>
-      <c r="J2" s="118"/>
-      <c r="K2" s="118"/>
-      <c r="L2" s="118"/>
-      <c r="M2" s="118"/>
-      <c r="N2" s="118"/>
-      <c r="O2" s="118"/>
-      <c r="P2" s="118"/>
-      <c r="Q2" s="118"/>
-      <c r="R2" s="118"/>
-      <c r="S2" s="118"/>
-      <c r="T2" s="118"/>
-      <c r="U2" s="118"/>
-      <c r="V2" s="118"/>
-      <c r="W2" s="118"/>
-      <c r="X2" s="118"/>
-      <c r="Y2" s="118"/>
-      <c r="Z2" s="118"/>
-      <c r="AA2" s="118"/>
-      <c r="AB2" s="118"/>
-      <c r="AC2" s="118"/>
-      <c r="AD2" s="118"/>
-      <c r="AE2" s="118"/>
-      <c r="AF2" s="119"/>
-      <c r="AH2" s="124" t="s">
+      <c r="B2" s="121"/>
+      <c r="C2" s="121"/>
+      <c r="D2" s="121"/>
+      <c r="E2" s="121"/>
+      <c r="F2" s="121"/>
+      <c r="G2" s="121"/>
+      <c r="H2" s="121"/>
+      <c r="I2" s="121"/>
+      <c r="J2" s="121"/>
+      <c r="K2" s="121"/>
+      <c r="L2" s="121"/>
+      <c r="M2" s="121"/>
+      <c r="N2" s="121"/>
+      <c r="O2" s="121"/>
+      <c r="P2" s="121"/>
+      <c r="Q2" s="121"/>
+      <c r="R2" s="121"/>
+      <c r="S2" s="121"/>
+      <c r="T2" s="121"/>
+      <c r="U2" s="121"/>
+      <c r="V2" s="121"/>
+      <c r="W2" s="121"/>
+      <c r="X2" s="121"/>
+      <c r="Y2" s="121"/>
+      <c r="Z2" s="121"/>
+      <c r="AA2" s="121"/>
+      <c r="AB2" s="121"/>
+      <c r="AC2" s="121"/>
+      <c r="AD2" s="121"/>
+      <c r="AE2" s="121"/>
+      <c r="AF2" s="122"/>
+      <c r="AH2" s="127" t="s">
         <v>4</v>
       </c>
-      <c r="AI2" s="124" t="s">
+      <c r="AI2" s="127" t="s">
         <v>5</v>
       </c>
-      <c r="AJ2" s="124" t="s">
+      <c r="AJ2" s="127" t="s">
         <v>6</v>
       </c>
-      <c r="AK2" s="124" t="s">
+      <c r="AK2" s="127" t="s">
         <v>7</v>
       </c>
-      <c r="AL2" s="124" t="s">
+      <c r="AL2" s="127" t="s">
         <v>8</v>
       </c>
-      <c r="AM2" s="124" t="s">
+      <c r="AM2" s="127" t="s">
         <v>9</v>
       </c>
-      <c r="AN2" s="124" t="s">
+      <c r="AN2" s="127" t="s">
         <v>10</v>
       </c>
       <c r="AO2" s="3"/>
-      <c r="AP2" s="120" t="s">
+      <c r="AP2" s="123" t="s">
         <v>11</v>
       </c>
-      <c r="AQ2" s="120" t="s">
+      <c r="AQ2" s="123" t="s">
         <v>12</v>
       </c>
-      <c r="AR2" s="120" t="s">
+      <c r="AR2" s="123" t="s">
         <v>13</v>
       </c>
-      <c r="AS2" s="120" t="s">
+      <c r="AS2" s="123" t="s">
         <v>14</v>
       </c>
-      <c r="AT2" s="120" t="s">
+      <c r="AT2" s="123" t="s">
         <v>15</v>
       </c>
-      <c r="AU2" s="120" t="s">
+      <c r="AU2" s="123" t="s">
         <v>16</v>
       </c>
-      <c r="AV2" s="120" t="s">
+      <c r="AV2" s="123" t="s">
         <v>17</v>
       </c>
-      <c r="AW2" s="120" t="s">
+      <c r="AW2" s="123" t="s">
         <v>18</v>
       </c>
-      <c r="AX2" s="120" t="s">
+      <c r="AX2" s="123" t="s">
         <v>19</v>
       </c>
-      <c r="AY2" s="120" t="s">
+      <c r="AY2" s="123" t="s">
         <v>20</v>
       </c>
-      <c r="AZ2" s="120" t="s">
+      <c r="AZ2" s="123" t="s">
         <v>21</v>
       </c>
-      <c r="BA2" s="120" t="s">
+      <c r="BA2" s="123" t="s">
         <v>22</v>
       </c>
-      <c r="BB2" s="120" t="s">
+      <c r="BB2" s="123" t="s">
         <v>23</v>
       </c>
-      <c r="BC2" s="120" t="s">
+      <c r="BC2" s="123" t="s">
         <v>24</v>
       </c>
-      <c r="BD2" s="120" t="s">
+      <c r="BD2" s="123" t="s">
         <v>25</v>
       </c>
-      <c r="BE2" s="120" t="s">
+      <c r="BE2" s="123" t="s">
         <v>26</v>
       </c>
-      <c r="BF2" s="120" t="s">
+      <c r="BF2" s="123" t="s">
         <v>27</v>
       </c>
-      <c r="BG2" s="120" t="s">
+      <c r="BG2" s="123" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:59" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="125" t="s">
-        <v>464</v>
-      </c>
-      <c r="B3" s="129" t="s">
-        <v>463</v>
-      </c>
-      <c r="C3" s="129" t="s">
+      <c r="A3" s="128" t="s">
+        <v>459</v>
+      </c>
+      <c r="B3" s="132" t="s">
+        <v>458</v>
+      </c>
+      <c r="C3" s="132" t="s">
         <v>29</v>
       </c>
-      <c r="D3" s="127" t="s">
+      <c r="D3" s="130" t="s">
         <v>30</v>
       </c>
-      <c r="E3" s="128"/>
-      <c r="F3" s="127" t="s">
+      <c r="E3" s="131"/>
+      <c r="F3" s="130" t="s">
         <v>31</v>
       </c>
-      <c r="G3" s="128"/>
-      <c r="H3" s="128"/>
-      <c r="I3" s="128"/>
-      <c r="J3" s="128"/>
-      <c r="K3" s="128"/>
-      <c r="L3" s="130"/>
-      <c r="M3" s="127" t="s">
+      <c r="G3" s="131"/>
+      <c r="H3" s="131"/>
+      <c r="I3" s="131"/>
+      <c r="J3" s="131"/>
+      <c r="K3" s="131"/>
+      <c r="L3" s="133"/>
+      <c r="M3" s="130" t="s">
         <v>32</v>
       </c>
-      <c r="N3" s="128"/>
-      <c r="O3" s="128"/>
-      <c r="P3" s="128"/>
-      <c r="Q3" s="130"/>
-      <c r="R3" s="134" t="s">
+      <c r="N3" s="131"/>
+      <c r="O3" s="131"/>
+      <c r="P3" s="131"/>
+      <c r="Q3" s="133"/>
+      <c r="R3" s="137" t="s">
         <v>33</v>
       </c>
-      <c r="S3" s="118"/>
-      <c r="T3" s="118"/>
-      <c r="U3" s="118"/>
-      <c r="V3" s="118"/>
-      <c r="W3" s="119"/>
-      <c r="X3" s="131" t="s">
+      <c r="S3" s="121"/>
+      <c r="T3" s="121"/>
+      <c r="U3" s="121"/>
+      <c r="V3" s="121"/>
+      <c r="W3" s="122"/>
+      <c r="X3" s="134" t="s">
         <v>34</v>
       </c>
-      <c r="Y3" s="132"/>
-      <c r="Z3" s="122" t="s">
+      <c r="Y3" s="135"/>
+      <c r="Z3" s="125" t="s">
         <v>35</v>
       </c>
-      <c r="AA3" s="133" t="s">
+      <c r="AA3" s="136" t="s">
         <v>36</v>
       </c>
-      <c r="AB3" s="127" t="s">
+      <c r="AB3" s="130" t="s">
         <v>37</v>
       </c>
-      <c r="AC3" s="128"/>
-      <c r="AD3" s="128"/>
-      <c r="AE3" s="130"/>
-      <c r="AF3" s="133" t="s">
+      <c r="AC3" s="131"/>
+      <c r="AD3" s="131"/>
+      <c r="AE3" s="133"/>
+      <c r="AF3" s="136" t="s">
         <v>38</v>
       </c>
       <c r="AG3" s="5"/>
-      <c r="AH3" s="121"/>
-      <c r="AI3" s="121"/>
-      <c r="AJ3" s="121"/>
-      <c r="AK3" s="121"/>
-      <c r="AL3" s="121"/>
-      <c r="AM3" s="121"/>
-      <c r="AN3" s="121"/>
+      <c r="AH3" s="124"/>
+      <c r="AI3" s="124"/>
+      <c r="AJ3" s="124"/>
+      <c r="AK3" s="124"/>
+      <c r="AL3" s="124"/>
+      <c r="AM3" s="124"/>
+      <c r="AN3" s="124"/>
       <c r="AO3" s="3"/>
-      <c r="AP3" s="121"/>
-      <c r="AQ3" s="121"/>
-      <c r="AR3" s="121"/>
-      <c r="AS3" s="121"/>
-      <c r="AT3" s="121"/>
-      <c r="AU3" s="121"/>
-      <c r="AV3" s="121"/>
-      <c r="AW3" s="121"/>
-      <c r="AX3" s="121"/>
-      <c r="AY3" s="121"/>
-      <c r="AZ3" s="121"/>
-      <c r="BA3" s="121"/>
-      <c r="BB3" s="121"/>
-      <c r="BC3" s="121"/>
-      <c r="BD3" s="121"/>
-      <c r="BE3" s="121"/>
-      <c r="BF3" s="121"/>
-      <c r="BG3" s="121"/>
+      <c r="AP3" s="124"/>
+      <c r="AQ3" s="124"/>
+      <c r="AR3" s="124"/>
+      <c r="AS3" s="124"/>
+      <c r="AT3" s="124"/>
+      <c r="AU3" s="124"/>
+      <c r="AV3" s="124"/>
+      <c r="AW3" s="124"/>
+      <c r="AX3" s="124"/>
+      <c r="AY3" s="124"/>
+      <c r="AZ3" s="124"/>
+      <c r="BA3" s="124"/>
+      <c r="BB3" s="124"/>
+      <c r="BC3" s="124"/>
+      <c r="BD3" s="124"/>
+      <c r="BE3" s="124"/>
+      <c r="BF3" s="124"/>
+      <c r="BG3" s="124"/>
     </row>
     <row r="4" spans="1:59" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="123"/>
-      <c r="B4" s="123"/>
-      <c r="C4" s="123"/>
+      <c r="A4" s="126"/>
+      <c r="B4" s="126"/>
+      <c r="C4" s="126"/>
       <c r="D4" s="6" t="s">
         <v>39</v>
       </c>
@@ -3220,10 +3236,10 @@
         <v>54</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="U4" s="4" t="s">
-        <v>466</v>
+        <v>461</v>
       </c>
       <c r="V4" s="4" t="s">
         <v>55</v>
@@ -3232,13 +3248,13 @@
         <v>56</v>
       </c>
       <c r="X4" s="4" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
       <c r="Y4" s="4" t="s">
-        <v>466</v>
-      </c>
-      <c r="Z4" s="123"/>
-      <c r="AA4" s="123"/>
+        <v>461</v>
+      </c>
+      <c r="Z4" s="126"/>
+      <c r="AA4" s="126"/>
       <c r="AB4" s="4" t="s">
         <v>57</v>
       </c>
@@ -3251,33 +3267,33 @@
       <c r="AE4" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="AF4" s="123"/>
-      <c r="AH4" s="123"/>
-      <c r="AI4" s="123"/>
-      <c r="AJ4" s="123"/>
-      <c r="AK4" s="123"/>
-      <c r="AL4" s="123"/>
-      <c r="AM4" s="123"/>
-      <c r="AN4" s="123"/>
+      <c r="AF4" s="126"/>
+      <c r="AH4" s="126"/>
+      <c r="AI4" s="126"/>
+      <c r="AJ4" s="126"/>
+      <c r="AK4" s="126"/>
+      <c r="AL4" s="126"/>
+      <c r="AM4" s="126"/>
+      <c r="AN4" s="126"/>
       <c r="AO4" s="3"/>
-      <c r="AP4" s="121"/>
-      <c r="AQ4" s="121"/>
-      <c r="AR4" s="121"/>
-      <c r="AS4" s="121"/>
-      <c r="AT4" s="121"/>
-      <c r="AU4" s="121"/>
-      <c r="AV4" s="121"/>
-      <c r="AW4" s="121"/>
-      <c r="AX4" s="121"/>
-      <c r="AY4" s="121"/>
-      <c r="AZ4" s="121"/>
-      <c r="BA4" s="121"/>
-      <c r="BB4" s="121"/>
-      <c r="BC4" s="121"/>
-      <c r="BD4" s="121"/>
-      <c r="BE4" s="121"/>
-      <c r="BF4" s="121"/>
-      <c r="BG4" s="121"/>
+      <c r="AP4" s="124"/>
+      <c r="AQ4" s="124"/>
+      <c r="AR4" s="124"/>
+      <c r="AS4" s="124"/>
+      <c r="AT4" s="124"/>
+      <c r="AU4" s="124"/>
+      <c r="AV4" s="124"/>
+      <c r="AW4" s="124"/>
+      <c r="AX4" s="124"/>
+      <c r="AY4" s="124"/>
+      <c r="AZ4" s="124"/>
+      <c r="BA4" s="124"/>
+      <c r="BB4" s="124"/>
+      <c r="BC4" s="124"/>
+      <c r="BD4" s="124"/>
+      <c r="BE4" s="124"/>
+      <c r="BF4" s="124"/>
+      <c r="BG4" s="124"/>
     </row>
     <row r="5" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
@@ -34471,7 +34487,7 @@
         <v>20</v>
       </c>
       <c r="D221" s="84">
-        <v>8401</v>
+        <v>8000</v>
       </c>
       <c r="E221" s="32">
         <v>0.5</v>
@@ -34492,10 +34508,10 @@
         <v>67</v>
       </c>
       <c r="K221" s="32">
-        <v>60.8</v>
+        <v>59.9</v>
       </c>
       <c r="L221" s="83">
-        <v>58.4</v>
+        <v>57.9</v>
       </c>
       <c r="M221" s="35" t="s">
         <v>64</v>
@@ -34526,12 +34542,10 @@
       <c r="W221" s="30">
         <v>2.0499999999999998</v>
       </c>
-      <c r="X221" s="35" t="s">
-        <v>64</v>
-      </c>
-      <c r="Y221" s="98" t="s">
-        <v>64</v>
-      </c>
+      <c r="X221" s="35">
+        <v>60</v>
+      </c>
+      <c r="Y221" s="98"/>
       <c r="Z221" s="96" t="s">
         <v>65</v>
       </c>
@@ -34545,10 +34559,10 @@
         <v>3.5</v>
       </c>
       <c r="AD221" s="32">
-        <v>50.8</v>
+        <v>120</v>
       </c>
       <c r="AE221" s="83">
-        <v>60</v>
+        <v>125</v>
       </c>
       <c r="AF221" s="28">
         <v>2354</v>
@@ -34576,8 +34590,8 @@
       </c>
       <c r="AP221" s="40"/>
       <c r="AQ221" s="41"/>
-      <c r="AR221" s="41" t="s">
-        <v>355</v>
+      <c r="AR221" s="119" t="s">
+        <v>469</v>
       </c>
       <c r="AS221" s="41" t="s">
         <v>274</v>
@@ -34669,10 +34683,12 @@
       <c r="W222" s="30">
         <v>2.0499999999999998</v>
       </c>
-      <c r="X222" s="31">
-        <v>60</v>
-      </c>
-      <c r="Y222" s="83"/>
+      <c r="X222" s="117" t="s">
+        <v>64</v>
+      </c>
+      <c r="Y222" s="118" t="s">
+        <v>64</v>
+      </c>
       <c r="Z222" s="96" t="s">
         <v>65</v>
       </c>
@@ -34686,10 +34702,10 @@
         <v>3.5</v>
       </c>
       <c r="AD222" s="32">
-        <v>120</v>
+        <v>50.8</v>
       </c>
       <c r="AE222" s="83">
-        <v>125</v>
+        <v>60</v>
       </c>
       <c r="AF222" s="28">
         <v>2354</v>
@@ -34717,8 +34733,8 @@
       </c>
       <c r="AP222" s="40"/>
       <c r="AQ222" s="41"/>
-      <c r="AR222" s="41" t="s">
-        <v>356</v>
+      <c r="AR222" s="119" t="s">
+        <v>470</v>
       </c>
       <c r="AS222" s="41" t="s">
         <v>274</v>
@@ -34811,7 +34827,7 @@
         <v>2.0499999999999998</v>
       </c>
       <c r="X223" s="31">
-        <v>75</v>
+        <v>45</v>
       </c>
       <c r="Y223" s="83"/>
       <c r="Z223" s="96" t="s">
@@ -34827,10 +34843,10 @@
         <v>3.5</v>
       </c>
       <c r="AD223" s="32">
-        <v>137</v>
+        <v>116</v>
       </c>
       <c r="AE223" s="83">
-        <v>150</v>
+        <v>125</v>
       </c>
       <c r="AF223" s="28">
         <v>2354</v>
@@ -34858,8 +34874,8 @@
       </c>
       <c r="AP223" s="40"/>
       <c r="AQ223" s="41"/>
-      <c r="AR223" s="41" t="s">
-        <v>357</v>
+      <c r="AR223" s="119" t="s">
+        <v>471</v>
       </c>
       <c r="AS223" s="41" t="s">
         <v>274</v>
@@ -34952,7 +34968,7 @@
         <v>2.0499999999999998</v>
       </c>
       <c r="X224" s="31">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="Y224" s="83"/>
       <c r="Z224" s="96" t="s">
@@ -34968,10 +34984,10 @@
         <v>3.5</v>
       </c>
       <c r="AD224" s="32">
-        <v>116</v>
+        <v>137</v>
       </c>
       <c r="AE224" s="83">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="AF224" s="28">
         <v>2354</v>
@@ -34999,8 +35015,8 @@
       </c>
       <c r="AP224" s="40"/>
       <c r="AQ224" s="41"/>
-      <c r="AR224" s="41" t="s">
-        <v>358</v>
+      <c r="AR224" s="119" t="s">
+        <v>472</v>
       </c>
       <c r="AS224" s="41" t="s">
         <v>274</v>
@@ -35037,7 +35053,7 @@
         <v>20</v>
       </c>
       <c r="D225" s="84">
-        <v>8401</v>
+        <v>8000</v>
       </c>
       <c r="E225" s="32">
         <v>0.5</v>
@@ -35058,10 +35074,10 @@
         <v>67</v>
       </c>
       <c r="K225" s="32">
-        <v>60.8</v>
+        <v>59.9</v>
       </c>
       <c r="L225" s="83">
-        <v>58.4</v>
+        <v>57.9</v>
       </c>
       <c r="M225" s="35" t="s">
         <v>64</v>
@@ -35140,8 +35156,8 @@
       </c>
       <c r="AP225" s="40"/>
       <c r="AQ225" s="41"/>
-      <c r="AR225" s="41" t="s">
-        <v>359</v>
+      <c r="AR225" s="119" t="s">
+        <v>473</v>
       </c>
       <c r="AS225" s="41" t="s">
         <v>274</v>
@@ -35172,7 +35188,7 @@
         <v>61</v>
       </c>
       <c r="B226" s="29" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="C226" s="83">
         <v>20</v>
@@ -35282,7 +35298,7 @@
       <c r="AP226" s="40"/>
       <c r="AQ226" s="41"/>
       <c r="AR226" s="41" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="AS226" s="41" t="s">
         <v>274</v>
@@ -35298,12 +35314,12 @@
       <c r="AZ226" s="41"/>
       <c r="BA226" s="41"/>
       <c r="BB226" s="29" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="BC226" s="41"/>
       <c r="BD226" s="41"/>
       <c r="BE226" s="29" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="BF226" s="41"/>
       <c r="BG226" s="44"/>
@@ -35313,7 +35329,7 @@
         <v>61</v>
       </c>
       <c r="B227" s="29" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="C227" s="83">
         <v>20</v>
@@ -35423,7 +35439,7 @@
       <c r="AP227" s="40"/>
       <c r="AQ227" s="41"/>
       <c r="AR227" s="41" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="AS227" s="41" t="s">
         <v>274</v>
@@ -35439,12 +35455,12 @@
       <c r="AZ227" s="41"/>
       <c r="BA227" s="41"/>
       <c r="BB227" s="29" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="BC227" s="41"/>
       <c r="BD227" s="41"/>
       <c r="BE227" s="29" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="BF227" s="41"/>
       <c r="BG227" s="44"/>
@@ -35454,7 +35470,7 @@
         <v>61</v>
       </c>
       <c r="B228" s="29" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="C228" s="83">
         <v>20</v>
@@ -35564,7 +35580,7 @@
       <c r="AP228" s="40"/>
       <c r="AQ228" s="41"/>
       <c r="AR228" s="41" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="AS228" s="41" t="s">
         <v>274</v>
@@ -35580,12 +35596,12 @@
       <c r="AZ228" s="41"/>
       <c r="BA228" s="41"/>
       <c r="BB228" s="29" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="BC228" s="41"/>
       <c r="BD228" s="41"/>
       <c r="BE228" s="29" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="BF228" s="41"/>
       <c r="BG228" s="44"/>
@@ -35595,7 +35611,7 @@
         <v>61</v>
       </c>
       <c r="B229" s="29" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="C229" s="83">
         <v>20</v>
@@ -35705,7 +35721,7 @@
       <c r="AP229" s="40"/>
       <c r="AQ229" s="41"/>
       <c r="AR229" s="41" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="AS229" s="41" t="s">
         <v>274</v>
@@ -35721,12 +35737,12 @@
       <c r="AZ229" s="41"/>
       <c r="BA229" s="41"/>
       <c r="BB229" s="29" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="BC229" s="41"/>
       <c r="BD229" s="41"/>
       <c r="BE229" s="29" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="BF229" s="41"/>
       <c r="BG229" s="44"/>
@@ -35736,7 +35752,7 @@
         <v>61</v>
       </c>
       <c r="B230" s="29" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="C230" s="83">
         <v>20</v>
@@ -35848,7 +35864,7 @@
       <c r="AP230" s="40"/>
       <c r="AQ230" s="41"/>
       <c r="AR230" s="41" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="AS230" s="41" t="s">
         <v>274</v>
@@ -35864,12 +35880,12 @@
       <c r="AZ230" s="41"/>
       <c r="BA230" s="41"/>
       <c r="BB230" s="29" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="BC230" s="41"/>
       <c r="BD230" s="41"/>
       <c r="BE230" s="29" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="BF230" s="41"/>
       <c r="BG230" s="44"/>
@@ -35991,7 +36007,7 @@
       <c r="AP231" s="40"/>
       <c r="AQ231" s="41"/>
       <c r="AR231" s="41" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="AS231" s="41" t="s">
         <v>274</v>
@@ -36022,7 +36038,7 @@
         <v>61</v>
       </c>
       <c r="B232" s="29" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="C232" s="83">
         <v>15</v>
@@ -36132,7 +36148,7 @@
       <c r="AP232" s="40"/>
       <c r="AQ232" s="41"/>
       <c r="AR232" s="41" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="AS232" s="41" t="s">
         <v>274</v>
@@ -36148,12 +36164,12 @@
       <c r="AZ232" s="41"/>
       <c r="BA232" s="41"/>
       <c r="BB232" s="29" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="BC232" s="41"/>
       <c r="BD232" s="41"/>
       <c r="BE232" s="29" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="BF232" s="41"/>
       <c r="BG232" s="44"/>
@@ -36163,7 +36179,7 @@
         <v>61</v>
       </c>
       <c r="B233" s="29" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="C233" s="83">
         <v>15</v>
@@ -36273,7 +36289,7 @@
       <c r="AP233" s="40"/>
       <c r="AQ233" s="41"/>
       <c r="AR233" s="41" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="AS233" s="41" t="s">
         <v>274</v>
@@ -36289,12 +36305,12 @@
       <c r="AZ233" s="41"/>
       <c r="BA233" s="41"/>
       <c r="BB233" s="29" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="BC233" s="41"/>
       <c r="BD233" s="41"/>
       <c r="BE233" s="29" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="BF233" s="41"/>
       <c r="BG233" s="44"/>
@@ -36304,7 +36320,7 @@
         <v>61</v>
       </c>
       <c r="B234" s="29" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="C234" s="83">
         <v>15</v>
@@ -36414,7 +36430,7 @@
       <c r="AP234" s="40"/>
       <c r="AQ234" s="41"/>
       <c r="AR234" s="41" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="AS234" s="41" t="s">
         <v>274</v>
@@ -36430,12 +36446,12 @@
       <c r="AZ234" s="41"/>
       <c r="BA234" s="41"/>
       <c r="BB234" s="29" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="BC234" s="41"/>
       <c r="BD234" s="41"/>
       <c r="BE234" s="29" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="BF234" s="41"/>
       <c r="BG234" s="44"/>
@@ -36445,7 +36461,7 @@
         <v>61</v>
       </c>
       <c r="B235" s="29" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="C235" s="83">
         <v>15</v>
@@ -36557,7 +36573,7 @@
       <c r="AP235" s="40"/>
       <c r="AQ235" s="41"/>
       <c r="AR235" s="41" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="AS235" s="41" t="s">
         <v>274</v>
@@ -36573,12 +36589,12 @@
       <c r="AZ235" s="41"/>
       <c r="BA235" s="41"/>
       <c r="BB235" s="29" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="BC235" s="41"/>
       <c r="BD235" s="41"/>
       <c r="BE235" s="29" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="BF235" s="41"/>
       <c r="BG235" s="44"/>
@@ -36698,7 +36714,7 @@
       <c r="AP236" s="40"/>
       <c r="AQ236" s="41"/>
       <c r="AR236" s="41" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="AS236" s="41" t="s">
         <v>269</v>
@@ -36841,7 +36857,7 @@
       <c r="AP237" s="40"/>
       <c r="AQ237" s="41"/>
       <c r="AR237" s="41" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="AS237" s="41" t="s">
         <v>269</v>
@@ -36872,7 +36888,7 @@
         <v>61</v>
       </c>
       <c r="B238" s="29" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="C238" s="83">
         <v>12.5</v>
@@ -36982,7 +36998,7 @@
       <c r="AP238" s="40"/>
       <c r="AQ238" s="41"/>
       <c r="AR238" s="41" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="AS238" s="41" t="s">
         <v>269</v>
@@ -36998,12 +37014,12 @@
       <c r="AZ238" s="41"/>
       <c r="BA238" s="41"/>
       <c r="BB238" s="29" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="BC238" s="41"/>
       <c r="BD238" s="41"/>
       <c r="BE238" s="29" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="BF238" s="41"/>
       <c r="BG238" s="44"/>
@@ -37013,7 +37029,7 @@
         <v>61</v>
       </c>
       <c r="B239" s="29" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="C239" s="83">
         <v>10</v>
@@ -37123,7 +37139,7 @@
       <c r="AP239" s="40"/>
       <c r="AQ239" s="41"/>
       <c r="AR239" s="41" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="AS239" s="41" t="s">
         <v>269</v>
@@ -37139,12 +37155,12 @@
       <c r="AZ239" s="41"/>
       <c r="BA239" s="41"/>
       <c r="BB239" s="29" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="BC239" s="41"/>
       <c r="BD239" s="41"/>
       <c r="BE239" s="29" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="BF239" s="41"/>
       <c r="BG239" s="44"/>
@@ -37154,7 +37170,7 @@
         <v>61</v>
       </c>
       <c r="B240" s="29" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="C240" s="83">
         <v>12.5</v>
@@ -37264,7 +37280,7 @@
       <c r="AP240" s="40"/>
       <c r="AQ240" s="41"/>
       <c r="AR240" s="41" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="AS240" s="41" t="s">
         <v>269</v>
@@ -37280,12 +37296,12 @@
       <c r="AZ240" s="41"/>
       <c r="BA240" s="41"/>
       <c r="BB240" s="29" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="BC240" s="41"/>
       <c r="BD240" s="41"/>
       <c r="BE240" s="29" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="BF240" s="41"/>
       <c r="BG240" s="44"/>
@@ -37295,7 +37311,7 @@
         <v>61</v>
       </c>
       <c r="B241" s="29" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="C241" s="83">
         <v>12.5</v>
@@ -37405,7 +37421,7 @@
       <c r="AP241" s="40"/>
       <c r="AQ241" s="41"/>
       <c r="AR241" s="41" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="AS241" s="41" t="s">
         <v>269</v>
@@ -37421,12 +37437,12 @@
       <c r="AZ241" s="41"/>
       <c r="BA241" s="41"/>
       <c r="BB241" s="29" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="BC241" s="41"/>
       <c r="BD241" s="41"/>
       <c r="BE241" s="29" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="BF241" s="41"/>
       <c r="BG241" s="44"/>
@@ -37436,7 +37452,7 @@
         <v>61</v>
       </c>
       <c r="B242" s="29" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="C242" s="83">
         <v>12.5</v>
@@ -37546,7 +37562,7 @@
       <c r="AP242" s="40"/>
       <c r="AQ242" s="41"/>
       <c r="AR242" s="41" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="AS242" s="41" t="s">
         <v>269</v>
@@ -37562,12 +37578,12 @@
       <c r="AZ242" s="41"/>
       <c r="BA242" s="41"/>
       <c r="BB242" s="29" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="BC242" s="41"/>
       <c r="BD242" s="41"/>
       <c r="BE242" s="29" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="BF242" s="41"/>
       <c r="BG242" s="44"/>
@@ -37577,7 +37593,7 @@
         <v>61</v>
       </c>
       <c r="B243" s="29" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="C243" s="83">
         <v>12.5</v>
@@ -37689,7 +37705,7 @@
       <c r="AP243" s="40"/>
       <c r="AQ243" s="41"/>
       <c r="AR243" s="41" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="AS243" s="41" t="s">
         <v>269</v>
@@ -37705,12 +37721,12 @@
       <c r="AZ243" s="41"/>
       <c r="BA243" s="41"/>
       <c r="BB243" s="29" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="BC243" s="41"/>
       <c r="BD243" s="41"/>
       <c r="BE243" s="29" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="BF243" s="41"/>
       <c r="BG243" s="44"/>
@@ -37720,7 +37736,7 @@
         <v>61</v>
       </c>
       <c r="B244" s="29" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="C244" s="83">
         <v>10</v>
@@ -37830,7 +37846,7 @@
       <c r="AP244" s="40"/>
       <c r="AQ244" s="41"/>
       <c r="AR244" s="41" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="AS244" s="41" t="s">
         <v>269</v>
@@ -37846,12 +37862,12 @@
       <c r="AZ244" s="41"/>
       <c r="BA244" s="41"/>
       <c r="BB244" s="29" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="BC244" s="41"/>
       <c r="BD244" s="41"/>
       <c r="BE244" s="29" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="BF244" s="41"/>
       <c r="BG244" s="44"/>
@@ -37861,7 +37877,7 @@
         <v>61</v>
       </c>
       <c r="B245" s="29" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="C245" s="83">
         <v>8.5</v>
@@ -37973,7 +37989,7 @@
       <c r="AP245" s="40"/>
       <c r="AQ245" s="41"/>
       <c r="AR245" s="41" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="AS245" s="41" t="s">
         <v>269</v>
@@ -37989,12 +38005,12 @@
       <c r="AZ245" s="41"/>
       <c r="BA245" s="41"/>
       <c r="BB245" s="29" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="BC245" s="41"/>
       <c r="BD245" s="41"/>
       <c r="BE245" s="29" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="BF245" s="41"/>
       <c r="BG245" s="44"/>
@@ -38004,7 +38020,7 @@
         <v>61</v>
       </c>
       <c r="B246" s="29" t="s">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="C246" s="83">
         <v>10</v>
@@ -38114,7 +38130,7 @@
       <c r="AP246" s="40"/>
       <c r="AQ246" s="41"/>
       <c r="AR246" s="41" t="s">
-        <v>386</v>
+        <v>381</v>
       </c>
       <c r="AS246" s="41" t="s">
         <v>269</v>
@@ -38130,12 +38146,12 @@
       <c r="AZ246" s="41"/>
       <c r="BA246" s="41"/>
       <c r="BB246" s="29" t="s">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="BC246" s="41"/>
       <c r="BD246" s="41"/>
       <c r="BE246" s="29" t="s">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="BF246" s="41"/>
       <c r="BG246" s="44"/>
@@ -38145,7 +38161,7 @@
         <v>61</v>
       </c>
       <c r="B247" s="29" t="s">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="C247" s="83">
         <v>10</v>
@@ -38255,7 +38271,7 @@
       <c r="AP247" s="40"/>
       <c r="AQ247" s="41"/>
       <c r="AR247" s="41" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="AS247" s="41" t="s">
         <v>269</v>
@@ -38271,12 +38287,12 @@
       <c r="AZ247" s="41"/>
       <c r="BA247" s="41"/>
       <c r="BB247" s="29" t="s">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="BC247" s="41"/>
       <c r="BD247" s="41"/>
       <c r="BE247" s="29" t="s">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="BF247" s="41"/>
       <c r="BG247" s="44"/>
@@ -38286,7 +38302,7 @@
         <v>61</v>
       </c>
       <c r="B248" s="29" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="C248" s="83">
         <v>10</v>
@@ -38396,7 +38412,7 @@
       <c r="AP248" s="40"/>
       <c r="AQ248" s="41"/>
       <c r="AR248" s="41" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="AS248" s="41" t="s">
         <v>269</v>
@@ -38412,12 +38428,12 @@
       <c r="AZ248" s="41"/>
       <c r="BA248" s="41"/>
       <c r="BB248" s="29" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="BC248" s="41"/>
       <c r="BD248" s="41"/>
       <c r="BE248" s="29" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="BF248" s="41"/>
       <c r="BG248" s="44"/>
@@ -38427,7 +38443,7 @@
         <v>61</v>
       </c>
       <c r="B249" s="29" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="C249" s="83">
         <v>10</v>
@@ -38539,7 +38555,7 @@
       <c r="AP249" s="40"/>
       <c r="AQ249" s="41"/>
       <c r="AR249" s="41" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="AS249" s="41" t="s">
         <v>269</v>
@@ -38555,12 +38571,12 @@
       <c r="AZ249" s="41"/>
       <c r="BA249" s="41"/>
       <c r="BB249" s="29" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="BC249" s="41"/>
       <c r="BD249" s="41"/>
       <c r="BE249" s="29" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="BF249" s="41"/>
       <c r="BG249" s="44"/>
@@ -38570,7 +38586,7 @@
         <v>61</v>
       </c>
       <c r="B250" s="29" t="s">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="C250" s="83">
         <v>10</v>
@@ -38680,7 +38696,7 @@
       <c r="AP250" s="40"/>
       <c r="AQ250" s="41"/>
       <c r="AR250" s="41" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="AS250" s="41" t="s">
         <v>269</v>
@@ -38696,12 +38712,12 @@
       <c r="AZ250" s="41"/>
       <c r="BA250" s="41"/>
       <c r="BB250" s="29" t="s">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="BC250" s="41"/>
       <c r="BD250" s="41"/>
       <c r="BE250" s="29" t="s">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="BF250" s="41"/>
       <c r="BG250" s="44"/>
@@ -38711,7 +38727,7 @@
         <v>61</v>
       </c>
       <c r="B251" s="29" t="s">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="C251" s="83">
         <v>10</v>
@@ -38823,7 +38839,7 @@
       <c r="AP251" s="40"/>
       <c r="AQ251" s="41"/>
       <c r="AR251" s="41" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="AS251" s="41" t="s">
         <v>269</v>
@@ -38839,12 +38855,12 @@
       <c r="AZ251" s="41"/>
       <c r="BA251" s="41"/>
       <c r="BB251" s="29" t="s">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="BC251" s="41"/>
       <c r="BD251" s="41"/>
       <c r="BE251" s="29" t="s">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="BF251" s="41"/>
       <c r="BG251" s="44"/>
@@ -38854,7 +38870,7 @@
         <v>61</v>
       </c>
       <c r="B252" s="29" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="C252" s="83">
         <v>8.5</v>
@@ -38964,7 +38980,7 @@
       <c r="AP252" s="40"/>
       <c r="AQ252" s="41"/>
       <c r="AR252" s="41" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="AS252" s="41" t="s">
         <v>269</v>
@@ -38980,12 +38996,12 @@
       <c r="AZ252" s="41"/>
       <c r="BA252" s="41"/>
       <c r="BB252" s="29" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="BC252" s="41"/>
       <c r="BD252" s="41"/>
       <c r="BE252" s="29" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="BF252" s="41"/>
       <c r="BG252" s="44"/>
@@ -38995,7 +39011,7 @@
         <v>61</v>
       </c>
       <c r="B253" s="29" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="C253" s="83">
         <v>8.5</v>
@@ -39105,7 +39121,7 @@
       <c r="AP253" s="40"/>
       <c r="AQ253" s="41"/>
       <c r="AR253" s="41" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="AS253" s="41" t="s">
         <v>269</v>
@@ -39121,12 +39137,12 @@
       <c r="AZ253" s="41"/>
       <c r="BA253" s="41"/>
       <c r="BB253" s="29" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="BC253" s="41"/>
       <c r="BD253" s="41"/>
       <c r="BE253" s="29" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="BF253" s="41"/>
       <c r="BG253" s="44"/>
@@ -39136,7 +39152,7 @@
         <v>61</v>
       </c>
       <c r="B254" s="29" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="C254" s="83">
         <v>8.5</v>
@@ -39246,7 +39262,7 @@
       <c r="AP254" s="40"/>
       <c r="AQ254" s="41"/>
       <c r="AR254" s="41" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="AS254" s="41" t="s">
         <v>269</v>
@@ -39262,12 +39278,12 @@
       <c r="AZ254" s="41"/>
       <c r="BA254" s="41"/>
       <c r="BB254" s="29" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="BC254" s="41"/>
       <c r="BD254" s="41"/>
       <c r="BE254" s="29" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="BF254" s="41"/>
       <c r="BG254" s="44"/>
@@ -39277,7 +39293,7 @@
         <v>61</v>
       </c>
       <c r="B255" s="29" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="C255" s="83">
         <v>8.5</v>
@@ -39389,7 +39405,7 @@
       <c r="AP255" s="40"/>
       <c r="AQ255" s="41"/>
       <c r="AR255" s="41" t="s">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="AS255" s="41" t="s">
         <v>269</v>
@@ -39405,12 +39421,12 @@
       <c r="AZ255" s="41"/>
       <c r="BA255" s="41"/>
       <c r="BB255" s="29" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="BC255" s="41"/>
       <c r="BD255" s="41"/>
       <c r="BE255" s="29" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="BF255" s="41"/>
       <c r="BG255" s="44"/>
@@ -39420,7 +39436,7 @@
         <v>61</v>
       </c>
       <c r="B256" s="29" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="C256" s="83">
         <v>8.5</v>
@@ -39530,7 +39546,7 @@
       <c r="AP256" s="40"/>
       <c r="AQ256" s="41"/>
       <c r="AR256" s="41" t="s">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="AS256" s="41" t="s">
         <v>269</v>
@@ -39546,12 +39562,12 @@
       <c r="AZ256" s="41"/>
       <c r="BA256" s="41"/>
       <c r="BB256" s="29" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="BC256" s="41"/>
       <c r="BD256" s="41"/>
       <c r="BE256" s="29" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="BF256" s="41"/>
       <c r="BG256" s="44"/>
@@ -39561,7 +39577,7 @@
         <v>61</v>
       </c>
       <c r="B257" s="29" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="C257" s="83">
         <v>8.5</v>
@@ -39671,7 +39687,7 @@
       <c r="AP257" s="40"/>
       <c r="AQ257" s="41"/>
       <c r="AR257" s="41" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="AS257" s="41" t="s">
         <v>269</v>
@@ -39687,12 +39703,12 @@
       <c r="AZ257" s="41"/>
       <c r="BA257" s="41"/>
       <c r="BB257" s="29" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="BC257" s="41"/>
       <c r="BD257" s="41"/>
       <c r="BE257" s="29" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="BF257" s="41"/>
       <c r="BG257" s="44"/>
@@ -39702,7 +39718,7 @@
         <v>61</v>
       </c>
       <c r="B258" s="29" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="C258" s="83">
         <v>8.5</v>
@@ -39812,7 +39828,7 @@
       <c r="AP258" s="40"/>
       <c r="AQ258" s="41"/>
       <c r="AR258" s="41" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="AS258" s="41" t="s">
         <v>269</v>
@@ -39828,12 +39844,12 @@
       <c r="AZ258" s="41"/>
       <c r="BA258" s="41"/>
       <c r="BB258" s="29" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="BC258" s="41"/>
       <c r="BD258" s="41"/>
       <c r="BE258" s="29" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="BF258" s="41"/>
       <c r="BG258" s="44"/>
@@ -39843,7 +39859,7 @@
         <v>61</v>
       </c>
       <c r="B259" s="29" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="C259" s="83">
         <v>7.5</v>
@@ -39861,7 +39877,7 @@
         <v>69011</v>
       </c>
       <c r="H259" s="32" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="I259" s="32">
         <v>80</v>
@@ -39953,7 +39969,7 @@
       <c r="AP259" s="40"/>
       <c r="AQ259" s="41"/>
       <c r="AR259" s="41" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="AS259" s="41" t="s">
         <v>269</v>
@@ -39969,12 +39985,12 @@
       <c r="AZ259" s="41"/>
       <c r="BA259" s="41"/>
       <c r="BB259" s="29" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="BC259" s="41"/>
       <c r="BD259" s="41"/>
       <c r="BE259" s="29" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="BF259" s="41"/>
       <c r="BG259" s="44"/>
@@ -39984,7 +40000,7 @@
         <v>61</v>
       </c>
       <c r="B260" s="29" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="C260" s="83">
         <v>7.5</v>
@@ -40002,7 +40018,7 @@
         <v>69011</v>
       </c>
       <c r="H260" s="32" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="I260" s="32">
         <v>80</v>
@@ -40094,7 +40110,7 @@
       <c r="AP260" s="40"/>
       <c r="AQ260" s="41"/>
       <c r="AR260" s="41" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="AS260" s="41" t="s">
         <v>269</v>
@@ -40110,12 +40126,12 @@
       <c r="AZ260" s="41"/>
       <c r="BA260" s="41"/>
       <c r="BB260" s="29" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="BC260" s="41"/>
       <c r="BD260" s="41"/>
       <c r="BE260" s="29" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="BF260" s="41"/>
       <c r="BG260" s="44"/>
@@ -40125,7 +40141,7 @@
         <v>61</v>
       </c>
       <c r="B261" s="29" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="C261" s="83">
         <v>7.5</v>
@@ -40143,7 +40159,7 @@
         <v>69011</v>
       </c>
       <c r="H261" s="32" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="I261" s="32">
         <v>80</v>
@@ -40235,7 +40251,7 @@
       <c r="AP261" s="40"/>
       <c r="AQ261" s="41"/>
       <c r="AR261" s="41" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="AS261" s="41" t="s">
         <v>269</v>
@@ -40251,12 +40267,12 @@
       <c r="AZ261" s="41"/>
       <c r="BA261" s="41"/>
       <c r="BB261" s="29" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="BC261" s="41"/>
       <c r="BD261" s="41"/>
       <c r="BE261" s="29" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="BF261" s="41"/>
       <c r="BG261" s="44"/>
@@ -40266,7 +40282,7 @@
         <v>61</v>
       </c>
       <c r="B262" s="29" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="C262" s="83">
         <v>7.5</v>
@@ -40284,7 +40300,7 @@
         <v>69011</v>
       </c>
       <c r="H262" s="32" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="I262" s="32">
         <v>80</v>
@@ -40378,7 +40394,7 @@
       <c r="AP262" s="40"/>
       <c r="AQ262" s="41"/>
       <c r="AR262" s="41" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="AS262" s="41" t="s">
         <v>269</v>
@@ -40394,12 +40410,12 @@
       <c r="AZ262" s="41"/>
       <c r="BA262" s="41"/>
       <c r="BB262" s="29" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="BC262" s="41"/>
       <c r="BD262" s="41"/>
       <c r="BE262" s="29" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="BF262" s="41"/>
       <c r="BG262" s="44"/>
@@ -40409,7 +40425,7 @@
         <v>61</v>
       </c>
       <c r="B263" s="29" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="C263" s="83">
         <v>7.5</v>
@@ -40427,7 +40443,7 @@
         <v>69011</v>
       </c>
       <c r="H263" s="32" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="I263" s="32">
         <v>80</v>
@@ -40519,7 +40535,7 @@
       <c r="AP263" s="40"/>
       <c r="AQ263" s="41"/>
       <c r="AR263" s="41" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="AS263" s="41" t="s">
         <v>269</v>
@@ -40535,12 +40551,12 @@
       <c r="AZ263" s="41"/>
       <c r="BA263" s="41"/>
       <c r="BB263" s="29" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="BC263" s="41"/>
       <c r="BD263" s="41"/>
       <c r="BE263" s="29" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="BF263" s="41"/>
       <c r="BG263" s="44"/>
@@ -40550,7 +40566,7 @@
         <v>61</v>
       </c>
       <c r="B264" s="29" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="C264" s="83">
         <v>7.5</v>
@@ -40568,7 +40584,7 @@
         <v>69011</v>
       </c>
       <c r="H264" s="32" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="I264" s="32">
         <v>80</v>
@@ -40660,7 +40676,7 @@
       <c r="AP264" s="40"/>
       <c r="AQ264" s="41"/>
       <c r="AR264" s="41" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="AS264" s="41" t="s">
         <v>269</v>
@@ -40676,12 +40692,12 @@
       <c r="AZ264" s="41"/>
       <c r="BA264" s="41"/>
       <c r="BB264" s="29" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="BC264" s="41"/>
       <c r="BD264" s="41"/>
       <c r="BE264" s="29" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="BF264" s="41"/>
       <c r="BG264" s="44"/>
@@ -40691,7 +40707,7 @@
         <v>61</v>
       </c>
       <c r="B265" s="29" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="C265" s="83">
         <v>7.5</v>
@@ -40709,7 +40725,7 @@
         <v>69011</v>
       </c>
       <c r="H265" s="32" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="I265" s="32">
         <v>80</v>
@@ -40801,7 +40817,7 @@
       <c r="AP265" s="40"/>
       <c r="AQ265" s="41"/>
       <c r="AR265" s="41" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="AS265" s="41" t="s">
         <v>269</v>
@@ -40817,12 +40833,12 @@
       <c r="AZ265" s="41"/>
       <c r="BA265" s="41"/>
       <c r="BB265" s="29" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="BC265" s="41"/>
       <c r="BD265" s="41"/>
       <c r="BE265" s="29" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="BF265" s="41"/>
       <c r="BG265" s="44"/>
@@ -40832,7 +40848,7 @@
         <v>61</v>
       </c>
       <c r="B266" s="29" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="C266" s="83">
         <v>7.5</v>
@@ -40850,7 +40866,7 @@
         <v>69011</v>
       </c>
       <c r="H266" s="32" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="I266" s="32">
         <v>80</v>
@@ -40944,7 +40960,7 @@
       <c r="AP266" s="40"/>
       <c r="AQ266" s="41"/>
       <c r="AR266" s="41" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="AS266" s="41" t="s">
         <v>269</v>
@@ -40960,12 +40976,12 @@
       <c r="AZ266" s="41"/>
       <c r="BA266" s="41"/>
       <c r="BB266" s="29" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="BC266" s="41"/>
       <c r="BD266" s="41"/>
       <c r="BE266" s="29" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="BF266" s="41"/>
       <c r="BG266" s="44"/>
@@ -40975,7 +40991,7 @@
         <v>61</v>
       </c>
       <c r="B267" s="29" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="C267" s="83">
         <v>6</v>
@@ -41085,7 +41101,7 @@
       <c r="AP267" s="40"/>
       <c r="AQ267" s="41"/>
       <c r="AR267" s="41" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="AS267" s="41" t="s">
         <v>264</v>
@@ -41101,12 +41117,12 @@
       <c r="AZ267" s="41"/>
       <c r="BA267" s="41"/>
       <c r="BB267" s="29" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="BC267" s="41"/>
       <c r="BD267" s="41"/>
       <c r="BE267" s="29" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="BF267" s="41"/>
       <c r="BG267" s="44"/>
@@ -41226,7 +41242,7 @@
       <c r="AP268" s="40"/>
       <c r="AQ268" s="41"/>
       <c r="AR268" s="41" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="AS268" s="41" t="s">
         <v>264</v>
@@ -41367,7 +41383,7 @@
       <c r="AP269" s="40"/>
       <c r="AQ269" s="41"/>
       <c r="AR269" s="41" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="AS269" s="41" t="s">
         <v>264</v>
@@ -41508,7 +41524,7 @@
       <c r="AP270" s="40"/>
       <c r="AQ270" s="41"/>
       <c r="AR270" s="41" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="AS270" s="41" t="s">
         <v>264</v>
@@ -41651,7 +41667,7 @@
       <c r="AP271" s="40"/>
       <c r="AQ271" s="41"/>
       <c r="AR271" s="41" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="AS271" s="41" t="s">
         <v>264</v>
@@ -41682,7 +41698,7 @@
         <v>61</v>
       </c>
       <c r="B272" s="29" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="C272" s="83">
         <v>6</v>
@@ -41792,7 +41808,7 @@
       <c r="AP272" s="40"/>
       <c r="AQ272" s="41"/>
       <c r="AR272" s="41" t="s">
-        <v>417</v>
+        <v>412</v>
       </c>
       <c r="AS272" s="41" t="s">
         <v>264</v>
@@ -41808,12 +41824,12 @@
       <c r="AZ272" s="41"/>
       <c r="BA272" s="41"/>
       <c r="BB272" s="29" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="BC272" s="41"/>
       <c r="BD272" s="41"/>
       <c r="BE272" s="29" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="BF272" s="41"/>
       <c r="BG272" s="44"/>
@@ -41823,7 +41839,7 @@
         <v>61</v>
       </c>
       <c r="B273" s="29" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="C273" s="83">
         <v>6</v>
@@ -41933,7 +41949,7 @@
       <c r="AP273" s="40"/>
       <c r="AQ273" s="41"/>
       <c r="AR273" s="41" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="AS273" s="41" t="s">
         <v>264</v>
@@ -41949,12 +41965,12 @@
       <c r="AZ273" s="41"/>
       <c r="BA273" s="41"/>
       <c r="BB273" s="29" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="BC273" s="41"/>
       <c r="BD273" s="41"/>
       <c r="BE273" s="29" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="BF273" s="41"/>
       <c r="BG273" s="44"/>
@@ -41964,7 +41980,7 @@
         <v>61</v>
       </c>
       <c r="B274" s="29" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="C274" s="83">
         <v>6</v>
@@ -42074,7 +42090,7 @@
       <c r="AP274" s="40"/>
       <c r="AQ274" s="41"/>
       <c r="AR274" s="41" t="s">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="AS274" s="41" t="s">
         <v>264</v>
@@ -42090,12 +42106,12 @@
       <c r="AZ274" s="41"/>
       <c r="BA274" s="41"/>
       <c r="BB274" s="29" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="BC274" s="41"/>
       <c r="BD274" s="41"/>
       <c r="BE274" s="29" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="BF274" s="41"/>
       <c r="BG274" s="44"/>
@@ -42105,7 +42121,7 @@
         <v>61</v>
       </c>
       <c r="B275" s="29" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="C275" s="83">
         <v>6</v>
@@ -42215,7 +42231,7 @@
       <c r="AP275" s="40"/>
       <c r="AQ275" s="41"/>
       <c r="AR275" s="41" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="AS275" s="41" t="s">
         <v>264</v>
@@ -42231,12 +42247,12 @@
       <c r="AZ275" s="41"/>
       <c r="BA275" s="41"/>
       <c r="BB275" s="29" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="BC275" s="41"/>
       <c r="BD275" s="41"/>
       <c r="BE275" s="29" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="BF275" s="41"/>
       <c r="BG275" s="44"/>
@@ -42246,7 +42262,7 @@
         <v>61</v>
       </c>
       <c r="B276" s="29" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="C276" s="83">
         <v>6</v>
@@ -42358,7 +42374,7 @@
       <c r="AP276" s="40"/>
       <c r="AQ276" s="41"/>
       <c r="AR276" s="41" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="AS276" s="41" t="s">
         <v>264</v>
@@ -42374,12 +42390,12 @@
       <c r="AZ276" s="41"/>
       <c r="BA276" s="41"/>
       <c r="BB276" s="29" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="BC276" s="41"/>
       <c r="BD276" s="41"/>
       <c r="BE276" s="29" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="BF276" s="41"/>
       <c r="BG276" s="44"/>
@@ -42389,7 +42405,7 @@
         <v>61</v>
       </c>
       <c r="B277" s="29" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="C277" s="83">
         <v>5</v>
@@ -42407,7 +42423,7 @@
         <v>47695</v>
       </c>
       <c r="H277" s="32" t="s">
-        <v>423</v>
+        <v>418</v>
       </c>
       <c r="I277" s="32">
         <v>80</v>
@@ -42499,7 +42515,7 @@
       <c r="AP277" s="40"/>
       <c r="AQ277" s="41"/>
       <c r="AR277" s="41" t="s">
-        <v>424</v>
+        <v>419</v>
       </c>
       <c r="AS277" s="41" t="s">
         <v>264</v>
@@ -42515,12 +42531,12 @@
       <c r="AZ277" s="41"/>
       <c r="BA277" s="41"/>
       <c r="BB277" s="29" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="BC277" s="41"/>
       <c r="BD277" s="41"/>
       <c r="BE277" s="29" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="BF277" s="41"/>
       <c r="BG277" s="44"/>
@@ -42530,7 +42546,7 @@
         <v>61</v>
       </c>
       <c r="B278" s="29" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="C278" s="83">
         <v>5</v>
@@ -42548,7 +42564,7 @@
         <v>47695</v>
       </c>
       <c r="H278" s="32" t="s">
-        <v>423</v>
+        <v>418</v>
       </c>
       <c r="I278" s="32">
         <v>80</v>
@@ -42640,7 +42656,7 @@
       <c r="AP278" s="40"/>
       <c r="AQ278" s="41"/>
       <c r="AR278" s="41" t="s">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="AS278" s="41" t="s">
         <v>264</v>
@@ -42656,12 +42672,12 @@
       <c r="AZ278" s="41"/>
       <c r="BA278" s="41"/>
       <c r="BB278" s="29" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="BC278" s="41"/>
       <c r="BD278" s="41"/>
       <c r="BE278" s="29" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="BF278" s="41"/>
       <c r="BG278" s="44"/>
@@ -42671,7 +42687,7 @@
         <v>61</v>
       </c>
       <c r="B279" s="29" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="C279" s="83">
         <v>5</v>
@@ -42689,7 +42705,7 @@
         <v>47695</v>
       </c>
       <c r="H279" s="32" t="s">
-        <v>423</v>
+        <v>418</v>
       </c>
       <c r="I279" s="32">
         <v>80</v>
@@ -42781,7 +42797,7 @@
       <c r="AP279" s="40"/>
       <c r="AQ279" s="41"/>
       <c r="AR279" s="41" t="s">
-        <v>426</v>
+        <v>421</v>
       </c>
       <c r="AS279" s="41" t="s">
         <v>264</v>
@@ -42797,12 +42813,12 @@
       <c r="AZ279" s="41"/>
       <c r="BA279" s="41"/>
       <c r="BB279" s="29" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="BC279" s="41"/>
       <c r="BD279" s="41"/>
       <c r="BE279" s="29" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="BF279" s="41"/>
       <c r="BG279" s="44"/>
@@ -42812,7 +42828,7 @@
         <v>61</v>
       </c>
       <c r="B280" s="29" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="C280" s="83">
         <v>5</v>
@@ -42830,7 +42846,7 @@
         <v>47695</v>
       </c>
       <c r="H280" s="32" t="s">
-        <v>423</v>
+        <v>418</v>
       </c>
       <c r="I280" s="32">
         <v>80</v>
@@ -42924,7 +42940,7 @@
       <c r="AP280" s="40"/>
       <c r="AQ280" s="41"/>
       <c r="AR280" s="41" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="AS280" s="41" t="s">
         <v>264</v>
@@ -42940,12 +42956,12 @@
       <c r="AZ280" s="41"/>
       <c r="BA280" s="41"/>
       <c r="BB280" s="29" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="BC280" s="41"/>
       <c r="BD280" s="41"/>
       <c r="BE280" s="29" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="BF280" s="41"/>
       <c r="BG280" s="44"/>
@@ -42955,7 +42971,7 @@
         <v>61</v>
       </c>
       <c r="B281" s="29" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="C281" s="83">
         <v>5</v>
@@ -42973,7 +42989,7 @@
         <v>47539</v>
       </c>
       <c r="H281" s="32" t="s">
-        <v>423</v>
+        <v>418</v>
       </c>
       <c r="I281" s="32">
         <v>80</v>
@@ -43065,7 +43081,7 @@
       <c r="AP281" s="40"/>
       <c r="AQ281" s="41"/>
       <c r="AR281" s="41" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
       <c r="AS281" s="41" t="s">
         <v>264</v>
@@ -43081,12 +43097,12 @@
       <c r="AZ281" s="41"/>
       <c r="BA281" s="41"/>
       <c r="BB281" s="29" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="BC281" s="41"/>
       <c r="BD281" s="41"/>
       <c r="BE281" s="29" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="BF281" s="41"/>
       <c r="BG281" s="44"/>
@@ -43096,7 +43112,7 @@
         <v>61</v>
       </c>
       <c r="B282" s="29" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="C282" s="83">
         <v>5</v>
@@ -43114,7 +43130,7 @@
         <v>47539</v>
       </c>
       <c r="H282" s="32" t="s">
-        <v>423</v>
+        <v>418</v>
       </c>
       <c r="I282" s="32">
         <v>80</v>
@@ -43206,7 +43222,7 @@
       <c r="AP282" s="40"/>
       <c r="AQ282" s="41"/>
       <c r="AR282" s="41" t="s">
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="AS282" s="41" t="s">
         <v>264</v>
@@ -43222,12 +43238,12 @@
       <c r="AZ282" s="41"/>
       <c r="BA282" s="41"/>
       <c r="BB282" s="29" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="BC282" s="41"/>
       <c r="BD282" s="41"/>
       <c r="BE282" s="29" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="BF282" s="41"/>
       <c r="BG282" s="44"/>
@@ -43237,7 +43253,7 @@
         <v>61</v>
       </c>
       <c r="B283" s="29" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="C283" s="83">
         <v>5</v>
@@ -43255,7 +43271,7 @@
         <v>47539</v>
       </c>
       <c r="H283" s="32" t="s">
-        <v>423</v>
+        <v>418</v>
       </c>
       <c r="I283" s="32">
         <v>80</v>
@@ -43347,7 +43363,7 @@
       <c r="AP283" s="40"/>
       <c r="AQ283" s="41"/>
       <c r="AR283" s="41" t="s">
-        <v>431</v>
+        <v>426</v>
       </c>
       <c r="AS283" s="41" t="s">
         <v>264</v>
@@ -43363,12 +43379,12 @@
       <c r="AZ283" s="41"/>
       <c r="BA283" s="41"/>
       <c r="BB283" s="29" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="BC283" s="41"/>
       <c r="BD283" s="41"/>
       <c r="BE283" s="29" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="BF283" s="41"/>
       <c r="BG283" s="44"/>
@@ -43378,7 +43394,7 @@
         <v>61</v>
       </c>
       <c r="B284" s="29" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="C284" s="83">
         <v>5</v>
@@ -43396,7 +43412,7 @@
         <v>47539</v>
       </c>
       <c r="H284" s="32" t="s">
-        <v>423</v>
+        <v>418</v>
       </c>
       <c r="I284" s="32">
         <v>80</v>
@@ -43490,7 +43506,7 @@
       <c r="AP284" s="40"/>
       <c r="AQ284" s="41"/>
       <c r="AR284" s="41" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="AS284" s="41" t="s">
         <v>264</v>
@@ -43506,12 +43522,12 @@
       <c r="AZ284" s="41"/>
       <c r="BA284" s="41"/>
       <c r="BB284" s="29" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="BC284" s="41"/>
       <c r="BD284" s="41"/>
       <c r="BE284" s="29" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="BF284" s="41"/>
       <c r="BG284" s="44"/>
@@ -43521,7 +43537,7 @@
         <v>61</v>
       </c>
       <c r="B285" s="29" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="C285" s="83">
         <v>4</v>
@@ -43539,7 +43555,7 @@
         <v>36667</v>
       </c>
       <c r="H285" s="32" t="s">
-        <v>423</v>
+        <v>418</v>
       </c>
       <c r="I285" s="32">
         <v>80</v>
@@ -43631,7 +43647,7 @@
       <c r="AP285" s="40"/>
       <c r="AQ285" s="41"/>
       <c r="AR285" s="41" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="AS285" s="41" t="s">
         <v>264</v>
@@ -43647,12 +43663,12 @@
       <c r="AZ285" s="41"/>
       <c r="BA285" s="41"/>
       <c r="BB285" s="29" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="BC285" s="41"/>
       <c r="BD285" s="41"/>
       <c r="BE285" s="29" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="BF285" s="41"/>
       <c r="BG285" s="44"/>
@@ -43662,7 +43678,7 @@
         <v>61</v>
       </c>
       <c r="B286" s="29" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="C286" s="83">
         <v>4</v>
@@ -43680,7 +43696,7 @@
         <v>36667</v>
       </c>
       <c r="H286" s="32" t="s">
-        <v>423</v>
+        <v>418</v>
       </c>
       <c r="I286" s="32">
         <v>80</v>
@@ -43772,7 +43788,7 @@
       <c r="AP286" s="40"/>
       <c r="AQ286" s="41"/>
       <c r="AR286" s="41" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="AS286" s="41" t="s">
         <v>264</v>
@@ -43788,12 +43804,12 @@
       <c r="AZ286" s="41"/>
       <c r="BA286" s="41"/>
       <c r="BB286" s="29" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="BC286" s="41"/>
       <c r="BD286" s="41"/>
       <c r="BE286" s="29" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="BF286" s="41"/>
       <c r="BG286" s="44"/>
@@ -43803,7 +43819,7 @@
         <v>61</v>
       </c>
       <c r="B287" s="29" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="C287" s="83">
         <v>4</v>
@@ -43821,7 +43837,7 @@
         <v>36667</v>
       </c>
       <c r="H287" s="32" t="s">
-        <v>423</v>
+        <v>418</v>
       </c>
       <c r="I287" s="32">
         <v>80</v>
@@ -43913,7 +43929,7 @@
       <c r="AP287" s="40"/>
       <c r="AQ287" s="41"/>
       <c r="AR287" s="41" t="s">
-        <v>436</v>
+        <v>431</v>
       </c>
       <c r="AS287" s="41" t="s">
         <v>264</v>
@@ -43929,12 +43945,12 @@
       <c r="AZ287" s="41"/>
       <c r="BA287" s="41"/>
       <c r="BB287" s="29" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="BC287" s="41"/>
       <c r="BD287" s="41"/>
       <c r="BE287" s="29" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="BF287" s="41"/>
       <c r="BG287" s="44"/>
@@ -43944,7 +43960,7 @@
         <v>61</v>
       </c>
       <c r="B288" s="29" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="C288" s="83">
         <v>4</v>
@@ -43962,7 +43978,7 @@
         <v>36667</v>
       </c>
       <c r="H288" s="32" t="s">
-        <v>423</v>
+        <v>418</v>
       </c>
       <c r="I288" s="32">
         <v>80</v>
@@ -44054,7 +44070,7 @@
       <c r="AP288" s="40"/>
       <c r="AQ288" s="41"/>
       <c r="AR288" s="41" t="s">
-        <v>437</v>
+        <v>432</v>
       </c>
       <c r="AS288" s="41" t="s">
         <v>264</v>
@@ -44070,12 +44086,12 @@
       <c r="AZ288" s="41"/>
       <c r="BA288" s="41"/>
       <c r="BB288" s="29" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="BC288" s="41"/>
       <c r="BD288" s="41"/>
       <c r="BE288" s="29" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="BF288" s="41"/>
       <c r="BG288" s="44"/>
@@ -44085,7 +44101,7 @@
         <v>61</v>
       </c>
       <c r="B289" s="29" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="C289" s="83">
         <v>4</v>
@@ -44103,7 +44119,7 @@
         <v>36667</v>
       </c>
       <c r="H289" s="32" t="s">
-        <v>423</v>
+        <v>418</v>
       </c>
       <c r="I289" s="32">
         <v>80</v>
@@ -44197,7 +44213,7 @@
       <c r="AP289" s="40"/>
       <c r="AQ289" s="41"/>
       <c r="AR289" s="41" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="AS289" s="41" t="s">
         <v>264</v>
@@ -44213,12 +44229,12 @@
       <c r="AZ289" s="41"/>
       <c r="BA289" s="41"/>
       <c r="BB289" s="29" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="BC289" s="41"/>
       <c r="BD289" s="41"/>
       <c r="BE289" s="29" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="BF289" s="41"/>
       <c r="BG289" s="44"/>
@@ -44228,7 +44244,7 @@
         <v>61</v>
       </c>
       <c r="B290" s="29" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="C290" s="83">
         <v>4</v>
@@ -44246,7 +44262,7 @@
         <v>36667</v>
       </c>
       <c r="H290" s="32" t="s">
-        <v>423</v>
+        <v>418</v>
       </c>
       <c r="I290" s="32">
         <v>80</v>
@@ -44338,7 +44354,7 @@
       <c r="AP290" s="40"/>
       <c r="AQ290" s="41"/>
       <c r="AR290" s="41" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="AS290" s="41" t="s">
         <v>264</v>
@@ -44354,12 +44370,12 @@
       <c r="AZ290" s="41"/>
       <c r="BA290" s="41"/>
       <c r="BB290" s="29" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="BC290" s="41"/>
       <c r="BD290" s="41"/>
       <c r="BE290" s="29" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="BF290" s="41"/>
       <c r="BG290" s="44"/>
@@ -44369,7 +44385,7 @@
         <v>61</v>
       </c>
       <c r="B291" s="29" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="C291" s="83">
         <v>4</v>
@@ -44387,7 +44403,7 @@
         <v>36667</v>
       </c>
       <c r="H291" s="32" t="s">
-        <v>423</v>
+        <v>418</v>
       </c>
       <c r="I291" s="32">
         <v>80</v>
@@ -44479,7 +44495,7 @@
       <c r="AP291" s="40"/>
       <c r="AQ291" s="41"/>
       <c r="AR291" s="41" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="AS291" s="41" t="s">
         <v>264</v>
@@ -44495,12 +44511,12 @@
       <c r="AZ291" s="41"/>
       <c r="BA291" s="41"/>
       <c r="BB291" s="29" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="BC291" s="41"/>
       <c r="BD291" s="41"/>
       <c r="BE291" s="29" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="BF291" s="41"/>
       <c r="BG291" s="44"/>
@@ -44510,7 +44526,7 @@
         <v>61</v>
       </c>
       <c r="B292" s="29" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="C292" s="83">
         <v>4</v>
@@ -44528,7 +44544,7 @@
         <v>36667</v>
       </c>
       <c r="H292" s="32" t="s">
-        <v>423</v>
+        <v>418</v>
       </c>
       <c r="I292" s="32">
         <v>80</v>
@@ -44620,7 +44636,7 @@
       <c r="AP292" s="40"/>
       <c r="AQ292" s="41"/>
       <c r="AR292" s="41" t="s">
-        <v>442</v>
+        <v>437</v>
       </c>
       <c r="AS292" s="41" t="s">
         <v>264</v>
@@ -44636,12 +44652,12 @@
       <c r="AZ292" s="41"/>
       <c r="BA292" s="41"/>
       <c r="BB292" s="29" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="BC292" s="41"/>
       <c r="BD292" s="41"/>
       <c r="BE292" s="29" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="BF292" s="41"/>
       <c r="BG292" s="44"/>
@@ -44651,7 +44667,7 @@
         <v>61</v>
       </c>
       <c r="B293" s="29" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="C293" s="83">
         <v>4</v>
@@ -44669,7 +44685,7 @@
         <v>36667</v>
       </c>
       <c r="H293" s="32" t="s">
-        <v>423</v>
+        <v>418</v>
       </c>
       <c r="I293" s="32">
         <v>80</v>
@@ -44761,7 +44777,7 @@
       <c r="AP293" s="40"/>
       <c r="AQ293" s="41"/>
       <c r="AR293" s="41" t="s">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="AS293" s="41" t="s">
         <v>264</v>
@@ -44777,12 +44793,12 @@
       <c r="AZ293" s="41"/>
       <c r="BA293" s="41"/>
       <c r="BB293" s="29" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="BC293" s="41"/>
       <c r="BD293" s="41"/>
       <c r="BE293" s="29" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="BF293" s="41"/>
       <c r="BG293" s="44"/>
@@ -44792,7 +44808,7 @@
         <v>61</v>
       </c>
       <c r="B294" s="29" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="C294" s="83">
         <v>4</v>
@@ -44810,7 +44826,7 @@
         <v>36667</v>
       </c>
       <c r="H294" s="32" t="s">
-        <v>423</v>
+        <v>418</v>
       </c>
       <c r="I294" s="32">
         <v>80</v>
@@ -44904,7 +44920,7 @@
       <c r="AP294" s="40"/>
       <c r="AQ294" s="41"/>
       <c r="AR294" s="41" t="s">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="AS294" s="41" t="s">
         <v>264</v>
@@ -44920,12 +44936,12 @@
       <c r="AZ294" s="41"/>
       <c r="BA294" s="41"/>
       <c r="BB294" s="29" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="BC294" s="41"/>
       <c r="BD294" s="41"/>
       <c r="BE294" s="29" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="BF294" s="41"/>
       <c r="BG294" s="44"/>
@@ -44935,7 +44951,7 @@
         <v>61</v>
       </c>
       <c r="B295" s="29" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="C295" s="83">
         <v>3</v>
@@ -44953,7 +44969,7 @@
         <v>27662</v>
       </c>
       <c r="H295" s="32" t="s">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="I295" s="32">
         <v>80</v>
@@ -45045,7 +45061,7 @@
       <c r="AP295" s="40"/>
       <c r="AQ295" s="41"/>
       <c r="AR295" s="41" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="AS295" s="41" t="s">
         <v>264</v>
@@ -45061,12 +45077,12 @@
       <c r="AZ295" s="41"/>
       <c r="BA295" s="41"/>
       <c r="BB295" s="29" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="BC295" s="41"/>
       <c r="BD295" s="41"/>
       <c r="BE295" s="29" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="BF295" s="41"/>
       <c r="BG295" s="44"/>
@@ -45076,7 +45092,7 @@
         <v>61</v>
       </c>
       <c r="B296" s="29" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="C296" s="83">
         <v>3</v>
@@ -45094,7 +45110,7 @@
         <v>27662</v>
       </c>
       <c r="H296" s="32" t="s">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="I296" s="32">
         <v>80</v>
@@ -45186,7 +45202,7 @@
       <c r="AP296" s="40"/>
       <c r="AQ296" s="41"/>
       <c r="AR296" s="41" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="AS296" s="41" t="s">
         <v>264</v>
@@ -45202,12 +45218,12 @@
       <c r="AZ296" s="41"/>
       <c r="BA296" s="41"/>
       <c r="BB296" s="29" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="BC296" s="41"/>
       <c r="BD296" s="41"/>
       <c r="BE296" s="29" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="BF296" s="41"/>
       <c r="BG296" s="44"/>
@@ -45217,7 +45233,7 @@
         <v>61</v>
       </c>
       <c r="B297" s="29" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="C297" s="83">
         <v>3</v>
@@ -45235,7 +45251,7 @@
         <v>27662</v>
       </c>
       <c r="H297" s="32" t="s">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="I297" s="32">
         <v>80</v>
@@ -45327,7 +45343,7 @@
       <c r="AP297" s="40"/>
       <c r="AQ297" s="41"/>
       <c r="AR297" s="41" t="s">
-        <v>449</v>
+        <v>444</v>
       </c>
       <c r="AS297" s="41" t="s">
         <v>264</v>
@@ -45343,12 +45359,12 @@
       <c r="AZ297" s="41"/>
       <c r="BA297" s="41"/>
       <c r="BB297" s="29" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="BC297" s="41"/>
       <c r="BD297" s="41"/>
       <c r="BE297" s="29" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="BF297" s="41"/>
       <c r="BG297" s="44"/>
@@ -45358,7 +45374,7 @@
         <v>61</v>
       </c>
       <c r="B298" s="29" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="C298" s="83">
         <v>3</v>
@@ -45376,7 +45392,7 @@
         <v>27662</v>
       </c>
       <c r="H298" s="32" t="s">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="I298" s="32">
         <v>80</v>
@@ -45470,7 +45486,7 @@
       <c r="AP298" s="40"/>
       <c r="AQ298" s="41"/>
       <c r="AR298" s="41" t="s">
-        <v>450</v>
+        <v>445</v>
       </c>
       <c r="AS298" s="41" t="s">
         <v>264</v>
@@ -45486,12 +45502,12 @@
       <c r="AZ298" s="41"/>
       <c r="BA298" s="41"/>
       <c r="BB298" s="29" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="BC298" s="41"/>
       <c r="BD298" s="41"/>
       <c r="BE298" s="29" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="BF298" s="41"/>
       <c r="BG298" s="44"/>
@@ -45501,7 +45517,7 @@
         <v>61</v>
       </c>
       <c r="B299" s="29" t="s">
-        <v>451</v>
+        <v>446</v>
       </c>
       <c r="C299" s="83">
         <v>3</v>
@@ -45519,7 +45535,7 @@
         <v>28087</v>
       </c>
       <c r="H299" s="32" t="s">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="I299" s="32">
         <v>80</v>
@@ -45611,7 +45627,7 @@
       <c r="AP299" s="40"/>
       <c r="AQ299" s="41"/>
       <c r="AR299" s="41" t="s">
-        <v>452</v>
+        <v>447</v>
       </c>
       <c r="AS299" s="41" t="s">
         <v>264</v>
@@ -45627,12 +45643,12 @@
       <c r="AZ299" s="41"/>
       <c r="BA299" s="41"/>
       <c r="BB299" s="29" t="s">
-        <v>451</v>
+        <v>446</v>
       </c>
       <c r="BC299" s="41"/>
       <c r="BD299" s="41"/>
       <c r="BE299" s="29" t="s">
-        <v>451</v>
+        <v>446</v>
       </c>
       <c r="BF299" s="41"/>
       <c r="BG299" s="44"/>
@@ -45642,7 +45658,7 @@
         <v>61</v>
       </c>
       <c r="B300" s="29" t="s">
-        <v>451</v>
+        <v>446</v>
       </c>
       <c r="C300" s="83">
         <v>3</v>
@@ -45660,7 +45676,7 @@
         <v>28087</v>
       </c>
       <c r="H300" s="32" t="s">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="I300" s="32">
         <v>80</v>
@@ -45752,7 +45768,7 @@
       <c r="AP300" s="40"/>
       <c r="AQ300" s="41"/>
       <c r="AR300" s="41" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="AS300" s="41" t="s">
         <v>264</v>
@@ -45768,12 +45784,12 @@
       <c r="AZ300" s="41"/>
       <c r="BA300" s="41"/>
       <c r="BB300" s="29" t="s">
-        <v>451</v>
+        <v>446</v>
       </c>
       <c r="BC300" s="41"/>
       <c r="BD300" s="41"/>
       <c r="BE300" s="29" t="s">
-        <v>451</v>
+        <v>446</v>
       </c>
       <c r="BF300" s="41"/>
       <c r="BG300" s="44"/>
@@ -45783,7 +45799,7 @@
         <v>61</v>
       </c>
       <c r="B301" s="29" t="s">
-        <v>451</v>
+        <v>446</v>
       </c>
       <c r="C301" s="83">
         <v>3</v>
@@ -45801,7 +45817,7 @@
         <v>28087</v>
       </c>
       <c r="H301" s="32" t="s">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="I301" s="32">
         <v>80</v>
@@ -45893,7 +45909,7 @@
       <c r="AP301" s="40"/>
       <c r="AQ301" s="41"/>
       <c r="AR301" s="41" t="s">
-        <v>454</v>
+        <v>449</v>
       </c>
       <c r="AS301" s="41" t="s">
         <v>264</v>
@@ -45909,12 +45925,12 @@
       <c r="AZ301" s="41"/>
       <c r="BA301" s="41"/>
       <c r="BB301" s="29" t="s">
-        <v>451</v>
+        <v>446</v>
       </c>
       <c r="BC301" s="41"/>
       <c r="BD301" s="41"/>
       <c r="BE301" s="29" t="s">
-        <v>451</v>
+        <v>446</v>
       </c>
       <c r="BF301" s="41"/>
       <c r="BG301" s="44"/>
@@ -45924,7 +45940,7 @@
         <v>61</v>
       </c>
       <c r="B302" s="100" t="s">
-        <v>451</v>
+        <v>446</v>
       </c>
       <c r="C302" s="101">
         <v>3</v>
@@ -45942,7 +45958,7 @@
         <v>28087</v>
       </c>
       <c r="H302" s="71" t="s">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="I302" s="71">
         <v>80</v>
@@ -46036,7 +46052,7 @@
       <c r="AP302" s="66"/>
       <c r="AQ302" s="67"/>
       <c r="AR302" s="67" t="s">
-        <v>455</v>
+        <v>450</v>
       </c>
       <c r="AS302" s="67" t="s">
         <v>264</v>
@@ -46052,12 +46068,12 @@
       <c r="AZ302" s="67"/>
       <c r="BA302" s="67"/>
       <c r="BB302" s="100" t="s">
-        <v>451</v>
+        <v>446</v>
       </c>
       <c r="BC302" s="67"/>
       <c r="BD302" s="67"/>
       <c r="BE302" s="100" t="s">
-        <v>451</v>
+        <v>446</v>
       </c>
       <c r="BF302" s="67"/>
       <c r="BG302" s="70"/>
@@ -46179,7 +46195,7 @@
       <c r="AP303" s="80"/>
       <c r="AQ303" s="81"/>
       <c r="AR303" s="114" t="s">
-        <v>468</v>
+        <v>463</v>
       </c>
       <c r="AS303" s="81" t="s">
         <v>295</v>
@@ -46322,7 +46338,7 @@
       <c r="AP304" s="40"/>
       <c r="AQ304" s="41"/>
       <c r="AR304" s="115" t="s">
-        <v>469</v>
+        <v>464</v>
       </c>
       <c r="AS304" s="41" t="s">
         <v>295</v>
@@ -46465,7 +46481,7 @@
       <c r="AP305" s="40"/>
       <c r="AQ305" s="41"/>
       <c r="AR305" s="115" t="s">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="AS305" s="41" t="s">
         <v>295</v>
@@ -46608,7 +46624,7 @@
       <c r="AP306" s="40"/>
       <c r="AQ306" s="41"/>
       <c r="AR306" s="115" t="s">
-        <v>471</v>
+        <v>466</v>
       </c>
       <c r="AS306" s="41" t="s">
         <v>295</v>
@@ -46751,7 +46767,7 @@
       <c r="AP307" s="40"/>
       <c r="AQ307" s="41"/>
       <c r="AR307" s="115" t="s">
-        <v>472</v>
+        <v>467</v>
       </c>
       <c r="AS307" s="41" t="s">
         <v>295</v>
@@ -46894,7 +46910,7 @@
       <c r="AP308" s="91"/>
       <c r="AQ308" s="92"/>
       <c r="AR308" s="116" t="s">
-        <v>473</v>
+        <v>468</v>
       </c>
       <c r="AS308" s="92" t="s">
         <v>295</v>
@@ -46975,37 +46991,37 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>456</v>
+        <v>451</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>457</v>
+        <v>452</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>458</v>
+        <v>453</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>460</v>
+        <v>455</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>461</v>
+        <v>456</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>462</v>
+        <v>457</v>
       </c>
     </row>
   </sheetData>
